--- a/models/Master_Commodity_Treasury_Model.xlsx
+++ b/models/Master_Commodity_Treasury_Model.xlsx
@@ -8,16 +8,17 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interactive Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="75% Annual" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="80% Annual" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="85% Annual" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="100% Annual" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="120% Annual" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIFT City CME Bridge" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Employee Legal Framework" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NG Risk and Sizing" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NG Inputs" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NG Data" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="50% Annual" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="75% Annual" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="80% Annual" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="85% Annual" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="100% Annual" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="120% Annual" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIFT City CME Bridge" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Employee Legal Framework" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NG Risk and Sizing" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NG Inputs" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NG Data" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9614,6 +9615,686 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>NG RISK AND SIZING  ·  roll cost · margin-hike trap · Kelly</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="36" t="inlineStr">
+        <is>
+          <t>Three small natural-gas checks on one page. Blue = edit here, green = linked from NG Inputs / NG Data / NG Scenarios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="37" t="inlineStr">
+        <is>
+          <t>1 · ROLL &amp; COST DRAG  —  what rolling contracts and costs take from return on capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="38" t="inlineStr">
+        <is>
+          <t>Roll gap per roll (% notional)</t>
+        </is>
+      </c>
+      <c r="B5" s="39" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C5" s="40" t="inlineStr">
+        <is>
+          <t>Placeholder — measure from your prices; contango months can exceed 2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="38" t="inlineStr">
+        <is>
+          <t>Expected rolls per trade</t>
+        </is>
+      </c>
+      <c r="B6" s="41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C6" s="40" t="inlineStr">
+        <is>
+          <t>Swing duration ÷ contract window</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="38" t="inlineStr">
+        <is>
+          <t>Txn + brokerage round trip (% notional)</t>
+        </is>
+      </c>
+      <c r="B7" s="42">
+        <f>'NG Inputs'!B6</f>
+        <v/>
+      </c>
+      <c r="C7" s="40" t="inlineStr">
+        <is>
+          <t>From NG Inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="38" t="inlineStr">
+        <is>
+          <t>Margin % (base case)</t>
+        </is>
+      </c>
+      <c r="B8" s="43">
+        <f>'NG Data'!D134</f>
+        <v/>
+      </c>
+      <c r="C8" s="40" t="inlineStr">
+        <is>
+          <t>25–30% bucket average from NG Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="38" t="inlineStr">
+        <is>
+          <t>Gross move per trade</t>
+        </is>
+      </c>
+      <c r="B9" s="43">
+        <f>'NG Scenarios'!B6</f>
+        <v/>
+      </c>
+      <c r="C9" s="40" t="inlineStr">
+        <is>
+          <t>Base-case move from NG Scenarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="38" t="inlineStr">
+        <is>
+          <t>Company tax rate</t>
+        </is>
+      </c>
+      <c r="B10" s="43">
+        <f>'NG Inputs'!B4</f>
+        <v/>
+      </c>
+      <c r="C10" s="40" t="inlineStr">
+        <is>
+          <t>From NG Inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="38" t="inlineStr">
+        <is>
+          <t>Cost per trade (% notional)</t>
+        </is>
+      </c>
+      <c r="B11" s="44">
+        <f>B5*B6+B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="38" t="inlineStr">
+        <is>
+          <t>Gross return on capital per trade</t>
+        </is>
+      </c>
+      <c r="B12" s="44">
+        <f>B9/B8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="38" t="inlineStr">
+        <is>
+          <t>ROC drag from costs</t>
+        </is>
+      </c>
+      <c r="B13" s="44">
+        <f>(B5*B6+B7)/B8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="38" t="inlineStr">
+        <is>
+          <t>NET return on capital per trade</t>
+        </is>
+      </c>
+      <c r="B14" s="44">
+        <f>(B9-B5*B6-B7)/B8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="38" t="inlineStr">
+        <is>
+          <t>Return lost per trade (points of ROC)</t>
+        </is>
+      </c>
+      <c r="B15" s="44">
+        <f>B12-B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="38" t="inlineStr">
+        <is>
+          <t>15-year terminal impact, 2 trades/yr, after tax (× factor)</t>
+        </is>
+      </c>
+      <c r="B16" s="45">
+        <f>((1+B14*(1-B10))/(1+B12*(1-B10)))^30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="37" t="inlineStr">
+        <is>
+          <t>2 · MARGIN-HIKE TRAP  —  chance of capital being locked at a higher margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="38" t="inlineStr">
+        <is>
+          <t>Quiet-spike events observed</t>
+        </is>
+      </c>
+      <c r="B19" s="46" t="n">
+        <v>23</v>
+      </c>
+      <c r="C19" s="40" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="38" t="inlineStr">
+        <is>
+          <t>Observation years</t>
+        </is>
+      </c>
+      <c r="B20" s="47" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="C20" s="40" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="38" t="inlineStr">
+        <is>
+          <t>Trading days per year</t>
+        </is>
+      </c>
+      <c r="B21" s="46" t="n">
+        <v>250</v>
+      </c>
+      <c r="C21" s="40" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="38" t="inlineStr">
+        <is>
+          <t>Trade window (days)</t>
+        </is>
+      </c>
+      <c r="B22" s="46" t="n">
+        <v>30</v>
+      </c>
+      <c r="C22" s="40" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="38" t="inlineStr">
+        <is>
+          <t>Margin before hike</t>
+        </is>
+      </c>
+      <c r="B23" s="48">
+        <f>B8</f>
+        <v/>
+      </c>
+      <c r="C23" s="40" t="inlineStr">
+        <is>
+          <t>Linked to section 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="38" t="inlineStr">
+        <is>
+          <t>Margin after hike</t>
+        </is>
+      </c>
+      <c r="B24" s="39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C24" s="40" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="38" t="inlineStr">
+        <is>
+          <t>Share of move still to come when hiked</t>
+        </is>
+      </c>
+      <c r="B25" s="39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C25" s="40" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="38" t="inlineStr">
+        <is>
+          <t>Base gross ROC per trade</t>
+        </is>
+      </c>
+      <c r="B26" s="48">
+        <f>B12</f>
+        <v/>
+      </c>
+      <c r="C26" s="40" t="inlineStr">
+        <is>
+          <t>Linked to section 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="38" t="inlineStr">
+        <is>
+          <t>Daily quiet-spike probability</t>
+        </is>
+      </c>
+      <c r="B27" s="49">
+        <f>B19/(B20*B21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="38" t="inlineStr">
+        <is>
+          <t>Chance of a hike inside one trade window</t>
+        </is>
+      </c>
+      <c r="B28" s="44">
+        <f>1-(1-B19/(B20*B21))^B22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="38" t="inlineStr">
+        <is>
+          <t>Forced position cut if fully deployed</t>
+        </is>
+      </c>
+      <c r="B29" s="44">
+        <f>1-B23/B24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="38" t="inlineStr">
+        <is>
+          <t>Expected ROC haircut per trade</t>
+        </is>
+      </c>
+      <c r="B30" s="44">
+        <f>B28*B29*B25*B26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="38" t="inlineStr">
+        <is>
+          <t>Annualised return drag (2 trades/yr, after tax)</t>
+        </is>
+      </c>
+      <c r="B31" s="44">
+        <f>((1+(B26-B30)*(1-B10))^2)/((1+B26*(1-B10))^2)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="40" t="inlineStr">
+        <is>
+          <t>Rule: keep free collateral of at least 1 − (margin before ÷ margin after) of the corpus; another reason to stay below full Kelly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="37" t="inlineStr">
+        <is>
+          <t>3 · KELLY SIZING  —  how much of the corpus to put up as margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="38" t="inlineStr">
+        <is>
+          <t>Win probability p (YOUR estimate)</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C35" s="40" t="inlineStr">
+        <is>
+          <t>Not data-derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="38" t="inlineStr">
+        <is>
+          <t>Win return on capital b</t>
+        </is>
+      </c>
+      <c r="B36" s="48">
+        <f>B12</f>
+        <v/>
+      </c>
+      <c r="C36" s="40" t="inlineStr">
+        <is>
+          <t>Linked to section 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="38" t="inlineStr">
+        <is>
+          <t>Stop-loss adverse move</t>
+        </is>
+      </c>
+      <c r="B37" s="39" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C37" s="40" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="38" t="inlineStr">
+        <is>
+          <t>Margin %</t>
+        </is>
+      </c>
+      <c r="B38" s="48">
+        <f>B8</f>
+        <v/>
+      </c>
+      <c r="C38" s="40" t="inlineStr">
+        <is>
+          <t>Linked to section 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="38" t="inlineStr">
+        <is>
+          <t>Loss per unit staked (stop ÷ margin)</t>
+        </is>
+      </c>
+      <c r="B39" s="44">
+        <f>B37/B38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="38" t="inlineStr">
+        <is>
+          <t>Full Kelly f* = p/a − (1−p)/b</t>
+        </is>
+      </c>
+      <c r="B40" s="51">
+        <f>B35/B39-(1-B35)/B36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="38" t="inlineStr">
+        <is>
+          <t>Deployable (capped at 100%)</t>
+        </is>
+      </c>
+      <c r="B41" s="52">
+        <f>MIN(B40,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="38" t="inlineStr">
+        <is>
+          <t>Half-Kelly (recommended)</t>
+        </is>
+      </c>
+      <c r="B42" s="52">
+        <f>MIN(B40/2,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="38" t="inlineStr">
+        <is>
+          <t>Expected log-growth per trade at half-Kelly</t>
+        </is>
+      </c>
+      <c r="B43" s="53">
+        <f>B35*LN(1+B42*B36)+(1-B35)*LN(1-B42*B39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t>Sanity check</t>
+        </is>
+      </c>
+      <c r="B44" s="54">
+        <f>IF(B40&gt;1,"⚠ Full Kelly is above 100% — your win rate / stop imply an unrealistic edge; size well below it","OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="55" t="inlineStr">
+        <is>
+          <t>Full-Kelly sensitivity  —  win probability (rows) × stop-loss move (columns)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="56" t="inlineStr">
+        <is>
+          <t>p \ stop</t>
+        </is>
+      </c>
+      <c r="B47" s="57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C47" s="57" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D47" s="57" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E47" s="57" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F47" s="57" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="50" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="B48" s="58">
+        <f>$A48/(B$47/$B$38)-(1-$A48)/$B$36</f>
+        <v/>
+      </c>
+      <c r="C48" s="58">
+        <f>$A48/(C$47/$B$38)-(1-$A48)/$B$36</f>
+        <v/>
+      </c>
+      <c r="D48" s="58">
+        <f>$A48/(D$47/$B$38)-(1-$A48)/$B$36</f>
+        <v/>
+      </c>
+      <c r="E48" s="58">
+        <f>$A48/(E$47/$B$38)-(1-$A48)/$B$36</f>
+        <v/>
+      </c>
+      <c r="F48" s="58">
+        <f>$A48/(F$47/$B$38)-(1-$A48)/$B$36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B49" s="58">
+        <f>$A49/(B$47/$B$38)-(1-$A49)/$B$36</f>
+        <v/>
+      </c>
+      <c r="C49" s="58">
+        <f>$A49/(C$47/$B$38)-(1-$A49)/$B$36</f>
+        <v/>
+      </c>
+      <c r="D49" s="58">
+        <f>$A49/(D$47/$B$38)-(1-$A49)/$B$36</f>
+        <v/>
+      </c>
+      <c r="E49" s="58">
+        <f>$A49/(E$47/$B$38)-(1-$A49)/$B$36</f>
+        <v/>
+      </c>
+      <c r="F49" s="58">
+        <f>$A49/(F$47/$B$38)-(1-$A49)/$B$36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="50" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="B50" s="58">
+        <f>$A50/(B$47/$B$38)-(1-$A50)/$B$36</f>
+        <v/>
+      </c>
+      <c r="C50" s="58">
+        <f>$A50/(C$47/$B$38)-(1-$A50)/$B$36</f>
+        <v/>
+      </c>
+      <c r="D50" s="58">
+        <f>$A50/(D$47/$B$38)-(1-$A50)/$B$36</f>
+        <v/>
+      </c>
+      <c r="E50" s="58">
+        <f>$A50/(E$47/$B$38)-(1-$A50)/$B$36</f>
+        <v/>
+      </c>
+      <c r="F50" s="58">
+        <f>$A50/(F$47/$B$38)-(1-$A50)/$B$36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="50" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="B51" s="58">
+        <f>$A51/(B$47/$B$38)-(1-$A51)/$B$36</f>
+        <v/>
+      </c>
+      <c r="C51" s="58">
+        <f>$A51/(C$47/$B$38)-(1-$A51)/$B$36</f>
+        <v/>
+      </c>
+      <c r="D51" s="58">
+        <f>$A51/(D$47/$B$38)-(1-$A51)/$B$36</f>
+        <v/>
+      </c>
+      <c r="E51" s="58">
+        <f>$A51/(E$47/$B$38)-(1-$A51)/$B$36</f>
+        <v/>
+      </c>
+      <c r="F51" s="58">
+        <f>$A51/(F$47/$B$38)-(1-$A51)/$B$36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="50" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="B52" s="58">
+        <f>$A52/(B$47/$B$38)-(1-$A52)/$B$36</f>
+        <v/>
+      </c>
+      <c r="C52" s="58">
+        <f>$A52/(C$47/$B$38)-(1-$A52)/$B$36</f>
+        <v/>
+      </c>
+      <c r="D52" s="58">
+        <f>$A52/(D$47/$B$38)-(1-$A52)/$B$36</f>
+        <v/>
+      </c>
+      <c r="E52" s="58">
+        <f>$A52/(E$47/$B$38)-(1-$A52)/$B$36</f>
+        <v/>
+      </c>
+      <c r="F52" s="58">
+        <f>$A52/(F$47/$B$38)-(1-$A52)/$B$36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="50" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B53" s="58">
+        <f>$A53/(B$47/$B$38)-(1-$A53)/$B$36</f>
+        <v/>
+      </c>
+      <c r="C53" s="58">
+        <f>$A53/(C$47/$B$38)-(1-$A53)/$B$36</f>
+        <v/>
+      </c>
+      <c r="D53" s="58">
+        <f>$A53/(D$47/$B$38)-(1-$A53)/$B$36</f>
+        <v/>
+      </c>
+      <c r="E53" s="58">
+        <f>$A53/(E$47/$B$38)-(1-$A53)/$B$36</f>
+        <v/>
+      </c>
+      <c r="F53" s="58">
+        <f>$A53/(F$47/$B$38)-(1-$A53)/$B$36</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -9788,7 +10469,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="69" t="inlineStr">
         <is>
@@ -9897,8 +10577,6 @@
         <v/>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="56" t="inlineStr">
         <is>
@@ -9953,7 +10631,6 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="38" t="inlineStr">
         <is>
@@ -9984,7 +10661,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10014,7 +10691,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="61" t="inlineStr">
         <is>
@@ -12379,8 +13055,6 @@
         <v/>
       </c>
     </row>
-    <row r="128"/>
-    <row r="129"/>
     <row r="130">
       <c r="A130" s="77" t="inlineStr">
         <is>
@@ -12528,7 +13202,6 @@
         <v/>
       </c>
     </row>
-    <row r="136"/>
     <row r="137">
       <c r="A137" s="88" t="inlineStr">
         <is>
@@ -12588,14 +13261,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MCX COMMODITY TREASURY MODEL  ·  75% ANNUAL</t>
+          <t>MCX COMMODITY TREASURY MODEL  ·  50% ANNUAL</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Conservative Baseline (75% Return) · Live inputs: cream cells. All 20-year cycles dynamically evaluate.</t>
+          <t>Conservative Growth Tier (50% Return) · Live inputs: cream cells. All 20-year cycles dynamically evaluate.</t>
         </is>
       </c>
     </row>
@@ -12623,7 +13296,7 @@
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -19741,6 +20414,7186 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N166"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="106" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="31" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MCX COMMODITY TREASURY MODEL  ·  75% ANNUAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Conservative Baseline (75% Return) · Live inputs: cream cells. All 20-year cycles dynamically evaluate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>MODEL INPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Starting Capital (₹ Cr)</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>Annual Return</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>Company Tax Rate</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>0.25168</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Loanback Share</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>Salary Ceiling / Employee (₹ Cr)</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="n">
+        <v>0.1275</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>Salary Profit Fraction Cap</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Company Annual Costs (₹ Cr)</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Deployable Ceiling (₹ Cr)</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="n">
+        <v>103.0917</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Idle Cash Yield</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>0.065</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>CLOSING TRADING CAPITAL — ALL ROUTES, CYCLE 0–20 (₹ Cr)  [75% Annual]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Company Solo</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Company + 1 Staff</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>Company + 2 Staff</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Company + 3 Staff</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>3 Staff Advantage</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>3 Staff Loan Debt</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>Net Equity (Capital - Loans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B17" s="15">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="C17" s="15">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="D17" s="15">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="E17" s="15">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="F17" s="15">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="15">
+        <f>$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="15">
+        <f>M47</f>
+        <v/>
+      </c>
+      <c r="C18" s="15">
+        <f>M72</f>
+        <v/>
+      </c>
+      <c r="D18" s="15">
+        <f>M97</f>
+        <v/>
+      </c>
+      <c r="E18" s="15">
+        <f>M122</f>
+        <v/>
+      </c>
+      <c r="F18" s="25">
+        <f>M147</f>
+        <v/>
+      </c>
+      <c r="G18" s="26">
+        <f>F18-C18</f>
+        <v/>
+      </c>
+      <c r="H18" s="15">
+        <f>L147</f>
+        <v/>
+      </c>
+      <c r="I18" s="15">
+        <f>N147</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="15">
+        <f>M48</f>
+        <v/>
+      </c>
+      <c r="C19" s="15">
+        <f>M73</f>
+        <v/>
+      </c>
+      <c r="D19" s="15">
+        <f>M98</f>
+        <v/>
+      </c>
+      <c r="E19" s="15">
+        <f>M123</f>
+        <v/>
+      </c>
+      <c r="F19" s="25">
+        <f>M148</f>
+        <v/>
+      </c>
+      <c r="G19" s="26">
+        <f>F19-C19</f>
+        <v/>
+      </c>
+      <c r="H19" s="15">
+        <f>L148</f>
+        <v/>
+      </c>
+      <c r="I19" s="15">
+        <f>N148</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="15">
+        <f>M49</f>
+        <v/>
+      </c>
+      <c r="C20" s="15">
+        <f>M74</f>
+        <v/>
+      </c>
+      <c r="D20" s="15">
+        <f>M99</f>
+        <v/>
+      </c>
+      <c r="E20" s="15">
+        <f>M124</f>
+        <v/>
+      </c>
+      <c r="F20" s="25">
+        <f>M149</f>
+        <v/>
+      </c>
+      <c r="G20" s="26">
+        <f>F20-C20</f>
+        <v/>
+      </c>
+      <c r="H20" s="15">
+        <f>L149</f>
+        <v/>
+      </c>
+      <c r="I20" s="15">
+        <f>N149</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="15">
+        <f>M50</f>
+        <v/>
+      </c>
+      <c r="C21" s="15">
+        <f>M75</f>
+        <v/>
+      </c>
+      <c r="D21" s="15">
+        <f>M100</f>
+        <v/>
+      </c>
+      <c r="E21" s="15">
+        <f>M125</f>
+        <v/>
+      </c>
+      <c r="F21" s="25">
+        <f>M150</f>
+        <v/>
+      </c>
+      <c r="G21" s="26">
+        <f>F21-C21</f>
+        <v/>
+      </c>
+      <c r="H21" s="15">
+        <f>L150</f>
+        <v/>
+      </c>
+      <c r="I21" s="15">
+        <f>N150</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="15">
+        <f>M51</f>
+        <v/>
+      </c>
+      <c r="C22" s="15">
+        <f>M76</f>
+        <v/>
+      </c>
+      <c r="D22" s="15">
+        <f>M101</f>
+        <v/>
+      </c>
+      <c r="E22" s="15">
+        <f>M126</f>
+        <v/>
+      </c>
+      <c r="F22" s="25">
+        <f>M151</f>
+        <v/>
+      </c>
+      <c r="G22" s="26">
+        <f>F22-C22</f>
+        <v/>
+      </c>
+      <c r="H22" s="15">
+        <f>L151</f>
+        <v/>
+      </c>
+      <c r="I22" s="15">
+        <f>N151</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="15">
+        <f>M52</f>
+        <v/>
+      </c>
+      <c r="C23" s="15">
+        <f>M77</f>
+        <v/>
+      </c>
+      <c r="D23" s="15">
+        <f>M102</f>
+        <v/>
+      </c>
+      <c r="E23" s="15">
+        <f>M127</f>
+        <v/>
+      </c>
+      <c r="F23" s="25">
+        <f>M152</f>
+        <v/>
+      </c>
+      <c r="G23" s="26">
+        <f>F23-C23</f>
+        <v/>
+      </c>
+      <c r="H23" s="15">
+        <f>L152</f>
+        <v/>
+      </c>
+      <c r="I23" s="15">
+        <f>N152</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="15">
+        <f>M53</f>
+        <v/>
+      </c>
+      <c r="C24" s="15">
+        <f>M78</f>
+        <v/>
+      </c>
+      <c r="D24" s="15">
+        <f>M103</f>
+        <v/>
+      </c>
+      <c r="E24" s="15">
+        <f>M128</f>
+        <v/>
+      </c>
+      <c r="F24" s="25">
+        <f>M153</f>
+        <v/>
+      </c>
+      <c r="G24" s="26">
+        <f>F24-C24</f>
+        <v/>
+      </c>
+      <c r="H24" s="15">
+        <f>L153</f>
+        <v/>
+      </c>
+      <c r="I24" s="15">
+        <f>N153</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" s="15">
+        <f>M54</f>
+        <v/>
+      </c>
+      <c r="C25" s="15">
+        <f>M79</f>
+        <v/>
+      </c>
+      <c r="D25" s="15">
+        <f>M104</f>
+        <v/>
+      </c>
+      <c r="E25" s="15">
+        <f>M129</f>
+        <v/>
+      </c>
+      <c r="F25" s="25">
+        <f>M154</f>
+        <v/>
+      </c>
+      <c r="G25" s="26">
+        <f>F25-C25</f>
+        <v/>
+      </c>
+      <c r="H25" s="15">
+        <f>L154</f>
+        <v/>
+      </c>
+      <c r="I25" s="15">
+        <f>N154</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B26" s="15">
+        <f>M55</f>
+        <v/>
+      </c>
+      <c r="C26" s="15">
+        <f>M80</f>
+        <v/>
+      </c>
+      <c r="D26" s="15">
+        <f>M105</f>
+        <v/>
+      </c>
+      <c r="E26" s="15">
+        <f>M130</f>
+        <v/>
+      </c>
+      <c r="F26" s="25">
+        <f>M155</f>
+        <v/>
+      </c>
+      <c r="G26" s="26">
+        <f>F26-C26</f>
+        <v/>
+      </c>
+      <c r="H26" s="15">
+        <f>L155</f>
+        <v/>
+      </c>
+      <c r="I26" s="15">
+        <f>N155</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B27" s="15">
+        <f>M56</f>
+        <v/>
+      </c>
+      <c r="C27" s="15">
+        <f>M81</f>
+        <v/>
+      </c>
+      <c r="D27" s="15">
+        <f>M106</f>
+        <v/>
+      </c>
+      <c r="E27" s="15">
+        <f>M131</f>
+        <v/>
+      </c>
+      <c r="F27" s="25">
+        <f>M156</f>
+        <v/>
+      </c>
+      <c r="G27" s="26">
+        <f>F27-C27</f>
+        <v/>
+      </c>
+      <c r="H27" s="15">
+        <f>L156</f>
+        <v/>
+      </c>
+      <c r="I27" s="15">
+        <f>N156</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B28" s="15">
+        <f>M57</f>
+        <v/>
+      </c>
+      <c r="C28" s="15">
+        <f>M82</f>
+        <v/>
+      </c>
+      <c r="D28" s="15">
+        <f>M107</f>
+        <v/>
+      </c>
+      <c r="E28" s="15">
+        <f>M132</f>
+        <v/>
+      </c>
+      <c r="F28" s="25">
+        <f>M157</f>
+        <v/>
+      </c>
+      <c r="G28" s="26">
+        <f>F28-C28</f>
+        <v/>
+      </c>
+      <c r="H28" s="15">
+        <f>L157</f>
+        <v/>
+      </c>
+      <c r="I28" s="15">
+        <f>N157</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" s="15">
+        <f>M58</f>
+        <v/>
+      </c>
+      <c r="C29" s="15">
+        <f>M83</f>
+        <v/>
+      </c>
+      <c r="D29" s="15">
+        <f>M108</f>
+        <v/>
+      </c>
+      <c r="E29" s="15">
+        <f>M133</f>
+        <v/>
+      </c>
+      <c r="F29" s="25">
+        <f>M158</f>
+        <v/>
+      </c>
+      <c r="G29" s="26">
+        <f>F29-C29</f>
+        <v/>
+      </c>
+      <c r="H29" s="15">
+        <f>L158</f>
+        <v/>
+      </c>
+      <c r="I29" s="15">
+        <f>N158</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B30" s="15">
+        <f>M59</f>
+        <v/>
+      </c>
+      <c r="C30" s="15">
+        <f>M84</f>
+        <v/>
+      </c>
+      <c r="D30" s="15">
+        <f>M109</f>
+        <v/>
+      </c>
+      <c r="E30" s="15">
+        <f>M134</f>
+        <v/>
+      </c>
+      <c r="F30" s="25">
+        <f>M159</f>
+        <v/>
+      </c>
+      <c r="G30" s="26">
+        <f>F30-C30</f>
+        <v/>
+      </c>
+      <c r="H30" s="15">
+        <f>L159</f>
+        <v/>
+      </c>
+      <c r="I30" s="15">
+        <f>N159</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B31" s="15">
+        <f>M60</f>
+        <v/>
+      </c>
+      <c r="C31" s="15">
+        <f>M85</f>
+        <v/>
+      </c>
+      <c r="D31" s="15">
+        <f>M110</f>
+        <v/>
+      </c>
+      <c r="E31" s="15">
+        <f>M135</f>
+        <v/>
+      </c>
+      <c r="F31" s="25">
+        <f>M160</f>
+        <v/>
+      </c>
+      <c r="G31" s="26">
+        <f>F31-C31</f>
+        <v/>
+      </c>
+      <c r="H31" s="15">
+        <f>L160</f>
+        <v/>
+      </c>
+      <c r="I31" s="15">
+        <f>N160</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B32" s="15">
+        <f>M61</f>
+        <v/>
+      </c>
+      <c r="C32" s="15">
+        <f>M86</f>
+        <v/>
+      </c>
+      <c r="D32" s="15">
+        <f>M111</f>
+        <v/>
+      </c>
+      <c r="E32" s="15">
+        <f>M136</f>
+        <v/>
+      </c>
+      <c r="F32" s="25">
+        <f>M161</f>
+        <v/>
+      </c>
+      <c r="G32" s="26">
+        <f>F32-C32</f>
+        <v/>
+      </c>
+      <c r="H32" s="15">
+        <f>L161</f>
+        <v/>
+      </c>
+      <c r="I32" s="15">
+        <f>N161</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="B33" s="15">
+        <f>M62</f>
+        <v/>
+      </c>
+      <c r="C33" s="15">
+        <f>M87</f>
+        <v/>
+      </c>
+      <c r="D33" s="15">
+        <f>M112</f>
+        <v/>
+      </c>
+      <c r="E33" s="15">
+        <f>M137</f>
+        <v/>
+      </c>
+      <c r="F33" s="25">
+        <f>M162</f>
+        <v/>
+      </c>
+      <c r="G33" s="26">
+        <f>F33-C33</f>
+        <v/>
+      </c>
+      <c r="H33" s="15">
+        <f>L162</f>
+        <v/>
+      </c>
+      <c r="I33" s="15">
+        <f>N162</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="B34" s="15">
+        <f>M63</f>
+        <v/>
+      </c>
+      <c r="C34" s="15">
+        <f>M88</f>
+        <v/>
+      </c>
+      <c r="D34" s="15">
+        <f>M113</f>
+        <v/>
+      </c>
+      <c r="E34" s="15">
+        <f>M138</f>
+        <v/>
+      </c>
+      <c r="F34" s="25">
+        <f>M163</f>
+        <v/>
+      </c>
+      <c r="G34" s="26">
+        <f>F34-C34</f>
+        <v/>
+      </c>
+      <c r="H34" s="15">
+        <f>L163</f>
+        <v/>
+      </c>
+      <c r="I34" s="15">
+        <f>N163</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="B35" s="15">
+        <f>M64</f>
+        <v/>
+      </c>
+      <c r="C35" s="15">
+        <f>M89</f>
+        <v/>
+      </c>
+      <c r="D35" s="15">
+        <f>M114</f>
+        <v/>
+      </c>
+      <c r="E35" s="15">
+        <f>M139</f>
+        <v/>
+      </c>
+      <c r="F35" s="25">
+        <f>M164</f>
+        <v/>
+      </c>
+      <c r="G35" s="26">
+        <f>F35-C35</f>
+        <v/>
+      </c>
+      <c r="H35" s="15">
+        <f>L164</f>
+        <v/>
+      </c>
+      <c r="I35" s="15">
+        <f>N164</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="B36" s="15">
+        <f>M65</f>
+        <v/>
+      </c>
+      <c r="C36" s="15">
+        <f>M90</f>
+        <v/>
+      </c>
+      <c r="D36" s="15">
+        <f>M115</f>
+        <v/>
+      </c>
+      <c r="E36" s="15">
+        <f>M140</f>
+        <v/>
+      </c>
+      <c r="F36" s="25">
+        <f>M165</f>
+        <v/>
+      </c>
+      <c r="G36" s="26">
+        <f>F36-C36</f>
+        <v/>
+      </c>
+      <c r="H36" s="15">
+        <f>L165</f>
+        <v/>
+      </c>
+      <c r="I36" s="15">
+        <f>N165</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="B37" s="15">
+        <f>M66</f>
+        <v/>
+      </c>
+      <c r="C37" s="15">
+        <f>M91</f>
+        <v/>
+      </c>
+      <c r="D37" s="15">
+        <f>M116</f>
+        <v/>
+      </c>
+      <c r="E37" s="15">
+        <f>M141</f>
+        <v/>
+      </c>
+      <c r="F37" s="25">
+        <f>M166</f>
+        <v/>
+      </c>
+      <c r="G37" s="26">
+        <f>F37-C37</f>
+        <v/>
+      </c>
+      <c r="H37" s="15">
+        <f>L166</f>
+        <v/>
+      </c>
+      <c r="I37" s="15">
+        <f>N166</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>PERSONAL TRADING ROUTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>Deployed</t>
+        </is>
+      </c>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>Idle</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>Profit</t>
+        </is>
+      </c>
+      <c r="F45" s="19" t="inlineStr">
+        <is>
+          <t>Overhead</t>
+        </is>
+      </c>
+      <c r="G45" s="19" t="inlineStr">
+        <is>
+          <t>Salary Paid</t>
+        </is>
+      </c>
+      <c r="H45" s="19" t="inlineStr">
+        <is>
+          <t>Taxable Profit</t>
+        </is>
+      </c>
+      <c r="I45" s="19" t="inlineStr">
+        <is>
+          <t>Income Tax</t>
+        </is>
+      </c>
+      <c r="J45" s="19" t="inlineStr">
+        <is>
+          <t>Not Lent Back</t>
+        </is>
+      </c>
+      <c r="K45" s="19" t="inlineStr">
+        <is>
+          <t>New Loan</t>
+        </is>
+      </c>
+      <c r="L45" s="19" t="inlineStr">
+        <is>
+          <t>Loans Outstanding</t>
+        </is>
+      </c>
+      <c r="M45" s="19" t="inlineStr">
+        <is>
+          <t>Closing Capital</t>
+        </is>
+      </c>
+      <c r="N45" s="19" t="inlineStr">
+        <is>
+          <t>Net Equity (Closing - Loans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="B46" s="15">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="C46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="15">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="N46" s="15">
+        <f>$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" s="15">
+        <f>M46</f>
+        <v/>
+      </c>
+      <c r="C47" s="15">
+        <f>MIN(B47, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D47" s="15">
+        <f>MAX(B47-C47, 0)</f>
+        <v/>
+      </c>
+      <c r="E47" s="15">
+        <f>C47*$B$6 + D47*$B$14</f>
+        <v/>
+      </c>
+      <c r="F47" s="15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G47" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="15">
+        <f>MAX(E47-F47, 0)</f>
+        <v/>
+      </c>
+      <c r="I47" s="15">
+        <f>IF(H47&lt;=0.12, 0, IF(H47&lt;=0.5, MIN((MAX(H47-0.04,0)*0.05+MAX(H47-0.08,0)*0.05+MAX(H47-0.12,0)*0.05+MAX(H47-0.16,0)*0.05+MAX(H47-0.2,0)*0.05+MAX(H47-0.24,0)*0.05), H47-0.12), MIN((MAX(H47-0.04,0)*0.05+MAX(H47-0.08,0)*0.05+MAX(H47-0.12,0)*0.05+MAX(H47-0.16,0)*0.05+MAX(H47-0.2,0)*0.05+MAX(H47-0.24,0)*0.05)*(1+IF(H47&lt;=1,0.1,IF(H47&lt;=2,0.15,0.25))), (MAX(IF(H47&lt;=1,0.5,IF(H47&lt;=2,1,2))-0.04,0)*0.05+MAX(IF(H47&lt;=1,0.5,IF(H47&lt;=2,1,2))-0.08,0)*0.05+MAX(IF(H47&lt;=1,0.5,IF(H47&lt;=2,1,2))-0.12,0)*0.05+MAX(IF(H47&lt;=1,0.5,IF(H47&lt;=2,1,2))-0.16,0)*0.05+MAX(IF(H47&lt;=1,0.5,IF(H47&lt;=2,1,2))-0.2,0)*0.05+MAX(IF(H47&lt;=1,0.5,IF(H47&lt;=2,1,2))-0.24,0)*0.05)*(1+IF(H47&lt;=1,0,IF(H47&lt;=2,0.1,0.15)))+H47-IF(H47&lt;=1,0.5,IF(H47&lt;=2,1,2))))*1.04)</f>
+        <v/>
+      </c>
+      <c r="J47" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="15">
+        <f>B47+E47-F47-I47</f>
+        <v/>
+      </c>
+      <c r="N47" s="15">
+        <f>M47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B48" s="15">
+        <f>M47</f>
+        <v/>
+      </c>
+      <c r="C48" s="15">
+        <f>MIN(B48, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D48" s="15">
+        <f>MAX(B48-C48, 0)</f>
+        <v/>
+      </c>
+      <c r="E48" s="15">
+        <f>C48*$B$6 + D48*$B$14</f>
+        <v/>
+      </c>
+      <c r="F48" s="15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G48" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="15">
+        <f>MAX(E48-F48, 0)</f>
+        <v/>
+      </c>
+      <c r="I48" s="15">
+        <f>IF(H48&lt;=0.12, 0, IF(H48&lt;=0.5, MIN((MAX(H48-0.04,0)*0.05+MAX(H48-0.08,0)*0.05+MAX(H48-0.12,0)*0.05+MAX(H48-0.16,0)*0.05+MAX(H48-0.2,0)*0.05+MAX(H48-0.24,0)*0.05), H48-0.12), MIN((MAX(H48-0.04,0)*0.05+MAX(H48-0.08,0)*0.05+MAX(H48-0.12,0)*0.05+MAX(H48-0.16,0)*0.05+MAX(H48-0.2,0)*0.05+MAX(H48-0.24,0)*0.05)*(1+IF(H48&lt;=1,0.1,IF(H48&lt;=2,0.15,0.25))), (MAX(IF(H48&lt;=1,0.5,IF(H48&lt;=2,1,2))-0.04,0)*0.05+MAX(IF(H48&lt;=1,0.5,IF(H48&lt;=2,1,2))-0.08,0)*0.05+MAX(IF(H48&lt;=1,0.5,IF(H48&lt;=2,1,2))-0.12,0)*0.05+MAX(IF(H48&lt;=1,0.5,IF(H48&lt;=2,1,2))-0.16,0)*0.05+MAX(IF(H48&lt;=1,0.5,IF(H48&lt;=2,1,2))-0.2,0)*0.05+MAX(IF(H48&lt;=1,0.5,IF(H48&lt;=2,1,2))-0.24,0)*0.05)*(1+IF(H48&lt;=1,0,IF(H48&lt;=2,0.1,0.15)))+H48-IF(H48&lt;=1,0.5,IF(H48&lt;=2,1,2))))*1.04)</f>
+        <v/>
+      </c>
+      <c r="J48" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="15">
+        <f>B48+E48-F48-I48</f>
+        <v/>
+      </c>
+      <c r="N48" s="15">
+        <f>M48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B49" s="15">
+        <f>M48</f>
+        <v/>
+      </c>
+      <c r="C49" s="15">
+        <f>MIN(B49, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D49" s="15">
+        <f>MAX(B49-C49, 0)</f>
+        <v/>
+      </c>
+      <c r="E49" s="15">
+        <f>C49*$B$6 + D49*$B$14</f>
+        <v/>
+      </c>
+      <c r="F49" s="15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G49" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="15">
+        <f>MAX(E49-F49, 0)</f>
+        <v/>
+      </c>
+      <c r="I49" s="15">
+        <f>IF(H49&lt;=0.12, 0, IF(H49&lt;=0.5, MIN((MAX(H49-0.04,0)*0.05+MAX(H49-0.08,0)*0.05+MAX(H49-0.12,0)*0.05+MAX(H49-0.16,0)*0.05+MAX(H49-0.2,0)*0.05+MAX(H49-0.24,0)*0.05), H49-0.12), MIN((MAX(H49-0.04,0)*0.05+MAX(H49-0.08,0)*0.05+MAX(H49-0.12,0)*0.05+MAX(H49-0.16,0)*0.05+MAX(H49-0.2,0)*0.05+MAX(H49-0.24,0)*0.05)*(1+IF(H49&lt;=1,0.1,IF(H49&lt;=2,0.15,0.25))), (MAX(IF(H49&lt;=1,0.5,IF(H49&lt;=2,1,2))-0.04,0)*0.05+MAX(IF(H49&lt;=1,0.5,IF(H49&lt;=2,1,2))-0.08,0)*0.05+MAX(IF(H49&lt;=1,0.5,IF(H49&lt;=2,1,2))-0.12,0)*0.05+MAX(IF(H49&lt;=1,0.5,IF(H49&lt;=2,1,2))-0.16,0)*0.05+MAX(IF(H49&lt;=1,0.5,IF(H49&lt;=2,1,2))-0.2,0)*0.05+MAX(IF(H49&lt;=1,0.5,IF(H49&lt;=2,1,2))-0.24,0)*0.05)*(1+IF(H49&lt;=1,0,IF(H49&lt;=2,0.1,0.15)))+H49-IF(H49&lt;=1,0.5,IF(H49&lt;=2,1,2))))*1.04)</f>
+        <v/>
+      </c>
+      <c r="J49" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="15">
+        <f>B49+E49-F49-I49</f>
+        <v/>
+      </c>
+      <c r="N49" s="15">
+        <f>M49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B50" s="15">
+        <f>M49</f>
+        <v/>
+      </c>
+      <c r="C50" s="15">
+        <f>MIN(B50, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D50" s="15">
+        <f>MAX(B50-C50, 0)</f>
+        <v/>
+      </c>
+      <c r="E50" s="15">
+        <f>C50*$B$6 + D50*$B$14</f>
+        <v/>
+      </c>
+      <c r="F50" s="15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="15">
+        <f>MAX(E50-F50, 0)</f>
+        <v/>
+      </c>
+      <c r="I50" s="15">
+        <f>IF(H50&lt;=0.12, 0, IF(H50&lt;=0.5, MIN((MAX(H50-0.04,0)*0.05+MAX(H50-0.08,0)*0.05+MAX(H50-0.12,0)*0.05+MAX(H50-0.16,0)*0.05+MAX(H50-0.2,0)*0.05+MAX(H50-0.24,0)*0.05), H50-0.12), MIN((MAX(H50-0.04,0)*0.05+MAX(H50-0.08,0)*0.05+MAX(H50-0.12,0)*0.05+MAX(H50-0.16,0)*0.05+MAX(H50-0.2,0)*0.05+MAX(H50-0.24,0)*0.05)*(1+IF(H50&lt;=1,0.1,IF(H50&lt;=2,0.15,0.25))), (MAX(IF(H50&lt;=1,0.5,IF(H50&lt;=2,1,2))-0.04,0)*0.05+MAX(IF(H50&lt;=1,0.5,IF(H50&lt;=2,1,2))-0.08,0)*0.05+MAX(IF(H50&lt;=1,0.5,IF(H50&lt;=2,1,2))-0.12,0)*0.05+MAX(IF(H50&lt;=1,0.5,IF(H50&lt;=2,1,2))-0.16,0)*0.05+MAX(IF(H50&lt;=1,0.5,IF(H50&lt;=2,1,2))-0.2,0)*0.05+MAX(IF(H50&lt;=1,0.5,IF(H50&lt;=2,1,2))-0.24,0)*0.05)*(1+IF(H50&lt;=1,0,IF(H50&lt;=2,0.1,0.15)))+H50-IF(H50&lt;=1,0.5,IF(H50&lt;=2,1,2))))*1.04)</f>
+        <v/>
+      </c>
+      <c r="J50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="15">
+        <f>B50+E50-F50-I50</f>
+        <v/>
+      </c>
+      <c r="N50" s="15">
+        <f>M50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B51" s="15">
+        <f>M50</f>
+        <v/>
+      </c>
+      <c r="C51" s="15">
+        <f>MIN(B51, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D51" s="15">
+        <f>MAX(B51-C51, 0)</f>
+        <v/>
+      </c>
+      <c r="E51" s="15">
+        <f>C51*$B$6 + D51*$B$14</f>
+        <v/>
+      </c>
+      <c r="F51" s="15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G51" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="15">
+        <f>MAX(E51-F51, 0)</f>
+        <v/>
+      </c>
+      <c r="I51" s="15">
+        <f>IF(H51&lt;=0.12, 0, IF(H51&lt;=0.5, MIN((MAX(H51-0.04,0)*0.05+MAX(H51-0.08,0)*0.05+MAX(H51-0.12,0)*0.05+MAX(H51-0.16,0)*0.05+MAX(H51-0.2,0)*0.05+MAX(H51-0.24,0)*0.05), H51-0.12), MIN((MAX(H51-0.04,0)*0.05+MAX(H51-0.08,0)*0.05+MAX(H51-0.12,0)*0.05+MAX(H51-0.16,0)*0.05+MAX(H51-0.2,0)*0.05+MAX(H51-0.24,0)*0.05)*(1+IF(H51&lt;=1,0.1,IF(H51&lt;=2,0.15,0.25))), (MAX(IF(H51&lt;=1,0.5,IF(H51&lt;=2,1,2))-0.04,0)*0.05+MAX(IF(H51&lt;=1,0.5,IF(H51&lt;=2,1,2))-0.08,0)*0.05+MAX(IF(H51&lt;=1,0.5,IF(H51&lt;=2,1,2))-0.12,0)*0.05+MAX(IF(H51&lt;=1,0.5,IF(H51&lt;=2,1,2))-0.16,0)*0.05+MAX(IF(H51&lt;=1,0.5,IF(H51&lt;=2,1,2))-0.2,0)*0.05+MAX(IF(H51&lt;=1,0.5,IF(H51&lt;=2,1,2))-0.24,0)*0.05)*(1+IF(H51&lt;=1,0,IF(H51&lt;=2,0.1,0.15)))+H51-IF(H51&lt;=1,0.5,IF(H51&lt;=2,1,2))))*1.04)</f>
+        <v/>
+      </c>
+      <c r="J51" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="15">
+        <f>B51+E51-F51-I51</f>
+        <v/>
+      </c>
+      <c r="N51" s="15">
+        <f>M51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B52" s="15">
+        <f>M51</f>
+        <v/>
+      </c>
+      <c r="C52" s="15">
+        <f>MIN(B52, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D52" s="15">
+        <f>MAX(B52-C52, 0)</f>
+        <v/>
+      </c>
+      <c r="E52" s="15">
+        <f>C52*$B$6 + D52*$B$14</f>
+        <v/>
+      </c>
+      <c r="F52" s="15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G52" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="15">
+        <f>MAX(E52-F52, 0)</f>
+        <v/>
+      </c>
+      <c r="I52" s="15">
+        <f>IF(H52&lt;=0.12, 0, IF(H52&lt;=0.5, MIN((MAX(H52-0.04,0)*0.05+MAX(H52-0.08,0)*0.05+MAX(H52-0.12,0)*0.05+MAX(H52-0.16,0)*0.05+MAX(H52-0.2,0)*0.05+MAX(H52-0.24,0)*0.05), H52-0.12), MIN((MAX(H52-0.04,0)*0.05+MAX(H52-0.08,0)*0.05+MAX(H52-0.12,0)*0.05+MAX(H52-0.16,0)*0.05+MAX(H52-0.2,0)*0.05+MAX(H52-0.24,0)*0.05)*(1+IF(H52&lt;=1,0.1,IF(H52&lt;=2,0.15,0.25))), (MAX(IF(H52&lt;=1,0.5,IF(H52&lt;=2,1,2))-0.04,0)*0.05+MAX(IF(H52&lt;=1,0.5,IF(H52&lt;=2,1,2))-0.08,0)*0.05+MAX(IF(H52&lt;=1,0.5,IF(H52&lt;=2,1,2))-0.12,0)*0.05+MAX(IF(H52&lt;=1,0.5,IF(H52&lt;=2,1,2))-0.16,0)*0.05+MAX(IF(H52&lt;=1,0.5,IF(H52&lt;=2,1,2))-0.2,0)*0.05+MAX(IF(H52&lt;=1,0.5,IF(H52&lt;=2,1,2))-0.24,0)*0.05)*(1+IF(H52&lt;=1,0,IF(H52&lt;=2,0.1,0.15)))+H52-IF(H52&lt;=1,0.5,IF(H52&lt;=2,1,2))))*1.04)</f>
+        <v/>
+      </c>
+      <c r="J52" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="15">
+        <f>B52+E52-F52-I52</f>
+        <v/>
+      </c>
+      <c r="N52" s="15">
+        <f>M52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B53" s="15">
+        <f>M52</f>
+        <v/>
+      </c>
+      <c r="C53" s="15">
+        <f>MIN(B53, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D53" s="15">
+        <f>MAX(B53-C53, 0)</f>
+        <v/>
+      </c>
+      <c r="E53" s="15">
+        <f>C53*$B$6 + D53*$B$14</f>
+        <v/>
+      </c>
+      <c r="F53" s="15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="15">
+        <f>MAX(E53-F53, 0)</f>
+        <v/>
+      </c>
+      <c r="I53" s="15">
+        <f>IF(H53&lt;=0.12, 0, IF(H53&lt;=0.5, MIN((MAX(H53-0.04,0)*0.05+MAX(H53-0.08,0)*0.05+MAX(H53-0.12,0)*0.05+MAX(H53-0.16,0)*0.05+MAX(H53-0.2,0)*0.05+MAX(H53-0.24,0)*0.05), H53-0.12), MIN((MAX(H53-0.04,0)*0.05+MAX(H53-0.08,0)*0.05+MAX(H53-0.12,0)*0.05+MAX(H53-0.16,0)*0.05+MAX(H53-0.2,0)*0.05+MAX(H53-0.24,0)*0.05)*(1+IF(H53&lt;=1,0.1,IF(H53&lt;=2,0.15,0.25))), (MAX(IF(H53&lt;=1,0.5,IF(H53&lt;=2,1,2))-0.04,0)*0.05+MAX(IF(H53&lt;=1,0.5,IF(H53&lt;=2,1,2))-0.08,0)*0.05+MAX(IF(H53&lt;=1,0.5,IF(H53&lt;=2,1,2))-0.12,0)*0.05+MAX(IF(H53&lt;=1,0.5,IF(H53&lt;=2,1,2))-0.16,0)*0.05+MAX(IF(H53&lt;=1,0.5,IF(H53&lt;=2,1,2))-0.2,0)*0.05+MAX(IF(H53&lt;=1,0.5,IF(H53&lt;=2,1,2))-0.24,0)*0.05)*(1+IF(H53&lt;=1,0,IF(H53&lt;=2,0.1,0.15)))+H53-IF(H53&lt;=1,0.5,IF(H53&lt;=2,1,2))))*1.04)</f>
+        <v/>
+      </c>
+      <c r="J53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="15">
+        <f>B53+E53-F53-I53</f>
+        <v/>
+      </c>
+      <c r="N53" s="15">
+        <f>M53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B54" s="15">
+        <f>M53</f>
+        <v/>
+      </c>
+      <c r="C54" s="15">
+        <f>MIN(B54, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D54" s="15">
+        <f>MAX(B54-C54, 0)</f>
+        <v/>
+      </c>
+      <c r="E54" s="15">
+        <f>C54*$B$6 + D54*$B$14</f>
+        <v/>
+      </c>
+      <c r="F54" s="15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G54" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="15">
+        <f>MAX(E54-F54, 0)</f>
+        <v/>
+      </c>
+      <c r="I54" s="15">
+        <f>IF(H54&lt;=0.12, 0, IF(H54&lt;=0.5, MIN((MAX(H54-0.04,0)*0.05+MAX(H54-0.08,0)*0.05+MAX(H54-0.12,0)*0.05+MAX(H54-0.16,0)*0.05+MAX(H54-0.2,0)*0.05+MAX(H54-0.24,0)*0.05), H54-0.12), MIN((MAX(H54-0.04,0)*0.05+MAX(H54-0.08,0)*0.05+MAX(H54-0.12,0)*0.05+MAX(H54-0.16,0)*0.05+MAX(H54-0.2,0)*0.05+MAX(H54-0.24,0)*0.05)*(1+IF(H54&lt;=1,0.1,IF(H54&lt;=2,0.15,0.25))), (MAX(IF(H54&lt;=1,0.5,IF(H54&lt;=2,1,2))-0.04,0)*0.05+MAX(IF(H54&lt;=1,0.5,IF(H54&lt;=2,1,2))-0.08,0)*0.05+MAX(IF(H54&lt;=1,0.5,IF(H54&lt;=2,1,2))-0.12,0)*0.05+MAX(IF(H54&lt;=1,0.5,IF(H54&lt;=2,1,2))-0.16,0)*0.05+MAX(IF(H54&lt;=1,0.5,IF(H54&lt;=2,1,2))-0.2,0)*0.05+MAX(IF(H54&lt;=1,0.5,IF(H54&lt;=2,1,2))-0.24,0)*0.05)*(1+IF(H54&lt;=1,0,IF(H54&lt;=2,0.1,0.15)))+H54-IF(H54&lt;=1,0.5,IF(H54&lt;=2,1,2))))*1.04)</f>
+        <v/>
+      </c>
+      <c r="J54" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="15">
+        <f>B54+E54-F54-I54</f>
+        <v/>
+      </c>
+      <c r="N54" s="15">
+        <f>M54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="B55" s="15">
+        <f>M54</f>
+        <v/>
+      </c>
+      <c r="C55" s="15">
+        <f>MIN(B55, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D55" s="15">
+        <f>MAX(B55-C55, 0)</f>
+        <v/>
+      </c>
+      <c r="E55" s="15">
+        <f>C55*$B$6 + D55*$B$14</f>
+        <v/>
+      </c>
+      <c r="F55" s="15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G55" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="15">
+        <f>MAX(E55-F55, 0)</f>
+        <v/>
+      </c>
+      <c r="I55" s="15">
+        <f>IF(H55&lt;=0.12, 0, IF(H55&lt;=0.5, MIN((MAX(H55-0.04,0)*0.05+MAX(H55-0.08,0)*0.05+MAX(H55-0.12,0)*0.05+MAX(H55-0.16,0)*0.05+MAX(H55-0.2,0)*0.05+MAX(H55-0.24,0)*0.05), H55-0.12), MIN((MAX(H55-0.04,0)*0.05+MAX(H55-0.08,0)*0.05+MAX(H55-0.12,0)*0.05+MAX(H55-0.16,0)*0.05+MAX(H55-0.2,0)*0.05+MAX(H55-0.24,0)*0.05)*(1+IF(H55&lt;=1,0.1,IF(H55&lt;=2,0.15,0.25))), (MAX(IF(H55&lt;=1,0.5,IF(H55&lt;=2,1,2))-0.04,0)*0.05+MAX(IF(H55&lt;=1,0.5,IF(H55&lt;=2,1,2))-0.08,0)*0.05+MAX(IF(H55&lt;=1,0.5,IF(H55&lt;=2,1,2))-0.12,0)*0.05+MAX(IF(H55&lt;=1,0.5,IF(H55&lt;=2,1,2))-0.16,0)*0.05+MAX(IF(H55&lt;=1,0.5,IF(H55&lt;=2,1,2))-0.2,0)*0.05+MAX(IF(H55&lt;=1,0.5,IF(H55&lt;=2,1,2))-0.24,0)*0.05)*(1+IF(H55&lt;=1,0,IF(H55&lt;=2,0.1,0.15)))+H55-IF(H55&lt;=1,0.5,IF(H55&lt;=2,1,2))))*1.04)</f>
+        <v/>
+      </c>
+      <c r="J55" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="15">
+        <f>B55+E55-F55-I55</f>
+        <v/>
+      </c>
+      <c r="N55" s="15">
+        <f>M55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B56" s="15">
+        <f>M55</f>
+        <v/>
+      </c>
+      <c r="C56" s="15">
+        <f>MIN(B56, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D56" s="15">
+        <f>MAX(B56-C56, 0)</f>
+        <v/>
+      </c>
+      <c r="E56" s="15">
+        <f>C56*$B$6 + D56*$B$14</f>
+        <v/>
+      </c>
+      <c r="F56" s="15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G56" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="15">
+        <f>MAX(E56-F56, 0)</f>
+        <v/>
+      </c>
+      <c r="I56" s="15">
+        <f>IF(H56&lt;=0.12, 0, IF(H56&lt;=0.5, MIN((MAX(H56-0.04,0)*0.05+MAX(H56-0.08,0)*0.05+MAX(H56-0.12,0)*0.05+MAX(H56-0.16,0)*0.05+MAX(H56-0.2,0)*0.05+MAX(H56-0.24,0)*0.05), H56-0.12), MIN((MAX(H56-0.04,0)*0.05+MAX(H56-0.08,0)*0.05+MAX(H56-0.12,0)*0.05+MAX(H56-0.16,0)*0.05+MAX(H56-0.2,0)*0.05+MAX(H56-0.24,0)*0.05)*(1+IF(H56&lt;=1,0.1,IF(H56&lt;=2,0.15,0.25))), (MAX(IF(H56&lt;=1,0.5,IF(H56&lt;=2,1,2))-0.04,0)*0.05+MAX(IF(H56&lt;=1,0.5,IF(H56&lt;=2,1,2))-0.08,0)*0.05+MAX(IF(H56&lt;=1,0.5,IF(H56&lt;=2,1,2))-0.12,0)*0.05+MAX(IF(H56&lt;=1,0.5,IF(H56&lt;=2,1,2))-0.16,0)*0.05+MAX(IF(H56&lt;=1,0.5,IF(H56&lt;=2,1,2))-0.2,0)*0.05+MAX(IF(H56&lt;=1,0.5,IF(H56&lt;=2,1,2))-0.24,0)*0.05)*(1+IF(H56&lt;=1,0,IF(H56&lt;=2,0.1,0.15)))+H56-IF(H56&lt;=1,0.5,IF(H56&lt;=2,1,2))))*1.04)</f>
+        <v/>
+      </c>
+      <c r="J56" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="15">
+        <f>B56+E56-F56-I56</f>
+        <v/>
+      </c>
+      <c r="N56" s="15">
+        <f>M56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="B57" s="15">
+        <f>M56</f>
+        <v/>
+      </c>
+      <c r="C57" s="15">
+        <f>MIN(B57, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D57" s="15">
+        <f>MAX(B57-C57, 0)</f>
+        <v/>
+      </c>
+      <c r="E57" s="15">
+        <f>C57*$B$6 + D57*$B$14</f>
+        <v/>
+      </c>
+      <c r="F57" s="15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G57" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="15">
+        <f>MAX(E57-F57, 0)</f>
+        <v/>
+      </c>
+      <c r="I57" s="15">
+        <f>IF(H57&lt;=0.12, 0, IF(H57&lt;=0.5, MIN((MAX(H57-0.04,0)*0.05+MAX(H57-0.08,0)*0.05+MAX(H57-0.12,0)*0.05+MAX(H57-0.16,0)*0.05+MAX(H57-0.2,0)*0.05+MAX(H57-0.24,0)*0.05), H57-0.12), MIN((MAX(H57-0.04,0)*0.05+MAX(H57-0.08,0)*0.05+MAX(H57-0.12,0)*0.05+MAX(H57-0.16,0)*0.05+MAX(H57-0.2,0)*0.05+MAX(H57-0.24,0)*0.05)*(1+IF(H57&lt;=1,0.1,IF(H57&lt;=2,0.15,0.25))), (MAX(IF(H57&lt;=1,0.5,IF(H57&lt;=2,1,2))-0.04,0)*0.05+MAX(IF(H57&lt;=1,0.5,IF(H57&lt;=2,1,2))-0.08,0)*0.05+MAX(IF(H57&lt;=1,0.5,IF(H57&lt;=2,1,2))-0.12,0)*0.05+MAX(IF(H57&lt;=1,0.5,IF(H57&lt;=2,1,2))-0.16,0)*0.05+MAX(IF(H57&lt;=1,0.5,IF(H57&lt;=2,1,2))-0.2,0)*0.05+MAX(IF(H57&lt;=1,0.5,IF(H57&lt;=2,1,2))-0.24,0)*0.05)*(1+IF(H57&lt;=1,0,IF(H57&lt;=2,0.1,0.15)))+H57-IF(H57&lt;=1,0.5,IF(H57&lt;=2,1,2))))*1.04)</f>
+        <v/>
+      </c>
+      <c r="J57" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="15">
+        <f>B57+E57-F57-I57</f>
+        <v/>
+      </c>
+      <c r="N57" s="15">
+        <f>M57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="B58" s="15">
+        <f>M57</f>
+        <v/>
+      </c>
+      <c r="C58" s="15">
+        <f>MIN(B58, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D58" s="15">
+        <f>MAX(B58-C58, 0)</f>
+        <v/>
+      </c>
+      <c r="E58" s="15">
+        <f>C58*$B$6 + D58*$B$14</f>
+        <v/>
+      </c>
+      <c r="F58" s="15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G58" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="15">
+        <f>MAX(E58-F58, 0)</f>
+        <v/>
+      </c>
+      <c r="I58" s="15">
+        <f>IF(H58&lt;=0.12, 0, IF(H58&lt;=0.5, MIN((MAX(H58-0.04,0)*0.05+MAX(H58-0.08,0)*0.05+MAX(H58-0.12,0)*0.05+MAX(H58-0.16,0)*0.05+MAX(H58-0.2,0)*0.05+MAX(H58-0.24,0)*0.05), H58-0.12), MIN((MAX(H58-0.04,0)*0.05+MAX(H58-0.08,0)*0.05+MAX(H58-0.12,0)*0.05+MAX(H58-0.16,0)*0.05+MAX(H58-0.2,0)*0.05+MAX(H58-0.24,0)*0.05)*(1+IF(H58&lt;=1,0.1,IF(H58&lt;=2,0.15,0.25))), (MAX(IF(H58&lt;=1,0.5,IF(H58&lt;=2,1,2))-0.04,0)*0.05+MAX(IF(H58&lt;=1,0.5,IF(H58&lt;=2,1,2))-0.08,0)*0.05+MAX(IF(H58&lt;=1,0.5,IF(H58&lt;=2,1,2))-0.12,0)*0.05+MAX(IF(H58&lt;=1,0.5,IF(H58&lt;=2,1,2))-0.16,0)*0.05+MAX(IF(H58&lt;=1,0.5,IF(H58&lt;=2,1,2))-0.2,0)*0.05+MAX(IF(H58&lt;=1,0.5,IF(H58&lt;=2,1,2))-0.24,0)*0.05)*(1+IF(H58&lt;=1,0,IF(H58&lt;=2,0.1,0.15)))+H58-IF(H58&lt;=1,0.5,IF(H58&lt;=2,1,2))))*1.04)</f>
+        <v/>
+      </c>
+      <c r="J58" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="15">
+        <f>B58+E58-F58-I58</f>
+        <v/>
+      </c>
+      <c r="N58" s="15">
+        <f>M58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="B59" s="15">
+        <f>M58</f>
+        <v/>
+      </c>
+      <c r="C59" s="15">
+        <f>MIN(B59, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D59" s="15">
+        <f>MAX(B59-C59, 0)</f>
+        <v/>
+      </c>
+      <c r="E59" s="15">
+        <f>C59*$B$6 + D59*$B$14</f>
+        <v/>
+      </c>
+      <c r="F59" s="15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G59" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="15">
+        <f>MAX(E59-F59, 0)</f>
+        <v/>
+      </c>
+      <c r="I59" s="15">
+        <f>IF(H59&lt;=0.12, 0, IF(H59&lt;=0.5, MIN((MAX(H59-0.04,0)*0.05+MAX(H59-0.08,0)*0.05+MAX(H59-0.12,0)*0.05+MAX(H59-0.16,0)*0.05+MAX(H59-0.2,0)*0.05+MAX(H59-0.24,0)*0.05), H59-0.12), MIN((MAX(H59-0.04,0)*0.05+MAX(H59-0.08,0)*0.05+MAX(H59-0.12,0)*0.05+MAX(H59-0.16,0)*0.05+MAX(H59-0.2,0)*0.05+MAX(H59-0.24,0)*0.05)*(1+IF(H59&lt;=1,0.1,IF(H59&lt;=2,0.15,0.25))), (MAX(IF(H59&lt;=1,0.5,IF(H59&lt;=2,1,2))-0.04,0)*0.05+MAX(IF(H59&lt;=1,0.5,IF(H59&lt;=2,1,2))-0.08,0)*0.05+MAX(IF(H59&lt;=1,0.5,IF(H59&lt;=2,1,2))-0.12,0)*0.05+MAX(IF(H59&lt;=1,0.5,IF(H59&lt;=2,1,2))-0.16,0)*0.05+MAX(IF(H59&lt;=1,0.5,IF(H59&lt;=2,1,2))-0.2,0)*0.05+MAX(IF(H59&lt;=1,0.5,IF(H59&lt;=2,1,2))-0.24,0)*0.05)*(1+IF(H59&lt;=1,0,IF(H59&lt;=2,0.1,0.15)))+H59-IF(H59&lt;=1,0.5,IF(H59&lt;=2,1,2))))*1.04)</f>
+        <v/>
+      </c>
+      <c r="J59" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="15">
+        <f>B59+E59-F59-I59</f>
+        <v/>
+      </c>
+      <c r="N59" s="15">
+        <f>M59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="B60" s="15">
+        <f>M59</f>
+        <v/>
+      </c>
+      <c r="C60" s="15">
+        <f>MIN(B60, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D60" s="15">
+        <f>MAX(B60-C60, 0)</f>
+        <v/>
+      </c>
+      <c r="E60" s="15">
+        <f>C60*$B$6 + D60*$B$14</f>
+        <v/>
+      </c>
+      <c r="F60" s="15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G60" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="15">
+        <f>MAX(E60-F60, 0)</f>
+        <v/>
+      </c>
+      <c r="I60" s="15">
+        <f>IF(H60&lt;=0.12, 0, IF(H60&lt;=0.5, MIN((MAX(H60-0.04,0)*0.05+MAX(H60-0.08,0)*0.05+MAX(H60-0.12,0)*0.05+MAX(H60-0.16,0)*0.05+MAX(H60-0.2,0)*0.05+MAX(H60-0.24,0)*0.05), H60-0.12), MIN((MAX(H60-0.04,0)*0.05+MAX(H60-0.08,0)*0.05+MAX(H60-0.12,0)*0.05+MAX(H60-0.16,0)*0.05+MAX(H60-0.2,0)*0.05+MAX(H60-0.24,0)*0.05)*(1+IF(H60&lt;=1,0.1,IF(H60&lt;=2,0.15,0.25))), (MAX(IF(H60&lt;=1,0.5,IF(H60&lt;=2,1,2))-0.04,0)*0.05+MAX(IF(H60&lt;=1,0.5,IF(H60&lt;=2,1,2))-0.08,0)*0.05+MAX(IF(H60&lt;=1,0.5,IF(H60&lt;=2,1,2))-0.12,0)*0.05+MAX(IF(H60&lt;=1,0.5,IF(H60&lt;=2,1,2))-0.16,0)*0.05+MAX(IF(H60&lt;=1,0.5,IF(H60&lt;=2,1,2))-0.2,0)*0.05+MAX(IF(H60&lt;=1,0.5,IF(H60&lt;=2,1,2))-0.24,0)*0.05)*(1+IF(H60&lt;=1,0,IF(H60&lt;=2,0.1,0.15)))+H60-IF(H60&lt;=1,0.5,IF(H60&lt;=2,1,2))))*1.04)</f>
+        <v/>
+      </c>
+      <c r="J60" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="15">
+        <f>B60+E60-F60-I60</f>
+        <v/>
+      </c>
+      <c r="N60" s="15">
+        <f>M60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B61" s="15">
+        <f>M60</f>
+        <v/>
+      </c>
+      <c r="C61" s="15">
+        <f>MIN(B61, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D61" s="15">
+        <f>MAX(B61-C61, 0)</f>
+        <v/>
+      </c>
+      <c r="E61" s="15">
+        <f>C61*$B$6 + D61*$B$14</f>
+        <v/>
+      </c>
+      <c r="F61" s="15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G61" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="15">
+        <f>MAX(E61-F61, 0)</f>
+        <v/>
+      </c>
+      <c r="I61" s="15">
+        <f>IF(H61&lt;=0.12, 0, IF(H61&lt;=0.5, MIN((MAX(H61-0.04,0)*0.05+MAX(H61-0.08,0)*0.05+MAX(H61-0.12,0)*0.05+MAX(H61-0.16,0)*0.05+MAX(H61-0.2,0)*0.05+MAX(H61-0.24,0)*0.05), H61-0.12), MIN((MAX(H61-0.04,0)*0.05+MAX(H61-0.08,0)*0.05+MAX(H61-0.12,0)*0.05+MAX(H61-0.16,0)*0.05+MAX(H61-0.2,0)*0.05+MAX(H61-0.24,0)*0.05)*(1+IF(H61&lt;=1,0.1,IF(H61&lt;=2,0.15,0.25))), (MAX(IF(H61&lt;=1,0.5,IF(H61&lt;=2,1,2))-0.04,0)*0.05+MAX(IF(H61&lt;=1,0.5,IF(H61&lt;=2,1,2))-0.08,0)*0.05+MAX(IF(H61&lt;=1,0.5,IF(H61&lt;=2,1,2))-0.12,0)*0.05+MAX(IF(H61&lt;=1,0.5,IF(H61&lt;=2,1,2))-0.16,0)*0.05+MAX(IF(H61&lt;=1,0.5,IF(H61&lt;=2,1,2))-0.2,0)*0.05+MAX(IF(H61&lt;=1,0.5,IF(H61&lt;=2,1,2))-0.24,0)*0.05)*(1+IF(H61&lt;=1,0,IF(H61&lt;=2,0.1,0.15)))+H61-IF(H61&lt;=1,0.5,IF(H61&lt;=2,1,2))))*1.04)</f>
+        <v/>
+      </c>
+      <c r="J61" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="15">
+        <f>B61+E61-F61-I61</f>
+        <v/>
+      </c>
+      <c r="N61" s="15">
+        <f>M61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="B62" s="15">
+        <f>M61</f>
+        <v/>
+      </c>
+      <c r="C62" s="15">
+        <f>MIN(B62, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D62" s="15">
+        <f>MAX(B62-C62, 0)</f>
+        <v/>
+      </c>
+      <c r="E62" s="15">
+        <f>C62*$B$6 + D62*$B$14</f>
+        <v/>
+      </c>
+      <c r="F62" s="15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G62" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="15">
+        <f>MAX(E62-F62, 0)</f>
+        <v/>
+      </c>
+      <c r="I62" s="15">
+        <f>IF(H62&lt;=0.12, 0, IF(H62&lt;=0.5, MIN((MAX(H62-0.04,0)*0.05+MAX(H62-0.08,0)*0.05+MAX(H62-0.12,0)*0.05+MAX(H62-0.16,0)*0.05+MAX(H62-0.2,0)*0.05+MAX(H62-0.24,0)*0.05), H62-0.12), MIN((MAX(H62-0.04,0)*0.05+MAX(H62-0.08,0)*0.05+MAX(H62-0.12,0)*0.05+MAX(H62-0.16,0)*0.05+MAX(H62-0.2,0)*0.05+MAX(H62-0.24,0)*0.05)*(1+IF(H62&lt;=1,0.1,IF(H62&lt;=2,0.15,0.25))), (MAX(IF(H62&lt;=1,0.5,IF(H62&lt;=2,1,2))-0.04,0)*0.05+MAX(IF(H62&lt;=1,0.5,IF(H62&lt;=2,1,2))-0.08,0)*0.05+MAX(IF(H62&lt;=1,0.5,IF(H62&lt;=2,1,2))-0.12,0)*0.05+MAX(IF(H62&lt;=1,0.5,IF(H62&lt;=2,1,2))-0.16,0)*0.05+MAX(IF(H62&lt;=1,0.5,IF(H62&lt;=2,1,2))-0.2,0)*0.05+MAX(IF(H62&lt;=1,0.5,IF(H62&lt;=2,1,2))-0.24,0)*0.05)*(1+IF(H62&lt;=1,0,IF(H62&lt;=2,0.1,0.15)))+H62-IF(H62&lt;=1,0.5,IF(H62&lt;=2,1,2))))*1.04)</f>
+        <v/>
+      </c>
+      <c r="J62" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="15">
+        <f>B62+E62-F62-I62</f>
+        <v/>
+      </c>
+      <c r="N62" s="15">
+        <f>M62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B63" s="15">
+        <f>M62</f>
+        <v/>
+      </c>
+      <c r="C63" s="15">
+        <f>MIN(B63, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D63" s="15">
+        <f>MAX(B63-C63, 0)</f>
+        <v/>
+      </c>
+      <c r="E63" s="15">
+        <f>C63*$B$6 + D63*$B$14</f>
+        <v/>
+      </c>
+      <c r="F63" s="15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G63" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="15">
+        <f>MAX(E63-F63, 0)</f>
+        <v/>
+      </c>
+      <c r="I63" s="15">
+        <f>IF(H63&lt;=0.12, 0, IF(H63&lt;=0.5, MIN((MAX(H63-0.04,0)*0.05+MAX(H63-0.08,0)*0.05+MAX(H63-0.12,0)*0.05+MAX(H63-0.16,0)*0.05+MAX(H63-0.2,0)*0.05+MAX(H63-0.24,0)*0.05), H63-0.12), MIN((MAX(H63-0.04,0)*0.05+MAX(H63-0.08,0)*0.05+MAX(H63-0.12,0)*0.05+MAX(H63-0.16,0)*0.05+MAX(H63-0.2,0)*0.05+MAX(H63-0.24,0)*0.05)*(1+IF(H63&lt;=1,0.1,IF(H63&lt;=2,0.15,0.25))), (MAX(IF(H63&lt;=1,0.5,IF(H63&lt;=2,1,2))-0.04,0)*0.05+MAX(IF(H63&lt;=1,0.5,IF(H63&lt;=2,1,2))-0.08,0)*0.05+MAX(IF(H63&lt;=1,0.5,IF(H63&lt;=2,1,2))-0.12,0)*0.05+MAX(IF(H63&lt;=1,0.5,IF(H63&lt;=2,1,2))-0.16,0)*0.05+MAX(IF(H63&lt;=1,0.5,IF(H63&lt;=2,1,2))-0.2,0)*0.05+MAX(IF(H63&lt;=1,0.5,IF(H63&lt;=2,1,2))-0.24,0)*0.05)*(1+IF(H63&lt;=1,0,IF(H63&lt;=2,0.1,0.15)))+H63-IF(H63&lt;=1,0.5,IF(H63&lt;=2,1,2))))*1.04)</f>
+        <v/>
+      </c>
+      <c r="J63" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="15">
+        <f>B63+E63-F63-I63</f>
+        <v/>
+      </c>
+      <c r="N63" s="15">
+        <f>M63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B64" s="15">
+        <f>M63</f>
+        <v/>
+      </c>
+      <c r="C64" s="15">
+        <f>MIN(B64, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D64" s="15">
+        <f>MAX(B64-C64, 0)</f>
+        <v/>
+      </c>
+      <c r="E64" s="15">
+        <f>C64*$B$6 + D64*$B$14</f>
+        <v/>
+      </c>
+      <c r="F64" s="15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G64" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="15">
+        <f>MAX(E64-F64, 0)</f>
+        <v/>
+      </c>
+      <c r="I64" s="15">
+        <f>IF(H64&lt;=0.12, 0, IF(H64&lt;=0.5, MIN((MAX(H64-0.04,0)*0.05+MAX(H64-0.08,0)*0.05+MAX(H64-0.12,0)*0.05+MAX(H64-0.16,0)*0.05+MAX(H64-0.2,0)*0.05+MAX(H64-0.24,0)*0.05), H64-0.12), MIN((MAX(H64-0.04,0)*0.05+MAX(H64-0.08,0)*0.05+MAX(H64-0.12,0)*0.05+MAX(H64-0.16,0)*0.05+MAX(H64-0.2,0)*0.05+MAX(H64-0.24,0)*0.05)*(1+IF(H64&lt;=1,0.1,IF(H64&lt;=2,0.15,0.25))), (MAX(IF(H64&lt;=1,0.5,IF(H64&lt;=2,1,2))-0.04,0)*0.05+MAX(IF(H64&lt;=1,0.5,IF(H64&lt;=2,1,2))-0.08,0)*0.05+MAX(IF(H64&lt;=1,0.5,IF(H64&lt;=2,1,2))-0.12,0)*0.05+MAX(IF(H64&lt;=1,0.5,IF(H64&lt;=2,1,2))-0.16,0)*0.05+MAX(IF(H64&lt;=1,0.5,IF(H64&lt;=2,1,2))-0.2,0)*0.05+MAX(IF(H64&lt;=1,0.5,IF(H64&lt;=2,1,2))-0.24,0)*0.05)*(1+IF(H64&lt;=1,0,IF(H64&lt;=2,0.1,0.15)))+H64-IF(H64&lt;=1,0.5,IF(H64&lt;=2,1,2))))*1.04)</f>
+        <v/>
+      </c>
+      <c r="J64" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="15">
+        <f>B64+E64-F64-I64</f>
+        <v/>
+      </c>
+      <c r="N64" s="15">
+        <f>M64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B65" s="15">
+        <f>M64</f>
+        <v/>
+      </c>
+      <c r="C65" s="15">
+        <f>MIN(B65, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D65" s="15">
+        <f>MAX(B65-C65, 0)</f>
+        <v/>
+      </c>
+      <c r="E65" s="15">
+        <f>C65*$B$6 + D65*$B$14</f>
+        <v/>
+      </c>
+      <c r="F65" s="15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G65" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="15">
+        <f>MAX(E65-F65, 0)</f>
+        <v/>
+      </c>
+      <c r="I65" s="15">
+        <f>IF(H65&lt;=0.12, 0, IF(H65&lt;=0.5, MIN((MAX(H65-0.04,0)*0.05+MAX(H65-0.08,0)*0.05+MAX(H65-0.12,0)*0.05+MAX(H65-0.16,0)*0.05+MAX(H65-0.2,0)*0.05+MAX(H65-0.24,0)*0.05), H65-0.12), MIN((MAX(H65-0.04,0)*0.05+MAX(H65-0.08,0)*0.05+MAX(H65-0.12,0)*0.05+MAX(H65-0.16,0)*0.05+MAX(H65-0.2,0)*0.05+MAX(H65-0.24,0)*0.05)*(1+IF(H65&lt;=1,0.1,IF(H65&lt;=2,0.15,0.25))), (MAX(IF(H65&lt;=1,0.5,IF(H65&lt;=2,1,2))-0.04,0)*0.05+MAX(IF(H65&lt;=1,0.5,IF(H65&lt;=2,1,2))-0.08,0)*0.05+MAX(IF(H65&lt;=1,0.5,IF(H65&lt;=2,1,2))-0.12,0)*0.05+MAX(IF(H65&lt;=1,0.5,IF(H65&lt;=2,1,2))-0.16,0)*0.05+MAX(IF(H65&lt;=1,0.5,IF(H65&lt;=2,1,2))-0.2,0)*0.05+MAX(IF(H65&lt;=1,0.5,IF(H65&lt;=2,1,2))-0.24,0)*0.05)*(1+IF(H65&lt;=1,0,IF(H65&lt;=2,0.1,0.15)))+H65-IF(H65&lt;=1,0.5,IF(H65&lt;=2,1,2))))*1.04)</f>
+        <v/>
+      </c>
+      <c r="J65" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="15">
+        <f>B65+E65-F65-I65</f>
+        <v/>
+      </c>
+      <c r="N65" s="15">
+        <f>M65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="B66" s="15">
+        <f>M65</f>
+        <v/>
+      </c>
+      <c r="C66" s="15">
+        <f>MIN(B66, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D66" s="15">
+        <f>MAX(B66-C66, 0)</f>
+        <v/>
+      </c>
+      <c r="E66" s="15">
+        <f>C66*$B$6 + D66*$B$14</f>
+        <v/>
+      </c>
+      <c r="F66" s="15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G66" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="15">
+        <f>MAX(E66-F66, 0)</f>
+        <v/>
+      </c>
+      <c r="I66" s="15">
+        <f>IF(H66&lt;=0.12, 0, IF(H66&lt;=0.5, MIN((MAX(H66-0.04,0)*0.05+MAX(H66-0.08,0)*0.05+MAX(H66-0.12,0)*0.05+MAX(H66-0.16,0)*0.05+MAX(H66-0.2,0)*0.05+MAX(H66-0.24,0)*0.05), H66-0.12), MIN((MAX(H66-0.04,0)*0.05+MAX(H66-0.08,0)*0.05+MAX(H66-0.12,0)*0.05+MAX(H66-0.16,0)*0.05+MAX(H66-0.2,0)*0.05+MAX(H66-0.24,0)*0.05)*(1+IF(H66&lt;=1,0.1,IF(H66&lt;=2,0.15,0.25))), (MAX(IF(H66&lt;=1,0.5,IF(H66&lt;=2,1,2))-0.04,0)*0.05+MAX(IF(H66&lt;=1,0.5,IF(H66&lt;=2,1,2))-0.08,0)*0.05+MAX(IF(H66&lt;=1,0.5,IF(H66&lt;=2,1,2))-0.12,0)*0.05+MAX(IF(H66&lt;=1,0.5,IF(H66&lt;=2,1,2))-0.16,0)*0.05+MAX(IF(H66&lt;=1,0.5,IF(H66&lt;=2,1,2))-0.2,0)*0.05+MAX(IF(H66&lt;=1,0.5,IF(H66&lt;=2,1,2))-0.24,0)*0.05)*(1+IF(H66&lt;=1,0,IF(H66&lt;=2,0.1,0.15)))+H66-IF(H66&lt;=1,0.5,IF(H66&lt;=2,1,2))))*1.04)</f>
+        <v/>
+      </c>
+      <c r="J66" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="15">
+        <f>B66+E66-F66-I66</f>
+        <v/>
+      </c>
+      <c r="N66" s="15">
+        <f>M66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>COMPANY SOLO ROUTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="19" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B70" s="19" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="C70" s="19" t="inlineStr">
+        <is>
+          <t>Deployed</t>
+        </is>
+      </c>
+      <c r="D70" s="19" t="inlineStr">
+        <is>
+          <t>Idle</t>
+        </is>
+      </c>
+      <c r="E70" s="19" t="inlineStr">
+        <is>
+          <t>Profit</t>
+        </is>
+      </c>
+      <c r="F70" s="19" t="inlineStr">
+        <is>
+          <t>Overhead</t>
+        </is>
+      </c>
+      <c r="G70" s="19" t="inlineStr">
+        <is>
+          <t>Salary Paid</t>
+        </is>
+      </c>
+      <c r="H70" s="19" t="inlineStr">
+        <is>
+          <t>Taxable Profit</t>
+        </is>
+      </c>
+      <c r="I70" s="19" t="inlineStr">
+        <is>
+          <t>Income Tax</t>
+        </is>
+      </c>
+      <c r="J70" s="19" t="inlineStr">
+        <is>
+          <t>Not Lent Back</t>
+        </is>
+      </c>
+      <c r="K70" s="19" t="inlineStr">
+        <is>
+          <t>New Loan</t>
+        </is>
+      </c>
+      <c r="L70" s="19" t="inlineStr">
+        <is>
+          <t>Loans Outstanding</t>
+        </is>
+      </c>
+      <c r="M70" s="19" t="inlineStr">
+        <is>
+          <t>Closing Capital</t>
+        </is>
+      </c>
+      <c r="N70" s="19" t="inlineStr">
+        <is>
+          <t>Net Equity (Closing - Loans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="B71" s="15">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="C71" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="15">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="N71" s="15">
+        <f>$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B72" s="15">
+        <f>M71</f>
+        <v/>
+      </c>
+      <c r="C72" s="15">
+        <f>MIN(B72, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D72" s="15">
+        <f>MAX(B72-C72, 0)</f>
+        <v/>
+      </c>
+      <c r="E72" s="15">
+        <f>C72*$B$6 + D72*$B$14</f>
+        <v/>
+      </c>
+      <c r="F72" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G72" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="15">
+        <f>MAX(E72-F72-G72, 0)</f>
+        <v/>
+      </c>
+      <c r="I72" s="15">
+        <f>H72*$B$7</f>
+        <v/>
+      </c>
+      <c r="J72" s="15">
+        <f>G72*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K72" s="15">
+        <f>G72*$B$10</f>
+        <v/>
+      </c>
+      <c r="L72" s="15">
+        <f>L71+K72</f>
+        <v/>
+      </c>
+      <c r="M72" s="15">
+        <f>B72+E72-F72-I72-J72</f>
+        <v/>
+      </c>
+      <c r="N72" s="15">
+        <f>M72-L72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B73" s="15">
+        <f>M72</f>
+        <v/>
+      </c>
+      <c r="C73" s="15">
+        <f>MIN(B73, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D73" s="15">
+        <f>MAX(B73-C73, 0)</f>
+        <v/>
+      </c>
+      <c r="E73" s="15">
+        <f>C73*$B$6 + D73*$B$14</f>
+        <v/>
+      </c>
+      <c r="F73" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G73" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="15">
+        <f>MAX(E73-F73-G73, 0)</f>
+        <v/>
+      </c>
+      <c r="I73" s="15">
+        <f>H73*$B$7</f>
+        <v/>
+      </c>
+      <c r="J73" s="15">
+        <f>G73*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K73" s="15">
+        <f>G73*$B$10</f>
+        <v/>
+      </c>
+      <c r="L73" s="15">
+        <f>L72+K73</f>
+        <v/>
+      </c>
+      <c r="M73" s="15">
+        <f>B73+E73-F73-I73-J73</f>
+        <v/>
+      </c>
+      <c r="N73" s="15">
+        <f>M73-L73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B74" s="15">
+        <f>M73</f>
+        <v/>
+      </c>
+      <c r="C74" s="15">
+        <f>MIN(B74, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D74" s="15">
+        <f>MAX(B74-C74, 0)</f>
+        <v/>
+      </c>
+      <c r="E74" s="15">
+        <f>C74*$B$6 + D74*$B$14</f>
+        <v/>
+      </c>
+      <c r="F74" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G74" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="15">
+        <f>MAX(E74-F74-G74, 0)</f>
+        <v/>
+      </c>
+      <c r="I74" s="15">
+        <f>H74*$B$7</f>
+        <v/>
+      </c>
+      <c r="J74" s="15">
+        <f>G74*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K74" s="15">
+        <f>G74*$B$10</f>
+        <v/>
+      </c>
+      <c r="L74" s="15">
+        <f>L73+K74</f>
+        <v/>
+      </c>
+      <c r="M74" s="15">
+        <f>B74+E74-F74-I74-J74</f>
+        <v/>
+      </c>
+      <c r="N74" s="15">
+        <f>M74-L74</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B75" s="15">
+        <f>M74</f>
+        <v/>
+      </c>
+      <c r="C75" s="15">
+        <f>MIN(B75, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D75" s="15">
+        <f>MAX(B75-C75, 0)</f>
+        <v/>
+      </c>
+      <c r="E75" s="15">
+        <f>C75*$B$6 + D75*$B$14</f>
+        <v/>
+      </c>
+      <c r="F75" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G75" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="15">
+        <f>MAX(E75-F75-G75, 0)</f>
+        <v/>
+      </c>
+      <c r="I75" s="15">
+        <f>H75*$B$7</f>
+        <v/>
+      </c>
+      <c r="J75" s="15">
+        <f>G75*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K75" s="15">
+        <f>G75*$B$10</f>
+        <v/>
+      </c>
+      <c r="L75" s="15">
+        <f>L74+K75</f>
+        <v/>
+      </c>
+      <c r="M75" s="15">
+        <f>B75+E75-F75-I75-J75</f>
+        <v/>
+      </c>
+      <c r="N75" s="15">
+        <f>M75-L75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B76" s="15">
+        <f>M75</f>
+        <v/>
+      </c>
+      <c r="C76" s="15">
+        <f>MIN(B76, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D76" s="15">
+        <f>MAX(B76-C76, 0)</f>
+        <v/>
+      </c>
+      <c r="E76" s="15">
+        <f>C76*$B$6 + D76*$B$14</f>
+        <v/>
+      </c>
+      <c r="F76" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G76" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="15">
+        <f>MAX(E76-F76-G76, 0)</f>
+        <v/>
+      </c>
+      <c r="I76" s="15">
+        <f>H76*$B$7</f>
+        <v/>
+      </c>
+      <c r="J76" s="15">
+        <f>G76*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K76" s="15">
+        <f>G76*$B$10</f>
+        <v/>
+      </c>
+      <c r="L76" s="15">
+        <f>L75+K76</f>
+        <v/>
+      </c>
+      <c r="M76" s="15">
+        <f>B76+E76-F76-I76-J76</f>
+        <v/>
+      </c>
+      <c r="N76" s="15">
+        <f>M76-L76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B77" s="15">
+        <f>M76</f>
+        <v/>
+      </c>
+      <c r="C77" s="15">
+        <f>MIN(B77, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D77" s="15">
+        <f>MAX(B77-C77, 0)</f>
+        <v/>
+      </c>
+      <c r="E77" s="15">
+        <f>C77*$B$6 + D77*$B$14</f>
+        <v/>
+      </c>
+      <c r="F77" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G77" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="15">
+        <f>MAX(E77-F77-G77, 0)</f>
+        <v/>
+      </c>
+      <c r="I77" s="15">
+        <f>H77*$B$7</f>
+        <v/>
+      </c>
+      <c r="J77" s="15">
+        <f>G77*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K77" s="15">
+        <f>G77*$B$10</f>
+        <v/>
+      </c>
+      <c r="L77" s="15">
+        <f>L76+K77</f>
+        <v/>
+      </c>
+      <c r="M77" s="15">
+        <f>B77+E77-F77-I77-J77</f>
+        <v/>
+      </c>
+      <c r="N77" s="15">
+        <f>M77-L77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B78" s="15">
+        <f>M77</f>
+        <v/>
+      </c>
+      <c r="C78" s="15">
+        <f>MIN(B78, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D78" s="15">
+        <f>MAX(B78-C78, 0)</f>
+        <v/>
+      </c>
+      <c r="E78" s="15">
+        <f>C78*$B$6 + D78*$B$14</f>
+        <v/>
+      </c>
+      <c r="F78" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G78" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="15">
+        <f>MAX(E78-F78-G78, 0)</f>
+        <v/>
+      </c>
+      <c r="I78" s="15">
+        <f>H78*$B$7</f>
+        <v/>
+      </c>
+      <c r="J78" s="15">
+        <f>G78*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K78" s="15">
+        <f>G78*$B$10</f>
+        <v/>
+      </c>
+      <c r="L78" s="15">
+        <f>L77+K78</f>
+        <v/>
+      </c>
+      <c r="M78" s="15">
+        <f>B78+E78-F78-I78-J78</f>
+        <v/>
+      </c>
+      <c r="N78" s="15">
+        <f>M78-L78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B79" s="15">
+        <f>M78</f>
+        <v/>
+      </c>
+      <c r="C79" s="15">
+        <f>MIN(B79, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D79" s="15">
+        <f>MAX(B79-C79, 0)</f>
+        <v/>
+      </c>
+      <c r="E79" s="15">
+        <f>C79*$B$6 + D79*$B$14</f>
+        <v/>
+      </c>
+      <c r="F79" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G79" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="15">
+        <f>MAX(E79-F79-G79, 0)</f>
+        <v/>
+      </c>
+      <c r="I79" s="15">
+        <f>H79*$B$7</f>
+        <v/>
+      </c>
+      <c r="J79" s="15">
+        <f>G79*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K79" s="15">
+        <f>G79*$B$10</f>
+        <v/>
+      </c>
+      <c r="L79" s="15">
+        <f>L78+K79</f>
+        <v/>
+      </c>
+      <c r="M79" s="15">
+        <f>B79+E79-F79-I79-J79</f>
+        <v/>
+      </c>
+      <c r="N79" s="15">
+        <f>M79-L79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="B80" s="15">
+        <f>M79</f>
+        <v/>
+      </c>
+      <c r="C80" s="15">
+        <f>MIN(B80, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D80" s="15">
+        <f>MAX(B80-C80, 0)</f>
+        <v/>
+      </c>
+      <c r="E80" s="15">
+        <f>C80*$B$6 + D80*$B$14</f>
+        <v/>
+      </c>
+      <c r="F80" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G80" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="15">
+        <f>MAX(E80-F80-G80, 0)</f>
+        <v/>
+      </c>
+      <c r="I80" s="15">
+        <f>H80*$B$7</f>
+        <v/>
+      </c>
+      <c r="J80" s="15">
+        <f>G80*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K80" s="15">
+        <f>G80*$B$10</f>
+        <v/>
+      </c>
+      <c r="L80" s="15">
+        <f>L79+K80</f>
+        <v/>
+      </c>
+      <c r="M80" s="15">
+        <f>B80+E80-F80-I80-J80</f>
+        <v/>
+      </c>
+      <c r="N80" s="15">
+        <f>M80-L80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B81" s="15">
+        <f>M80</f>
+        <v/>
+      </c>
+      <c r="C81" s="15">
+        <f>MIN(B81, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D81" s="15">
+        <f>MAX(B81-C81, 0)</f>
+        <v/>
+      </c>
+      <c r="E81" s="15">
+        <f>C81*$B$6 + D81*$B$14</f>
+        <v/>
+      </c>
+      <c r="F81" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G81" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="15">
+        <f>MAX(E81-F81-G81, 0)</f>
+        <v/>
+      </c>
+      <c r="I81" s="15">
+        <f>H81*$B$7</f>
+        <v/>
+      </c>
+      <c r="J81" s="15">
+        <f>G81*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K81" s="15">
+        <f>G81*$B$10</f>
+        <v/>
+      </c>
+      <c r="L81" s="15">
+        <f>L80+K81</f>
+        <v/>
+      </c>
+      <c r="M81" s="15">
+        <f>B81+E81-F81-I81-J81</f>
+        <v/>
+      </c>
+      <c r="N81" s="15">
+        <f>M81-L81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="B82" s="15">
+        <f>M81</f>
+        <v/>
+      </c>
+      <c r="C82" s="15">
+        <f>MIN(B82, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D82" s="15">
+        <f>MAX(B82-C82, 0)</f>
+        <v/>
+      </c>
+      <c r="E82" s="15">
+        <f>C82*$B$6 + D82*$B$14</f>
+        <v/>
+      </c>
+      <c r="F82" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G82" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="15">
+        <f>MAX(E82-F82-G82, 0)</f>
+        <v/>
+      </c>
+      <c r="I82" s="15">
+        <f>H82*$B$7</f>
+        <v/>
+      </c>
+      <c r="J82" s="15">
+        <f>G82*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K82" s="15">
+        <f>G82*$B$10</f>
+        <v/>
+      </c>
+      <c r="L82" s="15">
+        <f>L81+K82</f>
+        <v/>
+      </c>
+      <c r="M82" s="15">
+        <f>B82+E82-F82-I82-J82</f>
+        <v/>
+      </c>
+      <c r="N82" s="15">
+        <f>M82-L82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="B83" s="15">
+        <f>M82</f>
+        <v/>
+      </c>
+      <c r="C83" s="15">
+        <f>MIN(B83, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D83" s="15">
+        <f>MAX(B83-C83, 0)</f>
+        <v/>
+      </c>
+      <c r="E83" s="15">
+        <f>C83*$B$6 + D83*$B$14</f>
+        <v/>
+      </c>
+      <c r="F83" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G83" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="15">
+        <f>MAX(E83-F83-G83, 0)</f>
+        <v/>
+      </c>
+      <c r="I83" s="15">
+        <f>H83*$B$7</f>
+        <v/>
+      </c>
+      <c r="J83" s="15">
+        <f>G83*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K83" s="15">
+        <f>G83*$B$10</f>
+        <v/>
+      </c>
+      <c r="L83" s="15">
+        <f>L82+K83</f>
+        <v/>
+      </c>
+      <c r="M83" s="15">
+        <f>B83+E83-F83-I83-J83</f>
+        <v/>
+      </c>
+      <c r="N83" s="15">
+        <f>M83-L83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="B84" s="15">
+        <f>M83</f>
+        <v/>
+      </c>
+      <c r="C84" s="15">
+        <f>MIN(B84, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D84" s="15">
+        <f>MAX(B84-C84, 0)</f>
+        <v/>
+      </c>
+      <c r="E84" s="15">
+        <f>C84*$B$6 + D84*$B$14</f>
+        <v/>
+      </c>
+      <c r="F84" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G84" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="15">
+        <f>MAX(E84-F84-G84, 0)</f>
+        <v/>
+      </c>
+      <c r="I84" s="15">
+        <f>H84*$B$7</f>
+        <v/>
+      </c>
+      <c r="J84" s="15">
+        <f>G84*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K84" s="15">
+        <f>G84*$B$10</f>
+        <v/>
+      </c>
+      <c r="L84" s="15">
+        <f>L83+K84</f>
+        <v/>
+      </c>
+      <c r="M84" s="15">
+        <f>B84+E84-F84-I84-J84</f>
+        <v/>
+      </c>
+      <c r="N84" s="15">
+        <f>M84-L84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="B85" s="15">
+        <f>M84</f>
+        <v/>
+      </c>
+      <c r="C85" s="15">
+        <f>MIN(B85, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D85" s="15">
+        <f>MAX(B85-C85, 0)</f>
+        <v/>
+      </c>
+      <c r="E85" s="15">
+        <f>C85*$B$6 + D85*$B$14</f>
+        <v/>
+      </c>
+      <c r="F85" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G85" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="15">
+        <f>MAX(E85-F85-G85, 0)</f>
+        <v/>
+      </c>
+      <c r="I85" s="15">
+        <f>H85*$B$7</f>
+        <v/>
+      </c>
+      <c r="J85" s="15">
+        <f>G85*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K85" s="15">
+        <f>G85*$B$10</f>
+        <v/>
+      </c>
+      <c r="L85" s="15">
+        <f>L84+K85</f>
+        <v/>
+      </c>
+      <c r="M85" s="15">
+        <f>B85+E85-F85-I85-J85</f>
+        <v/>
+      </c>
+      <c r="N85" s="15">
+        <f>M85-L85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B86" s="15">
+        <f>M85</f>
+        <v/>
+      </c>
+      <c r="C86" s="15">
+        <f>MIN(B86, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D86" s="15">
+        <f>MAX(B86-C86, 0)</f>
+        <v/>
+      </c>
+      <c r="E86" s="15">
+        <f>C86*$B$6 + D86*$B$14</f>
+        <v/>
+      </c>
+      <c r="F86" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G86" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="15">
+        <f>MAX(E86-F86-G86, 0)</f>
+        <v/>
+      </c>
+      <c r="I86" s="15">
+        <f>H86*$B$7</f>
+        <v/>
+      </c>
+      <c r="J86" s="15">
+        <f>G86*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K86" s="15">
+        <f>G86*$B$10</f>
+        <v/>
+      </c>
+      <c r="L86" s="15">
+        <f>L85+K86</f>
+        <v/>
+      </c>
+      <c r="M86" s="15">
+        <f>B86+E86-F86-I86-J86</f>
+        <v/>
+      </c>
+      <c r="N86" s="15">
+        <f>M86-L86</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="B87" s="15">
+        <f>M86</f>
+        <v/>
+      </c>
+      <c r="C87" s="15">
+        <f>MIN(B87, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D87" s="15">
+        <f>MAX(B87-C87, 0)</f>
+        <v/>
+      </c>
+      <c r="E87" s="15">
+        <f>C87*$B$6 + D87*$B$14</f>
+        <v/>
+      </c>
+      <c r="F87" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G87" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="15">
+        <f>MAX(E87-F87-G87, 0)</f>
+        <v/>
+      </c>
+      <c r="I87" s="15">
+        <f>H87*$B$7</f>
+        <v/>
+      </c>
+      <c r="J87" s="15">
+        <f>G87*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K87" s="15">
+        <f>G87*$B$10</f>
+        <v/>
+      </c>
+      <c r="L87" s="15">
+        <f>L86+K87</f>
+        <v/>
+      </c>
+      <c r="M87" s="15">
+        <f>B87+E87-F87-I87-J87</f>
+        <v/>
+      </c>
+      <c r="N87" s="15">
+        <f>M87-L87</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B88" s="15">
+        <f>M87</f>
+        <v/>
+      </c>
+      <c r="C88" s="15">
+        <f>MIN(B88, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D88" s="15">
+        <f>MAX(B88-C88, 0)</f>
+        <v/>
+      </c>
+      <c r="E88" s="15">
+        <f>C88*$B$6 + D88*$B$14</f>
+        <v/>
+      </c>
+      <c r="F88" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G88" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="15">
+        <f>MAX(E88-F88-G88, 0)</f>
+        <v/>
+      </c>
+      <c r="I88" s="15">
+        <f>H88*$B$7</f>
+        <v/>
+      </c>
+      <c r="J88" s="15">
+        <f>G88*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K88" s="15">
+        <f>G88*$B$10</f>
+        <v/>
+      </c>
+      <c r="L88" s="15">
+        <f>L87+K88</f>
+        <v/>
+      </c>
+      <c r="M88" s="15">
+        <f>B88+E88-F88-I88-J88</f>
+        <v/>
+      </c>
+      <c r="N88" s="15">
+        <f>M88-L88</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B89" s="15">
+        <f>M88</f>
+        <v/>
+      </c>
+      <c r="C89" s="15">
+        <f>MIN(B89, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D89" s="15">
+        <f>MAX(B89-C89, 0)</f>
+        <v/>
+      </c>
+      <c r="E89" s="15">
+        <f>C89*$B$6 + D89*$B$14</f>
+        <v/>
+      </c>
+      <c r="F89" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G89" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="15">
+        <f>MAX(E89-F89-G89, 0)</f>
+        <v/>
+      </c>
+      <c r="I89" s="15">
+        <f>H89*$B$7</f>
+        <v/>
+      </c>
+      <c r="J89" s="15">
+        <f>G89*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K89" s="15">
+        <f>G89*$B$10</f>
+        <v/>
+      </c>
+      <c r="L89" s="15">
+        <f>L88+K89</f>
+        <v/>
+      </c>
+      <c r="M89" s="15">
+        <f>B89+E89-F89-I89-J89</f>
+        <v/>
+      </c>
+      <c r="N89" s="15">
+        <f>M89-L89</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B90" s="15">
+        <f>M89</f>
+        <v/>
+      </c>
+      <c r="C90" s="15">
+        <f>MIN(B90, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D90" s="15">
+        <f>MAX(B90-C90, 0)</f>
+        <v/>
+      </c>
+      <c r="E90" s="15">
+        <f>C90*$B$6 + D90*$B$14</f>
+        <v/>
+      </c>
+      <c r="F90" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G90" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="15">
+        <f>MAX(E90-F90-G90, 0)</f>
+        <v/>
+      </c>
+      <c r="I90" s="15">
+        <f>H90*$B$7</f>
+        <v/>
+      </c>
+      <c r="J90" s="15">
+        <f>G90*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K90" s="15">
+        <f>G90*$B$10</f>
+        <v/>
+      </c>
+      <c r="L90" s="15">
+        <f>L89+K90</f>
+        <v/>
+      </c>
+      <c r="M90" s="15">
+        <f>B90+E90-F90-I90-J90</f>
+        <v/>
+      </c>
+      <c r="N90" s="15">
+        <f>M90-L90</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="B91" s="15">
+        <f>M90</f>
+        <v/>
+      </c>
+      <c r="C91" s="15">
+        <f>MIN(B91, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D91" s="15">
+        <f>MAX(B91-C91, 0)</f>
+        <v/>
+      </c>
+      <c r="E91" s="15">
+        <f>C91*$B$6 + D91*$B$14</f>
+        <v/>
+      </c>
+      <c r="F91" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G91" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="15">
+        <f>MAX(E91-F91-G91, 0)</f>
+        <v/>
+      </c>
+      <c r="I91" s="15">
+        <f>H91*$B$7</f>
+        <v/>
+      </c>
+      <c r="J91" s="15">
+        <f>G91*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K91" s="15">
+        <f>G91*$B$10</f>
+        <v/>
+      </c>
+      <c r="L91" s="15">
+        <f>L90+K91</f>
+        <v/>
+      </c>
+      <c r="M91" s="15">
+        <f>B91+E91-F91-I91-J91</f>
+        <v/>
+      </c>
+      <c r="N91" s="15">
+        <f>M91-L91</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>COMPANY + 1 EMPLOYEE ROUTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="19" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B95" s="19" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="C95" s="19" t="inlineStr">
+        <is>
+          <t>Deployed</t>
+        </is>
+      </c>
+      <c r="D95" s="19" t="inlineStr">
+        <is>
+          <t>Idle</t>
+        </is>
+      </c>
+      <c r="E95" s="19" t="inlineStr">
+        <is>
+          <t>Profit</t>
+        </is>
+      </c>
+      <c r="F95" s="19" t="inlineStr">
+        <is>
+          <t>Overhead</t>
+        </is>
+      </c>
+      <c r="G95" s="19" t="inlineStr">
+        <is>
+          <t>Salary Paid</t>
+        </is>
+      </c>
+      <c r="H95" s="19" t="inlineStr">
+        <is>
+          <t>Taxable Profit</t>
+        </is>
+      </c>
+      <c r="I95" s="19" t="inlineStr">
+        <is>
+          <t>Income Tax</t>
+        </is>
+      </c>
+      <c r="J95" s="19" t="inlineStr">
+        <is>
+          <t>Not Lent Back</t>
+        </is>
+      </c>
+      <c r="K95" s="19" t="inlineStr">
+        <is>
+          <t>New Loan</t>
+        </is>
+      </c>
+      <c r="L95" s="19" t="inlineStr">
+        <is>
+          <t>Loans Outstanding</t>
+        </is>
+      </c>
+      <c r="M95" s="19" t="inlineStr">
+        <is>
+          <t>Closing Capital</t>
+        </is>
+      </c>
+      <c r="N95" s="19" t="inlineStr">
+        <is>
+          <t>Net Equity (Closing - Loans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="B96" s="15">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="C96" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="15">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="N96" s="15">
+        <f>$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B97" s="15">
+        <f>M96</f>
+        <v/>
+      </c>
+      <c r="C97" s="15">
+        <f>MIN(B97, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D97" s="15">
+        <f>MAX(B97-C97, 0)</f>
+        <v/>
+      </c>
+      <c r="E97" s="15">
+        <f>C97*$B$6 + D97*$B$14</f>
+        <v/>
+      </c>
+      <c r="F97" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G97" s="15">
+        <f>IF($B$7&gt;0, MIN(1*$B$9, $B$11*MAX(E97-F97, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H97" s="15">
+        <f>MAX(E97-F97-G97, 0)</f>
+        <v/>
+      </c>
+      <c r="I97" s="15">
+        <f>H97*$B$7</f>
+        <v/>
+      </c>
+      <c r="J97" s="15">
+        <f>G97*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K97" s="15">
+        <f>G97*$B$10</f>
+        <v/>
+      </c>
+      <c r="L97" s="15">
+        <f>L96+K97</f>
+        <v/>
+      </c>
+      <c r="M97" s="15">
+        <f>B97+E97-F97-I97-J97</f>
+        <v/>
+      </c>
+      <c r="N97" s="15">
+        <f>M97-L97</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B98" s="15">
+        <f>M97</f>
+        <v/>
+      </c>
+      <c r="C98" s="15">
+        <f>MIN(B98, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D98" s="15">
+        <f>MAX(B98-C98, 0)</f>
+        <v/>
+      </c>
+      <c r="E98" s="15">
+        <f>C98*$B$6 + D98*$B$14</f>
+        <v/>
+      </c>
+      <c r="F98" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G98" s="15">
+        <f>IF($B$7&gt;0, MIN(1*$B$9, $B$11*MAX(E98-F98, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H98" s="15">
+        <f>MAX(E98-F98-G98, 0)</f>
+        <v/>
+      </c>
+      <c r="I98" s="15">
+        <f>H98*$B$7</f>
+        <v/>
+      </c>
+      <c r="J98" s="15">
+        <f>G98*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K98" s="15">
+        <f>G98*$B$10</f>
+        <v/>
+      </c>
+      <c r="L98" s="15">
+        <f>L97+K98</f>
+        <v/>
+      </c>
+      <c r="M98" s="15">
+        <f>B98+E98-F98-I98-J98</f>
+        <v/>
+      </c>
+      <c r="N98" s="15">
+        <f>M98-L98</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B99" s="15">
+        <f>M98</f>
+        <v/>
+      </c>
+      <c r="C99" s="15">
+        <f>MIN(B99, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D99" s="15">
+        <f>MAX(B99-C99, 0)</f>
+        <v/>
+      </c>
+      <c r="E99" s="15">
+        <f>C99*$B$6 + D99*$B$14</f>
+        <v/>
+      </c>
+      <c r="F99" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G99" s="15">
+        <f>IF($B$7&gt;0, MIN(1*$B$9, $B$11*MAX(E99-F99, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H99" s="15">
+        <f>MAX(E99-F99-G99, 0)</f>
+        <v/>
+      </c>
+      <c r="I99" s="15">
+        <f>H99*$B$7</f>
+        <v/>
+      </c>
+      <c r="J99" s="15">
+        <f>G99*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K99" s="15">
+        <f>G99*$B$10</f>
+        <v/>
+      </c>
+      <c r="L99" s="15">
+        <f>L98+K99</f>
+        <v/>
+      </c>
+      <c r="M99" s="15">
+        <f>B99+E99-F99-I99-J99</f>
+        <v/>
+      </c>
+      <c r="N99" s="15">
+        <f>M99-L99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B100" s="15">
+        <f>M99</f>
+        <v/>
+      </c>
+      <c r="C100" s="15">
+        <f>MIN(B100, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D100" s="15">
+        <f>MAX(B100-C100, 0)</f>
+        <v/>
+      </c>
+      <c r="E100" s="15">
+        <f>C100*$B$6 + D100*$B$14</f>
+        <v/>
+      </c>
+      <c r="F100" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G100" s="15">
+        <f>IF($B$7&gt;0, MIN(1*$B$9, $B$11*MAX(E100-F100, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H100" s="15">
+        <f>MAX(E100-F100-G100, 0)</f>
+        <v/>
+      </c>
+      <c r="I100" s="15">
+        <f>H100*$B$7</f>
+        <v/>
+      </c>
+      <c r="J100" s="15">
+        <f>G100*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K100" s="15">
+        <f>G100*$B$10</f>
+        <v/>
+      </c>
+      <c r="L100" s="15">
+        <f>L99+K100</f>
+        <v/>
+      </c>
+      <c r="M100" s="15">
+        <f>B100+E100-F100-I100-J100</f>
+        <v/>
+      </c>
+      <c r="N100" s="15">
+        <f>M100-L100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B101" s="15">
+        <f>M100</f>
+        <v/>
+      </c>
+      <c r="C101" s="15">
+        <f>MIN(B101, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D101" s="15">
+        <f>MAX(B101-C101, 0)</f>
+        <v/>
+      </c>
+      <c r="E101" s="15">
+        <f>C101*$B$6 + D101*$B$14</f>
+        <v/>
+      </c>
+      <c r="F101" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G101" s="15">
+        <f>IF($B$7&gt;0, MIN(1*$B$9, $B$11*MAX(E101-F101, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H101" s="15">
+        <f>MAX(E101-F101-G101, 0)</f>
+        <v/>
+      </c>
+      <c r="I101" s="15">
+        <f>H101*$B$7</f>
+        <v/>
+      </c>
+      <c r="J101" s="15">
+        <f>G101*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K101" s="15">
+        <f>G101*$B$10</f>
+        <v/>
+      </c>
+      <c r="L101" s="15">
+        <f>L100+K101</f>
+        <v/>
+      </c>
+      <c r="M101" s="15">
+        <f>B101+E101-F101-I101-J101</f>
+        <v/>
+      </c>
+      <c r="N101" s="15">
+        <f>M101-L101</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B102" s="15">
+        <f>M101</f>
+        <v/>
+      </c>
+      <c r="C102" s="15">
+        <f>MIN(B102, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D102" s="15">
+        <f>MAX(B102-C102, 0)</f>
+        <v/>
+      </c>
+      <c r="E102" s="15">
+        <f>C102*$B$6 + D102*$B$14</f>
+        <v/>
+      </c>
+      <c r="F102" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G102" s="15">
+        <f>IF($B$7&gt;0, MIN(1*$B$9, $B$11*MAX(E102-F102, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H102" s="15">
+        <f>MAX(E102-F102-G102, 0)</f>
+        <v/>
+      </c>
+      <c r="I102" s="15">
+        <f>H102*$B$7</f>
+        <v/>
+      </c>
+      <c r="J102" s="15">
+        <f>G102*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K102" s="15">
+        <f>G102*$B$10</f>
+        <v/>
+      </c>
+      <c r="L102" s="15">
+        <f>L101+K102</f>
+        <v/>
+      </c>
+      <c r="M102" s="15">
+        <f>B102+E102-F102-I102-J102</f>
+        <v/>
+      </c>
+      <c r="N102" s="15">
+        <f>M102-L102</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B103" s="15">
+        <f>M102</f>
+        <v/>
+      </c>
+      <c r="C103" s="15">
+        <f>MIN(B103, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D103" s="15">
+        <f>MAX(B103-C103, 0)</f>
+        <v/>
+      </c>
+      <c r="E103" s="15">
+        <f>C103*$B$6 + D103*$B$14</f>
+        <v/>
+      </c>
+      <c r="F103" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G103" s="15">
+        <f>IF($B$7&gt;0, MIN(1*$B$9, $B$11*MAX(E103-F103, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H103" s="15">
+        <f>MAX(E103-F103-G103, 0)</f>
+        <v/>
+      </c>
+      <c r="I103" s="15">
+        <f>H103*$B$7</f>
+        <v/>
+      </c>
+      <c r="J103" s="15">
+        <f>G103*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K103" s="15">
+        <f>G103*$B$10</f>
+        <v/>
+      </c>
+      <c r="L103" s="15">
+        <f>L102+K103</f>
+        <v/>
+      </c>
+      <c r="M103" s="15">
+        <f>B103+E103-F103-I103-J103</f>
+        <v/>
+      </c>
+      <c r="N103" s="15">
+        <f>M103-L103</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B104" s="15">
+        <f>M103</f>
+        <v/>
+      </c>
+      <c r="C104" s="15">
+        <f>MIN(B104, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D104" s="15">
+        <f>MAX(B104-C104, 0)</f>
+        <v/>
+      </c>
+      <c r="E104" s="15">
+        <f>C104*$B$6 + D104*$B$14</f>
+        <v/>
+      </c>
+      <c r="F104" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G104" s="15">
+        <f>IF($B$7&gt;0, MIN(1*$B$9, $B$11*MAX(E104-F104, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H104" s="15">
+        <f>MAX(E104-F104-G104, 0)</f>
+        <v/>
+      </c>
+      <c r="I104" s="15">
+        <f>H104*$B$7</f>
+        <v/>
+      </c>
+      <c r="J104" s="15">
+        <f>G104*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K104" s="15">
+        <f>G104*$B$10</f>
+        <v/>
+      </c>
+      <c r="L104" s="15">
+        <f>L103+K104</f>
+        <v/>
+      </c>
+      <c r="M104" s="15">
+        <f>B104+E104-F104-I104-J104</f>
+        <v/>
+      </c>
+      <c r="N104" s="15">
+        <f>M104-L104</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="B105" s="15">
+        <f>M104</f>
+        <v/>
+      </c>
+      <c r="C105" s="15">
+        <f>MIN(B105, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D105" s="15">
+        <f>MAX(B105-C105, 0)</f>
+        <v/>
+      </c>
+      <c r="E105" s="15">
+        <f>C105*$B$6 + D105*$B$14</f>
+        <v/>
+      </c>
+      <c r="F105" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G105" s="15">
+        <f>IF($B$7&gt;0, MIN(1*$B$9, $B$11*MAX(E105-F105, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H105" s="15">
+        <f>MAX(E105-F105-G105, 0)</f>
+        <v/>
+      </c>
+      <c r="I105" s="15">
+        <f>H105*$B$7</f>
+        <v/>
+      </c>
+      <c r="J105" s="15">
+        <f>G105*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K105" s="15">
+        <f>G105*$B$10</f>
+        <v/>
+      </c>
+      <c r="L105" s="15">
+        <f>L104+K105</f>
+        <v/>
+      </c>
+      <c r="M105" s="15">
+        <f>B105+E105-F105-I105-J105</f>
+        <v/>
+      </c>
+      <c r="N105" s="15">
+        <f>M105-L105</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B106" s="15">
+        <f>M105</f>
+        <v/>
+      </c>
+      <c r="C106" s="15">
+        <f>MIN(B106, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D106" s="15">
+        <f>MAX(B106-C106, 0)</f>
+        <v/>
+      </c>
+      <c r="E106" s="15">
+        <f>C106*$B$6 + D106*$B$14</f>
+        <v/>
+      </c>
+      <c r="F106" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G106" s="15">
+        <f>IF($B$7&gt;0, MIN(1*$B$9, $B$11*MAX(E106-F106, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H106" s="15">
+        <f>MAX(E106-F106-G106, 0)</f>
+        <v/>
+      </c>
+      <c r="I106" s="15">
+        <f>H106*$B$7</f>
+        <v/>
+      </c>
+      <c r="J106" s="15">
+        <f>G106*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K106" s="15">
+        <f>G106*$B$10</f>
+        <v/>
+      </c>
+      <c r="L106" s="15">
+        <f>L105+K106</f>
+        <v/>
+      </c>
+      <c r="M106" s="15">
+        <f>B106+E106-F106-I106-J106</f>
+        <v/>
+      </c>
+      <c r="N106" s="15">
+        <f>M106-L106</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="B107" s="15">
+        <f>M106</f>
+        <v/>
+      </c>
+      <c r="C107" s="15">
+        <f>MIN(B107, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D107" s="15">
+        <f>MAX(B107-C107, 0)</f>
+        <v/>
+      </c>
+      <c r="E107" s="15">
+        <f>C107*$B$6 + D107*$B$14</f>
+        <v/>
+      </c>
+      <c r="F107" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G107" s="15">
+        <f>IF($B$7&gt;0, MIN(1*$B$9, $B$11*MAX(E107-F107, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H107" s="15">
+        <f>MAX(E107-F107-G107, 0)</f>
+        <v/>
+      </c>
+      <c r="I107" s="15">
+        <f>H107*$B$7</f>
+        <v/>
+      </c>
+      <c r="J107" s="15">
+        <f>G107*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K107" s="15">
+        <f>G107*$B$10</f>
+        <v/>
+      </c>
+      <c r="L107" s="15">
+        <f>L106+K107</f>
+        <v/>
+      </c>
+      <c r="M107" s="15">
+        <f>B107+E107-F107-I107-J107</f>
+        <v/>
+      </c>
+      <c r="N107" s="15">
+        <f>M107-L107</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="B108" s="15">
+        <f>M107</f>
+        <v/>
+      </c>
+      <c r="C108" s="15">
+        <f>MIN(B108, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D108" s="15">
+        <f>MAX(B108-C108, 0)</f>
+        <v/>
+      </c>
+      <c r="E108" s="15">
+        <f>C108*$B$6 + D108*$B$14</f>
+        <v/>
+      </c>
+      <c r="F108" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G108" s="15">
+        <f>IF($B$7&gt;0, MIN(1*$B$9, $B$11*MAX(E108-F108, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H108" s="15">
+        <f>MAX(E108-F108-G108, 0)</f>
+        <v/>
+      </c>
+      <c r="I108" s="15">
+        <f>H108*$B$7</f>
+        <v/>
+      </c>
+      <c r="J108" s="15">
+        <f>G108*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K108" s="15">
+        <f>G108*$B$10</f>
+        <v/>
+      </c>
+      <c r="L108" s="15">
+        <f>L107+K108</f>
+        <v/>
+      </c>
+      <c r="M108" s="15">
+        <f>B108+E108-F108-I108-J108</f>
+        <v/>
+      </c>
+      <c r="N108" s="15">
+        <f>M108-L108</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="B109" s="15">
+        <f>M108</f>
+        <v/>
+      </c>
+      <c r="C109" s="15">
+        <f>MIN(B109, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D109" s="15">
+        <f>MAX(B109-C109, 0)</f>
+        <v/>
+      </c>
+      <c r="E109" s="15">
+        <f>C109*$B$6 + D109*$B$14</f>
+        <v/>
+      </c>
+      <c r="F109" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G109" s="15">
+        <f>IF($B$7&gt;0, MIN(1*$B$9, $B$11*MAX(E109-F109, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H109" s="15">
+        <f>MAX(E109-F109-G109, 0)</f>
+        <v/>
+      </c>
+      <c r="I109" s="15">
+        <f>H109*$B$7</f>
+        <v/>
+      </c>
+      <c r="J109" s="15">
+        <f>G109*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K109" s="15">
+        <f>G109*$B$10</f>
+        <v/>
+      </c>
+      <c r="L109" s="15">
+        <f>L108+K109</f>
+        <v/>
+      </c>
+      <c r="M109" s="15">
+        <f>B109+E109-F109-I109-J109</f>
+        <v/>
+      </c>
+      <c r="N109" s="15">
+        <f>M109-L109</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="B110" s="15">
+        <f>M109</f>
+        <v/>
+      </c>
+      <c r="C110" s="15">
+        <f>MIN(B110, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D110" s="15">
+        <f>MAX(B110-C110, 0)</f>
+        <v/>
+      </c>
+      <c r="E110" s="15">
+        <f>C110*$B$6 + D110*$B$14</f>
+        <v/>
+      </c>
+      <c r="F110" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G110" s="15">
+        <f>IF($B$7&gt;0, MIN(1*$B$9, $B$11*MAX(E110-F110, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H110" s="15">
+        <f>MAX(E110-F110-G110, 0)</f>
+        <v/>
+      </c>
+      <c r="I110" s="15">
+        <f>H110*$B$7</f>
+        <v/>
+      </c>
+      <c r="J110" s="15">
+        <f>G110*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K110" s="15">
+        <f>G110*$B$10</f>
+        <v/>
+      </c>
+      <c r="L110" s="15">
+        <f>L109+K110</f>
+        <v/>
+      </c>
+      <c r="M110" s="15">
+        <f>B110+E110-F110-I110-J110</f>
+        <v/>
+      </c>
+      <c r="N110" s="15">
+        <f>M110-L110</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B111" s="15">
+        <f>M110</f>
+        <v/>
+      </c>
+      <c r="C111" s="15">
+        <f>MIN(B111, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D111" s="15">
+        <f>MAX(B111-C111, 0)</f>
+        <v/>
+      </c>
+      <c r="E111" s="15">
+        <f>C111*$B$6 + D111*$B$14</f>
+        <v/>
+      </c>
+      <c r="F111" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G111" s="15">
+        <f>IF($B$7&gt;0, MIN(1*$B$9, $B$11*MAX(E111-F111, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H111" s="15">
+        <f>MAX(E111-F111-G111, 0)</f>
+        <v/>
+      </c>
+      <c r="I111" s="15">
+        <f>H111*$B$7</f>
+        <v/>
+      </c>
+      <c r="J111" s="15">
+        <f>G111*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K111" s="15">
+        <f>G111*$B$10</f>
+        <v/>
+      </c>
+      <c r="L111" s="15">
+        <f>L110+K111</f>
+        <v/>
+      </c>
+      <c r="M111" s="15">
+        <f>B111+E111-F111-I111-J111</f>
+        <v/>
+      </c>
+      <c r="N111" s="15">
+        <f>M111-L111</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="B112" s="15">
+        <f>M111</f>
+        <v/>
+      </c>
+      <c r="C112" s="15">
+        <f>MIN(B112, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D112" s="15">
+        <f>MAX(B112-C112, 0)</f>
+        <v/>
+      </c>
+      <c r="E112" s="15">
+        <f>C112*$B$6 + D112*$B$14</f>
+        <v/>
+      </c>
+      <c r="F112" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G112" s="15">
+        <f>IF($B$7&gt;0, MIN(1*$B$9, $B$11*MAX(E112-F112, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H112" s="15">
+        <f>MAX(E112-F112-G112, 0)</f>
+        <v/>
+      </c>
+      <c r="I112" s="15">
+        <f>H112*$B$7</f>
+        <v/>
+      </c>
+      <c r="J112" s="15">
+        <f>G112*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K112" s="15">
+        <f>G112*$B$10</f>
+        <v/>
+      </c>
+      <c r="L112" s="15">
+        <f>L111+K112</f>
+        <v/>
+      </c>
+      <c r="M112" s="15">
+        <f>B112+E112-F112-I112-J112</f>
+        <v/>
+      </c>
+      <c r="N112" s="15">
+        <f>M112-L112</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B113" s="15">
+        <f>M112</f>
+        <v/>
+      </c>
+      <c r="C113" s="15">
+        <f>MIN(B113, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D113" s="15">
+        <f>MAX(B113-C113, 0)</f>
+        <v/>
+      </c>
+      <c r="E113" s="15">
+        <f>C113*$B$6 + D113*$B$14</f>
+        <v/>
+      </c>
+      <c r="F113" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G113" s="15">
+        <f>IF($B$7&gt;0, MIN(1*$B$9, $B$11*MAX(E113-F113, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H113" s="15">
+        <f>MAX(E113-F113-G113, 0)</f>
+        <v/>
+      </c>
+      <c r="I113" s="15">
+        <f>H113*$B$7</f>
+        <v/>
+      </c>
+      <c r="J113" s="15">
+        <f>G113*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K113" s="15">
+        <f>G113*$B$10</f>
+        <v/>
+      </c>
+      <c r="L113" s="15">
+        <f>L112+K113</f>
+        <v/>
+      </c>
+      <c r="M113" s="15">
+        <f>B113+E113-F113-I113-J113</f>
+        <v/>
+      </c>
+      <c r="N113" s="15">
+        <f>M113-L113</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B114" s="15">
+        <f>M113</f>
+        <v/>
+      </c>
+      <c r="C114" s="15">
+        <f>MIN(B114, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D114" s="15">
+        <f>MAX(B114-C114, 0)</f>
+        <v/>
+      </c>
+      <c r="E114" s="15">
+        <f>C114*$B$6 + D114*$B$14</f>
+        <v/>
+      </c>
+      <c r="F114" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G114" s="15">
+        <f>IF($B$7&gt;0, MIN(1*$B$9, $B$11*MAX(E114-F114, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H114" s="15">
+        <f>MAX(E114-F114-G114, 0)</f>
+        <v/>
+      </c>
+      <c r="I114" s="15">
+        <f>H114*$B$7</f>
+        <v/>
+      </c>
+      <c r="J114" s="15">
+        <f>G114*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K114" s="15">
+        <f>G114*$B$10</f>
+        <v/>
+      </c>
+      <c r="L114" s="15">
+        <f>L113+K114</f>
+        <v/>
+      </c>
+      <c r="M114" s="15">
+        <f>B114+E114-F114-I114-J114</f>
+        <v/>
+      </c>
+      <c r="N114" s="15">
+        <f>M114-L114</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B115" s="15">
+        <f>M114</f>
+        <v/>
+      </c>
+      <c r="C115" s="15">
+        <f>MIN(B115, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D115" s="15">
+        <f>MAX(B115-C115, 0)</f>
+        <v/>
+      </c>
+      <c r="E115" s="15">
+        <f>C115*$B$6 + D115*$B$14</f>
+        <v/>
+      </c>
+      <c r="F115" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G115" s="15">
+        <f>IF($B$7&gt;0, MIN(1*$B$9, $B$11*MAX(E115-F115, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H115" s="15">
+        <f>MAX(E115-F115-G115, 0)</f>
+        <v/>
+      </c>
+      <c r="I115" s="15">
+        <f>H115*$B$7</f>
+        <v/>
+      </c>
+      <c r="J115" s="15">
+        <f>G115*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K115" s="15">
+        <f>G115*$B$10</f>
+        <v/>
+      </c>
+      <c r="L115" s="15">
+        <f>L114+K115</f>
+        <v/>
+      </c>
+      <c r="M115" s="15">
+        <f>B115+E115-F115-I115-J115</f>
+        <v/>
+      </c>
+      <c r="N115" s="15">
+        <f>M115-L115</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="B116" s="15">
+        <f>M115</f>
+        <v/>
+      </c>
+      <c r="C116" s="15">
+        <f>MIN(B116, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D116" s="15">
+        <f>MAX(B116-C116, 0)</f>
+        <v/>
+      </c>
+      <c r="E116" s="15">
+        <f>C116*$B$6 + D116*$B$14</f>
+        <v/>
+      </c>
+      <c r="F116" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G116" s="15">
+        <f>IF($B$7&gt;0, MIN(1*$B$9, $B$11*MAX(E116-F116, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H116" s="15">
+        <f>MAX(E116-F116-G116, 0)</f>
+        <v/>
+      </c>
+      <c r="I116" s="15">
+        <f>H116*$B$7</f>
+        <v/>
+      </c>
+      <c r="J116" s="15">
+        <f>G116*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K116" s="15">
+        <f>G116*$B$10</f>
+        <v/>
+      </c>
+      <c r="L116" s="15">
+        <f>L115+K116</f>
+        <v/>
+      </c>
+      <c r="M116" s="15">
+        <f>B116+E116-F116-I116-J116</f>
+        <v/>
+      </c>
+      <c r="N116" s="15">
+        <f>M116-L116</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>COMPANY + 2 EMPLOYEES ROUTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="19" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B120" s="19" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="C120" s="19" t="inlineStr">
+        <is>
+          <t>Deployed</t>
+        </is>
+      </c>
+      <c r="D120" s="19" t="inlineStr">
+        <is>
+          <t>Idle</t>
+        </is>
+      </c>
+      <c r="E120" s="19" t="inlineStr">
+        <is>
+          <t>Profit</t>
+        </is>
+      </c>
+      <c r="F120" s="19" t="inlineStr">
+        <is>
+          <t>Overhead</t>
+        </is>
+      </c>
+      <c r="G120" s="19" t="inlineStr">
+        <is>
+          <t>Salary Paid</t>
+        </is>
+      </c>
+      <c r="H120" s="19" t="inlineStr">
+        <is>
+          <t>Taxable Profit</t>
+        </is>
+      </c>
+      <c r="I120" s="19" t="inlineStr">
+        <is>
+          <t>Income Tax</t>
+        </is>
+      </c>
+      <c r="J120" s="19" t="inlineStr">
+        <is>
+          <t>Not Lent Back</t>
+        </is>
+      </c>
+      <c r="K120" s="19" t="inlineStr">
+        <is>
+          <t>New Loan</t>
+        </is>
+      </c>
+      <c r="L120" s="19" t="inlineStr">
+        <is>
+          <t>Loans Outstanding</t>
+        </is>
+      </c>
+      <c r="M120" s="19" t="inlineStr">
+        <is>
+          <t>Closing Capital</t>
+        </is>
+      </c>
+      <c r="N120" s="19" t="inlineStr">
+        <is>
+          <t>Net Equity (Closing - Loans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="B121" s="15">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="C121" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="15">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="N121" s="15">
+        <f>$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B122" s="15">
+        <f>M121</f>
+        <v/>
+      </c>
+      <c r="C122" s="15">
+        <f>MIN(B122, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D122" s="15">
+        <f>MAX(B122-C122, 0)</f>
+        <v/>
+      </c>
+      <c r="E122" s="15">
+        <f>C122*$B$6 + D122*$B$14</f>
+        <v/>
+      </c>
+      <c r="F122" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G122" s="15">
+        <f>IF($B$7&gt;0, MIN(2*$B$9, $B$11*MAX(E122-F122, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H122" s="15">
+        <f>MAX(E122-F122-G122, 0)</f>
+        <v/>
+      </c>
+      <c r="I122" s="15">
+        <f>H122*$B$7</f>
+        <v/>
+      </c>
+      <c r="J122" s="15">
+        <f>G122*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K122" s="15">
+        <f>G122*$B$10</f>
+        <v/>
+      </c>
+      <c r="L122" s="15">
+        <f>L121+K122</f>
+        <v/>
+      </c>
+      <c r="M122" s="15">
+        <f>B122+E122-F122-I122-J122</f>
+        <v/>
+      </c>
+      <c r="N122" s="15">
+        <f>M122-L122</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B123" s="15">
+        <f>M122</f>
+        <v/>
+      </c>
+      <c r="C123" s="15">
+        <f>MIN(B123, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D123" s="15">
+        <f>MAX(B123-C123, 0)</f>
+        <v/>
+      </c>
+      <c r="E123" s="15">
+        <f>C123*$B$6 + D123*$B$14</f>
+        <v/>
+      </c>
+      <c r="F123" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G123" s="15">
+        <f>IF($B$7&gt;0, MIN(2*$B$9, $B$11*MAX(E123-F123, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H123" s="15">
+        <f>MAX(E123-F123-G123, 0)</f>
+        <v/>
+      </c>
+      <c r="I123" s="15">
+        <f>H123*$B$7</f>
+        <v/>
+      </c>
+      <c r="J123" s="15">
+        <f>G123*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K123" s="15">
+        <f>G123*$B$10</f>
+        <v/>
+      </c>
+      <c r="L123" s="15">
+        <f>L122+K123</f>
+        <v/>
+      </c>
+      <c r="M123" s="15">
+        <f>B123+E123-F123-I123-J123</f>
+        <v/>
+      </c>
+      <c r="N123" s="15">
+        <f>M123-L123</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B124" s="15">
+        <f>M123</f>
+        <v/>
+      </c>
+      <c r="C124" s="15">
+        <f>MIN(B124, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D124" s="15">
+        <f>MAX(B124-C124, 0)</f>
+        <v/>
+      </c>
+      <c r="E124" s="15">
+        <f>C124*$B$6 + D124*$B$14</f>
+        <v/>
+      </c>
+      <c r="F124" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G124" s="15">
+        <f>IF($B$7&gt;0, MIN(2*$B$9, $B$11*MAX(E124-F124, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H124" s="15">
+        <f>MAX(E124-F124-G124, 0)</f>
+        <v/>
+      </c>
+      <c r="I124" s="15">
+        <f>H124*$B$7</f>
+        <v/>
+      </c>
+      <c r="J124" s="15">
+        <f>G124*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K124" s="15">
+        <f>G124*$B$10</f>
+        <v/>
+      </c>
+      <c r="L124" s="15">
+        <f>L123+K124</f>
+        <v/>
+      </c>
+      <c r="M124" s="15">
+        <f>B124+E124-F124-I124-J124</f>
+        <v/>
+      </c>
+      <c r="N124" s="15">
+        <f>M124-L124</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B125" s="15">
+        <f>M124</f>
+        <v/>
+      </c>
+      <c r="C125" s="15">
+        <f>MIN(B125, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D125" s="15">
+        <f>MAX(B125-C125, 0)</f>
+        <v/>
+      </c>
+      <c r="E125" s="15">
+        <f>C125*$B$6 + D125*$B$14</f>
+        <v/>
+      </c>
+      <c r="F125" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G125" s="15">
+        <f>IF($B$7&gt;0, MIN(2*$B$9, $B$11*MAX(E125-F125, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H125" s="15">
+        <f>MAX(E125-F125-G125, 0)</f>
+        <v/>
+      </c>
+      <c r="I125" s="15">
+        <f>H125*$B$7</f>
+        <v/>
+      </c>
+      <c r="J125" s="15">
+        <f>G125*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K125" s="15">
+        <f>G125*$B$10</f>
+        <v/>
+      </c>
+      <c r="L125" s="15">
+        <f>L124+K125</f>
+        <v/>
+      </c>
+      <c r="M125" s="15">
+        <f>B125+E125-F125-I125-J125</f>
+        <v/>
+      </c>
+      <c r="N125" s="15">
+        <f>M125-L125</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B126" s="15">
+        <f>M125</f>
+        <v/>
+      </c>
+      <c r="C126" s="15">
+        <f>MIN(B126, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D126" s="15">
+        <f>MAX(B126-C126, 0)</f>
+        <v/>
+      </c>
+      <c r="E126" s="15">
+        <f>C126*$B$6 + D126*$B$14</f>
+        <v/>
+      </c>
+      <c r="F126" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G126" s="15">
+        <f>IF($B$7&gt;0, MIN(2*$B$9, $B$11*MAX(E126-F126, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H126" s="15">
+        <f>MAX(E126-F126-G126, 0)</f>
+        <v/>
+      </c>
+      <c r="I126" s="15">
+        <f>H126*$B$7</f>
+        <v/>
+      </c>
+      <c r="J126" s="15">
+        <f>G126*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K126" s="15">
+        <f>G126*$B$10</f>
+        <v/>
+      </c>
+      <c r="L126" s="15">
+        <f>L125+K126</f>
+        <v/>
+      </c>
+      <c r="M126" s="15">
+        <f>B126+E126-F126-I126-J126</f>
+        <v/>
+      </c>
+      <c r="N126" s="15">
+        <f>M126-L126</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B127" s="15">
+        <f>M126</f>
+        <v/>
+      </c>
+      <c r="C127" s="15">
+        <f>MIN(B127, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D127" s="15">
+        <f>MAX(B127-C127, 0)</f>
+        <v/>
+      </c>
+      <c r="E127" s="15">
+        <f>C127*$B$6 + D127*$B$14</f>
+        <v/>
+      </c>
+      <c r="F127" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G127" s="15">
+        <f>IF($B$7&gt;0, MIN(2*$B$9, $B$11*MAX(E127-F127, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H127" s="15">
+        <f>MAX(E127-F127-G127, 0)</f>
+        <v/>
+      </c>
+      <c r="I127" s="15">
+        <f>H127*$B$7</f>
+        <v/>
+      </c>
+      <c r="J127" s="15">
+        <f>G127*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K127" s="15">
+        <f>G127*$B$10</f>
+        <v/>
+      </c>
+      <c r="L127" s="15">
+        <f>L126+K127</f>
+        <v/>
+      </c>
+      <c r="M127" s="15">
+        <f>B127+E127-F127-I127-J127</f>
+        <v/>
+      </c>
+      <c r="N127" s="15">
+        <f>M127-L127</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B128" s="15">
+        <f>M127</f>
+        <v/>
+      </c>
+      <c r="C128" s="15">
+        <f>MIN(B128, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D128" s="15">
+        <f>MAX(B128-C128, 0)</f>
+        <v/>
+      </c>
+      <c r="E128" s="15">
+        <f>C128*$B$6 + D128*$B$14</f>
+        <v/>
+      </c>
+      <c r="F128" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G128" s="15">
+        <f>IF($B$7&gt;0, MIN(2*$B$9, $B$11*MAX(E128-F128, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H128" s="15">
+        <f>MAX(E128-F128-G128, 0)</f>
+        <v/>
+      </c>
+      <c r="I128" s="15">
+        <f>H128*$B$7</f>
+        <v/>
+      </c>
+      <c r="J128" s="15">
+        <f>G128*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K128" s="15">
+        <f>G128*$B$10</f>
+        <v/>
+      </c>
+      <c r="L128" s="15">
+        <f>L127+K128</f>
+        <v/>
+      </c>
+      <c r="M128" s="15">
+        <f>B128+E128-F128-I128-J128</f>
+        <v/>
+      </c>
+      <c r="N128" s="15">
+        <f>M128-L128</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B129" s="15">
+        <f>M128</f>
+        <v/>
+      </c>
+      <c r="C129" s="15">
+        <f>MIN(B129, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D129" s="15">
+        <f>MAX(B129-C129, 0)</f>
+        <v/>
+      </c>
+      <c r="E129" s="15">
+        <f>C129*$B$6 + D129*$B$14</f>
+        <v/>
+      </c>
+      <c r="F129" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G129" s="15">
+        <f>IF($B$7&gt;0, MIN(2*$B$9, $B$11*MAX(E129-F129, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H129" s="15">
+        <f>MAX(E129-F129-G129, 0)</f>
+        <v/>
+      </c>
+      <c r="I129" s="15">
+        <f>H129*$B$7</f>
+        <v/>
+      </c>
+      <c r="J129" s="15">
+        <f>G129*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K129" s="15">
+        <f>G129*$B$10</f>
+        <v/>
+      </c>
+      <c r="L129" s="15">
+        <f>L128+K129</f>
+        <v/>
+      </c>
+      <c r="M129" s="15">
+        <f>B129+E129-F129-I129-J129</f>
+        <v/>
+      </c>
+      <c r="N129" s="15">
+        <f>M129-L129</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="B130" s="15">
+        <f>M129</f>
+        <v/>
+      </c>
+      <c r="C130" s="15">
+        <f>MIN(B130, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D130" s="15">
+        <f>MAX(B130-C130, 0)</f>
+        <v/>
+      </c>
+      <c r="E130" s="15">
+        <f>C130*$B$6 + D130*$B$14</f>
+        <v/>
+      </c>
+      <c r="F130" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G130" s="15">
+        <f>IF($B$7&gt;0, MIN(2*$B$9, $B$11*MAX(E130-F130, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H130" s="15">
+        <f>MAX(E130-F130-G130, 0)</f>
+        <v/>
+      </c>
+      <c r="I130" s="15">
+        <f>H130*$B$7</f>
+        <v/>
+      </c>
+      <c r="J130" s="15">
+        <f>G130*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K130" s="15">
+        <f>G130*$B$10</f>
+        <v/>
+      </c>
+      <c r="L130" s="15">
+        <f>L129+K130</f>
+        <v/>
+      </c>
+      <c r="M130" s="15">
+        <f>B130+E130-F130-I130-J130</f>
+        <v/>
+      </c>
+      <c r="N130" s="15">
+        <f>M130-L130</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B131" s="15">
+        <f>M130</f>
+        <v/>
+      </c>
+      <c r="C131" s="15">
+        <f>MIN(B131, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D131" s="15">
+        <f>MAX(B131-C131, 0)</f>
+        <v/>
+      </c>
+      <c r="E131" s="15">
+        <f>C131*$B$6 + D131*$B$14</f>
+        <v/>
+      </c>
+      <c r="F131" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G131" s="15">
+        <f>IF($B$7&gt;0, MIN(2*$B$9, $B$11*MAX(E131-F131, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H131" s="15">
+        <f>MAX(E131-F131-G131, 0)</f>
+        <v/>
+      </c>
+      <c r="I131" s="15">
+        <f>H131*$B$7</f>
+        <v/>
+      </c>
+      <c r="J131" s="15">
+        <f>G131*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K131" s="15">
+        <f>G131*$B$10</f>
+        <v/>
+      </c>
+      <c r="L131" s="15">
+        <f>L130+K131</f>
+        <v/>
+      </c>
+      <c r="M131" s="15">
+        <f>B131+E131-F131-I131-J131</f>
+        <v/>
+      </c>
+      <c r="N131" s="15">
+        <f>M131-L131</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="B132" s="15">
+        <f>M131</f>
+        <v/>
+      </c>
+      <c r="C132" s="15">
+        <f>MIN(B132, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D132" s="15">
+        <f>MAX(B132-C132, 0)</f>
+        <v/>
+      </c>
+      <c r="E132" s="15">
+        <f>C132*$B$6 + D132*$B$14</f>
+        <v/>
+      </c>
+      <c r="F132" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G132" s="15">
+        <f>IF($B$7&gt;0, MIN(2*$B$9, $B$11*MAX(E132-F132, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H132" s="15">
+        <f>MAX(E132-F132-G132, 0)</f>
+        <v/>
+      </c>
+      <c r="I132" s="15">
+        <f>H132*$B$7</f>
+        <v/>
+      </c>
+      <c r="J132" s="15">
+        <f>G132*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K132" s="15">
+        <f>G132*$B$10</f>
+        <v/>
+      </c>
+      <c r="L132" s="15">
+        <f>L131+K132</f>
+        <v/>
+      </c>
+      <c r="M132" s="15">
+        <f>B132+E132-F132-I132-J132</f>
+        <v/>
+      </c>
+      <c r="N132" s="15">
+        <f>M132-L132</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="B133" s="15">
+        <f>M132</f>
+        <v/>
+      </c>
+      <c r="C133" s="15">
+        <f>MIN(B133, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D133" s="15">
+        <f>MAX(B133-C133, 0)</f>
+        <v/>
+      </c>
+      <c r="E133" s="15">
+        <f>C133*$B$6 + D133*$B$14</f>
+        <v/>
+      </c>
+      <c r="F133" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G133" s="15">
+        <f>IF($B$7&gt;0, MIN(2*$B$9, $B$11*MAX(E133-F133, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H133" s="15">
+        <f>MAX(E133-F133-G133, 0)</f>
+        <v/>
+      </c>
+      <c r="I133" s="15">
+        <f>H133*$B$7</f>
+        <v/>
+      </c>
+      <c r="J133" s="15">
+        <f>G133*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K133" s="15">
+        <f>G133*$B$10</f>
+        <v/>
+      </c>
+      <c r="L133" s="15">
+        <f>L132+K133</f>
+        <v/>
+      </c>
+      <c r="M133" s="15">
+        <f>B133+E133-F133-I133-J133</f>
+        <v/>
+      </c>
+      <c r="N133" s="15">
+        <f>M133-L133</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="B134" s="15">
+        <f>M133</f>
+        <v/>
+      </c>
+      <c r="C134" s="15">
+        <f>MIN(B134, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D134" s="15">
+        <f>MAX(B134-C134, 0)</f>
+        <v/>
+      </c>
+      <c r="E134" s="15">
+        <f>C134*$B$6 + D134*$B$14</f>
+        <v/>
+      </c>
+      <c r="F134" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G134" s="15">
+        <f>IF($B$7&gt;0, MIN(2*$B$9, $B$11*MAX(E134-F134, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H134" s="15">
+        <f>MAX(E134-F134-G134, 0)</f>
+        <v/>
+      </c>
+      <c r="I134" s="15">
+        <f>H134*$B$7</f>
+        <v/>
+      </c>
+      <c r="J134" s="15">
+        <f>G134*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K134" s="15">
+        <f>G134*$B$10</f>
+        <v/>
+      </c>
+      <c r="L134" s="15">
+        <f>L133+K134</f>
+        <v/>
+      </c>
+      <c r="M134" s="15">
+        <f>B134+E134-F134-I134-J134</f>
+        <v/>
+      </c>
+      <c r="N134" s="15">
+        <f>M134-L134</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="B135" s="15">
+        <f>M134</f>
+        <v/>
+      </c>
+      <c r="C135" s="15">
+        <f>MIN(B135, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D135" s="15">
+        <f>MAX(B135-C135, 0)</f>
+        <v/>
+      </c>
+      <c r="E135" s="15">
+        <f>C135*$B$6 + D135*$B$14</f>
+        <v/>
+      </c>
+      <c r="F135" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G135" s="15">
+        <f>IF($B$7&gt;0, MIN(2*$B$9, $B$11*MAX(E135-F135, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H135" s="15">
+        <f>MAX(E135-F135-G135, 0)</f>
+        <v/>
+      </c>
+      <c r="I135" s="15">
+        <f>H135*$B$7</f>
+        <v/>
+      </c>
+      <c r="J135" s="15">
+        <f>G135*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K135" s="15">
+        <f>G135*$B$10</f>
+        <v/>
+      </c>
+      <c r="L135" s="15">
+        <f>L134+K135</f>
+        <v/>
+      </c>
+      <c r="M135" s="15">
+        <f>B135+E135-F135-I135-J135</f>
+        <v/>
+      </c>
+      <c r="N135" s="15">
+        <f>M135-L135</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B136" s="15">
+        <f>M135</f>
+        <v/>
+      </c>
+      <c r="C136" s="15">
+        <f>MIN(B136, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D136" s="15">
+        <f>MAX(B136-C136, 0)</f>
+        <v/>
+      </c>
+      <c r="E136" s="15">
+        <f>C136*$B$6 + D136*$B$14</f>
+        <v/>
+      </c>
+      <c r="F136" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G136" s="15">
+        <f>IF($B$7&gt;0, MIN(2*$B$9, $B$11*MAX(E136-F136, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H136" s="15">
+        <f>MAX(E136-F136-G136, 0)</f>
+        <v/>
+      </c>
+      <c r="I136" s="15">
+        <f>H136*$B$7</f>
+        <v/>
+      </c>
+      <c r="J136" s="15">
+        <f>G136*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K136" s="15">
+        <f>G136*$B$10</f>
+        <v/>
+      </c>
+      <c r="L136" s="15">
+        <f>L135+K136</f>
+        <v/>
+      </c>
+      <c r="M136" s="15">
+        <f>B136+E136-F136-I136-J136</f>
+        <v/>
+      </c>
+      <c r="N136" s="15">
+        <f>M136-L136</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="B137" s="15">
+        <f>M136</f>
+        <v/>
+      </c>
+      <c r="C137" s="15">
+        <f>MIN(B137, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D137" s="15">
+        <f>MAX(B137-C137, 0)</f>
+        <v/>
+      </c>
+      <c r="E137" s="15">
+        <f>C137*$B$6 + D137*$B$14</f>
+        <v/>
+      </c>
+      <c r="F137" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G137" s="15">
+        <f>IF($B$7&gt;0, MIN(2*$B$9, $B$11*MAX(E137-F137, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H137" s="15">
+        <f>MAX(E137-F137-G137, 0)</f>
+        <v/>
+      </c>
+      <c r="I137" s="15">
+        <f>H137*$B$7</f>
+        <v/>
+      </c>
+      <c r="J137" s="15">
+        <f>G137*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K137" s="15">
+        <f>G137*$B$10</f>
+        <v/>
+      </c>
+      <c r="L137" s="15">
+        <f>L136+K137</f>
+        <v/>
+      </c>
+      <c r="M137" s="15">
+        <f>B137+E137-F137-I137-J137</f>
+        <v/>
+      </c>
+      <c r="N137" s="15">
+        <f>M137-L137</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B138" s="15">
+        <f>M137</f>
+        <v/>
+      </c>
+      <c r="C138" s="15">
+        <f>MIN(B138, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D138" s="15">
+        <f>MAX(B138-C138, 0)</f>
+        <v/>
+      </c>
+      <c r="E138" s="15">
+        <f>C138*$B$6 + D138*$B$14</f>
+        <v/>
+      </c>
+      <c r="F138" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G138" s="15">
+        <f>IF($B$7&gt;0, MIN(2*$B$9, $B$11*MAX(E138-F138, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H138" s="15">
+        <f>MAX(E138-F138-G138, 0)</f>
+        <v/>
+      </c>
+      <c r="I138" s="15">
+        <f>H138*$B$7</f>
+        <v/>
+      </c>
+      <c r="J138" s="15">
+        <f>G138*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K138" s="15">
+        <f>G138*$B$10</f>
+        <v/>
+      </c>
+      <c r="L138" s="15">
+        <f>L137+K138</f>
+        <v/>
+      </c>
+      <c r="M138" s="15">
+        <f>B138+E138-F138-I138-J138</f>
+        <v/>
+      </c>
+      <c r="N138" s="15">
+        <f>M138-L138</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B139" s="15">
+        <f>M138</f>
+        <v/>
+      </c>
+      <c r="C139" s="15">
+        <f>MIN(B139, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D139" s="15">
+        <f>MAX(B139-C139, 0)</f>
+        <v/>
+      </c>
+      <c r="E139" s="15">
+        <f>C139*$B$6 + D139*$B$14</f>
+        <v/>
+      </c>
+      <c r="F139" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G139" s="15">
+        <f>IF($B$7&gt;0, MIN(2*$B$9, $B$11*MAX(E139-F139, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H139" s="15">
+        <f>MAX(E139-F139-G139, 0)</f>
+        <v/>
+      </c>
+      <c r="I139" s="15">
+        <f>H139*$B$7</f>
+        <v/>
+      </c>
+      <c r="J139" s="15">
+        <f>G139*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K139" s="15">
+        <f>G139*$B$10</f>
+        <v/>
+      </c>
+      <c r="L139" s="15">
+        <f>L138+K139</f>
+        <v/>
+      </c>
+      <c r="M139" s="15">
+        <f>B139+E139-F139-I139-J139</f>
+        <v/>
+      </c>
+      <c r="N139" s="15">
+        <f>M139-L139</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B140" s="15">
+        <f>M139</f>
+        <v/>
+      </c>
+      <c r="C140" s="15">
+        <f>MIN(B140, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D140" s="15">
+        <f>MAX(B140-C140, 0)</f>
+        <v/>
+      </c>
+      <c r="E140" s="15">
+        <f>C140*$B$6 + D140*$B$14</f>
+        <v/>
+      </c>
+      <c r="F140" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G140" s="15">
+        <f>IF($B$7&gt;0, MIN(2*$B$9, $B$11*MAX(E140-F140, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H140" s="15">
+        <f>MAX(E140-F140-G140, 0)</f>
+        <v/>
+      </c>
+      <c r="I140" s="15">
+        <f>H140*$B$7</f>
+        <v/>
+      </c>
+      <c r="J140" s="15">
+        <f>G140*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K140" s="15">
+        <f>G140*$B$10</f>
+        <v/>
+      </c>
+      <c r="L140" s="15">
+        <f>L139+K140</f>
+        <v/>
+      </c>
+      <c r="M140" s="15">
+        <f>B140+E140-F140-I140-J140</f>
+        <v/>
+      </c>
+      <c r="N140" s="15">
+        <f>M140-L140</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="B141" s="15">
+        <f>M140</f>
+        <v/>
+      </c>
+      <c r="C141" s="15">
+        <f>MIN(B141, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D141" s="15">
+        <f>MAX(B141-C141, 0)</f>
+        <v/>
+      </c>
+      <c r="E141" s="15">
+        <f>C141*$B$6 + D141*$B$14</f>
+        <v/>
+      </c>
+      <c r="F141" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G141" s="15">
+        <f>IF($B$7&gt;0, MIN(2*$B$9, $B$11*MAX(E141-F141, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H141" s="15">
+        <f>MAX(E141-F141-G141, 0)</f>
+        <v/>
+      </c>
+      <c r="I141" s="15">
+        <f>H141*$B$7</f>
+        <v/>
+      </c>
+      <c r="J141" s="15">
+        <f>G141*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K141" s="15">
+        <f>G141*$B$10</f>
+        <v/>
+      </c>
+      <c r="L141" s="15">
+        <f>L140+K141</f>
+        <v/>
+      </c>
+      <c r="M141" s="15">
+        <f>B141+E141-F141-I141-J141</f>
+        <v/>
+      </c>
+      <c r="N141" s="15">
+        <f>M141-L141</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>COMPANY + 3 EMPLOYEES ROUTE (RECOMMENDED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="19" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B145" s="19" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="C145" s="19" t="inlineStr">
+        <is>
+          <t>Deployed</t>
+        </is>
+      </c>
+      <c r="D145" s="19" t="inlineStr">
+        <is>
+          <t>Idle</t>
+        </is>
+      </c>
+      <c r="E145" s="19" t="inlineStr">
+        <is>
+          <t>Profit</t>
+        </is>
+      </c>
+      <c r="F145" s="19" t="inlineStr">
+        <is>
+          <t>Overhead</t>
+        </is>
+      </c>
+      <c r="G145" s="19" t="inlineStr">
+        <is>
+          <t>Salary Paid</t>
+        </is>
+      </c>
+      <c r="H145" s="19" t="inlineStr">
+        <is>
+          <t>Taxable Profit</t>
+        </is>
+      </c>
+      <c r="I145" s="19" t="inlineStr">
+        <is>
+          <t>Income Tax</t>
+        </is>
+      </c>
+      <c r="J145" s="19" t="inlineStr">
+        <is>
+          <t>Not Lent Back</t>
+        </is>
+      </c>
+      <c r="K145" s="19" t="inlineStr">
+        <is>
+          <t>New Loan</t>
+        </is>
+      </c>
+      <c r="L145" s="19" t="inlineStr">
+        <is>
+          <t>Loans Outstanding</t>
+        </is>
+      </c>
+      <c r="M145" s="19" t="inlineStr">
+        <is>
+          <t>Closing Capital</t>
+        </is>
+      </c>
+      <c r="N145" s="19" t="inlineStr">
+        <is>
+          <t>Net Equity (Closing - Loans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="B146" s="15">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="C146" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="15">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="N146" s="15">
+        <f>$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B147" s="15">
+        <f>M146</f>
+        <v/>
+      </c>
+      <c r="C147" s="15">
+        <f>MIN(B147, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D147" s="15">
+        <f>MAX(B147-C147, 0)</f>
+        <v/>
+      </c>
+      <c r="E147" s="15">
+        <f>C147*$B$6 + D147*$B$14</f>
+        <v/>
+      </c>
+      <c r="F147" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G147" s="15">
+        <f>IF($B$7&gt;0, MIN(3*$B$9, $B$11*MAX(E147-F147, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H147" s="15">
+        <f>MAX(E147-F147-G147, 0)</f>
+        <v/>
+      </c>
+      <c r="I147" s="15">
+        <f>H147*$B$7</f>
+        <v/>
+      </c>
+      <c r="J147" s="15">
+        <f>G147*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K147" s="15">
+        <f>G147*$B$10</f>
+        <v/>
+      </c>
+      <c r="L147" s="15">
+        <f>L146+K147</f>
+        <v/>
+      </c>
+      <c r="M147" s="15">
+        <f>B147+E147-F147-I147-J147</f>
+        <v/>
+      </c>
+      <c r="N147" s="15">
+        <f>M147-L147</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B148" s="15">
+        <f>M147</f>
+        <v/>
+      </c>
+      <c r="C148" s="15">
+        <f>MIN(B148, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D148" s="15">
+        <f>MAX(B148-C148, 0)</f>
+        <v/>
+      </c>
+      <c r="E148" s="15">
+        <f>C148*$B$6 + D148*$B$14</f>
+        <v/>
+      </c>
+      <c r="F148" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G148" s="15">
+        <f>IF($B$7&gt;0, MIN(3*$B$9, $B$11*MAX(E148-F148, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H148" s="15">
+        <f>MAX(E148-F148-G148, 0)</f>
+        <v/>
+      </c>
+      <c r="I148" s="15">
+        <f>H148*$B$7</f>
+        <v/>
+      </c>
+      <c r="J148" s="15">
+        <f>G148*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K148" s="15">
+        <f>G148*$B$10</f>
+        <v/>
+      </c>
+      <c r="L148" s="15">
+        <f>L147+K148</f>
+        <v/>
+      </c>
+      <c r="M148" s="15">
+        <f>B148+E148-F148-I148-J148</f>
+        <v/>
+      </c>
+      <c r="N148" s="15">
+        <f>M148-L148</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B149" s="15">
+        <f>M148</f>
+        <v/>
+      </c>
+      <c r="C149" s="15">
+        <f>MIN(B149, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D149" s="15">
+        <f>MAX(B149-C149, 0)</f>
+        <v/>
+      </c>
+      <c r="E149" s="15">
+        <f>C149*$B$6 + D149*$B$14</f>
+        <v/>
+      </c>
+      <c r="F149" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G149" s="15">
+        <f>IF($B$7&gt;0, MIN(3*$B$9, $B$11*MAX(E149-F149, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H149" s="15">
+        <f>MAX(E149-F149-G149, 0)</f>
+        <v/>
+      </c>
+      <c r="I149" s="15">
+        <f>H149*$B$7</f>
+        <v/>
+      </c>
+      <c r="J149" s="15">
+        <f>G149*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K149" s="15">
+        <f>G149*$B$10</f>
+        <v/>
+      </c>
+      <c r="L149" s="15">
+        <f>L148+K149</f>
+        <v/>
+      </c>
+      <c r="M149" s="15">
+        <f>B149+E149-F149-I149-J149</f>
+        <v/>
+      </c>
+      <c r="N149" s="15">
+        <f>M149-L149</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B150" s="15">
+        <f>M149</f>
+        <v/>
+      </c>
+      <c r="C150" s="15">
+        <f>MIN(B150, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D150" s="15">
+        <f>MAX(B150-C150, 0)</f>
+        <v/>
+      </c>
+      <c r="E150" s="15">
+        <f>C150*$B$6 + D150*$B$14</f>
+        <v/>
+      </c>
+      <c r="F150" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G150" s="15">
+        <f>IF($B$7&gt;0, MIN(3*$B$9, $B$11*MAX(E150-F150, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H150" s="15">
+        <f>MAX(E150-F150-G150, 0)</f>
+        <v/>
+      </c>
+      <c r="I150" s="15">
+        <f>H150*$B$7</f>
+        <v/>
+      </c>
+      <c r="J150" s="15">
+        <f>G150*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K150" s="15">
+        <f>G150*$B$10</f>
+        <v/>
+      </c>
+      <c r="L150" s="15">
+        <f>L149+K150</f>
+        <v/>
+      </c>
+      <c r="M150" s="15">
+        <f>B150+E150-F150-I150-J150</f>
+        <v/>
+      </c>
+      <c r="N150" s="15">
+        <f>M150-L150</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B151" s="15">
+        <f>M150</f>
+        <v/>
+      </c>
+      <c r="C151" s="15">
+        <f>MIN(B151, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D151" s="15">
+        <f>MAX(B151-C151, 0)</f>
+        <v/>
+      </c>
+      <c r="E151" s="15">
+        <f>C151*$B$6 + D151*$B$14</f>
+        <v/>
+      </c>
+      <c r="F151" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G151" s="15">
+        <f>IF($B$7&gt;0, MIN(3*$B$9, $B$11*MAX(E151-F151, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H151" s="15">
+        <f>MAX(E151-F151-G151, 0)</f>
+        <v/>
+      </c>
+      <c r="I151" s="15">
+        <f>H151*$B$7</f>
+        <v/>
+      </c>
+      <c r="J151" s="15">
+        <f>G151*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K151" s="15">
+        <f>G151*$B$10</f>
+        <v/>
+      </c>
+      <c r="L151" s="15">
+        <f>L150+K151</f>
+        <v/>
+      </c>
+      <c r="M151" s="15">
+        <f>B151+E151-F151-I151-J151</f>
+        <v/>
+      </c>
+      <c r="N151" s="15">
+        <f>M151-L151</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B152" s="15">
+        <f>M151</f>
+        <v/>
+      </c>
+      <c r="C152" s="15">
+        <f>MIN(B152, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D152" s="15">
+        <f>MAX(B152-C152, 0)</f>
+        <v/>
+      </c>
+      <c r="E152" s="15">
+        <f>C152*$B$6 + D152*$B$14</f>
+        <v/>
+      </c>
+      <c r="F152" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G152" s="15">
+        <f>IF($B$7&gt;0, MIN(3*$B$9, $B$11*MAX(E152-F152, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H152" s="15">
+        <f>MAX(E152-F152-G152, 0)</f>
+        <v/>
+      </c>
+      <c r="I152" s="15">
+        <f>H152*$B$7</f>
+        <v/>
+      </c>
+      <c r="J152" s="15">
+        <f>G152*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K152" s="15">
+        <f>G152*$B$10</f>
+        <v/>
+      </c>
+      <c r="L152" s="15">
+        <f>L151+K152</f>
+        <v/>
+      </c>
+      <c r="M152" s="15">
+        <f>B152+E152-F152-I152-J152</f>
+        <v/>
+      </c>
+      <c r="N152" s="15">
+        <f>M152-L152</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B153" s="15">
+        <f>M152</f>
+        <v/>
+      </c>
+      <c r="C153" s="15">
+        <f>MIN(B153, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D153" s="15">
+        <f>MAX(B153-C153, 0)</f>
+        <v/>
+      </c>
+      <c r="E153" s="15">
+        <f>C153*$B$6 + D153*$B$14</f>
+        <v/>
+      </c>
+      <c r="F153" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G153" s="15">
+        <f>IF($B$7&gt;0, MIN(3*$B$9, $B$11*MAX(E153-F153, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H153" s="15">
+        <f>MAX(E153-F153-G153, 0)</f>
+        <v/>
+      </c>
+      <c r="I153" s="15">
+        <f>H153*$B$7</f>
+        <v/>
+      </c>
+      <c r="J153" s="15">
+        <f>G153*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K153" s="15">
+        <f>G153*$B$10</f>
+        <v/>
+      </c>
+      <c r="L153" s="15">
+        <f>L152+K153</f>
+        <v/>
+      </c>
+      <c r="M153" s="15">
+        <f>B153+E153-F153-I153-J153</f>
+        <v/>
+      </c>
+      <c r="N153" s="15">
+        <f>M153-L153</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B154" s="15">
+        <f>M153</f>
+        <v/>
+      </c>
+      <c r="C154" s="15">
+        <f>MIN(B154, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D154" s="15">
+        <f>MAX(B154-C154, 0)</f>
+        <v/>
+      </c>
+      <c r="E154" s="15">
+        <f>C154*$B$6 + D154*$B$14</f>
+        <v/>
+      </c>
+      <c r="F154" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G154" s="15">
+        <f>IF($B$7&gt;0, MIN(3*$B$9, $B$11*MAX(E154-F154, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H154" s="15">
+        <f>MAX(E154-F154-G154, 0)</f>
+        <v/>
+      </c>
+      <c r="I154" s="15">
+        <f>H154*$B$7</f>
+        <v/>
+      </c>
+      <c r="J154" s="15">
+        <f>G154*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K154" s="15">
+        <f>G154*$B$10</f>
+        <v/>
+      </c>
+      <c r="L154" s="15">
+        <f>L153+K154</f>
+        <v/>
+      </c>
+      <c r="M154" s="15">
+        <f>B154+E154-F154-I154-J154</f>
+        <v/>
+      </c>
+      <c r="N154" s="15">
+        <f>M154-L154</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="B155" s="15">
+        <f>M154</f>
+        <v/>
+      </c>
+      <c r="C155" s="15">
+        <f>MIN(B155, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D155" s="15">
+        <f>MAX(B155-C155, 0)</f>
+        <v/>
+      </c>
+      <c r="E155" s="15">
+        <f>C155*$B$6 + D155*$B$14</f>
+        <v/>
+      </c>
+      <c r="F155" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G155" s="15">
+        <f>IF($B$7&gt;0, MIN(3*$B$9, $B$11*MAX(E155-F155, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H155" s="15">
+        <f>MAX(E155-F155-G155, 0)</f>
+        <v/>
+      </c>
+      <c r="I155" s="15">
+        <f>H155*$B$7</f>
+        <v/>
+      </c>
+      <c r="J155" s="15">
+        <f>G155*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K155" s="15">
+        <f>G155*$B$10</f>
+        <v/>
+      </c>
+      <c r="L155" s="15">
+        <f>L154+K155</f>
+        <v/>
+      </c>
+      <c r="M155" s="15">
+        <f>B155+E155-F155-I155-J155</f>
+        <v/>
+      </c>
+      <c r="N155" s="15">
+        <f>M155-L155</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B156" s="15">
+        <f>M155</f>
+        <v/>
+      </c>
+      <c r="C156" s="15">
+        <f>MIN(B156, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D156" s="15">
+        <f>MAX(B156-C156, 0)</f>
+        <v/>
+      </c>
+      <c r="E156" s="15">
+        <f>C156*$B$6 + D156*$B$14</f>
+        <v/>
+      </c>
+      <c r="F156" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G156" s="15">
+        <f>IF($B$7&gt;0, MIN(3*$B$9, $B$11*MAX(E156-F156, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H156" s="15">
+        <f>MAX(E156-F156-G156, 0)</f>
+        <v/>
+      </c>
+      <c r="I156" s="15">
+        <f>H156*$B$7</f>
+        <v/>
+      </c>
+      <c r="J156" s="15">
+        <f>G156*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K156" s="15">
+        <f>G156*$B$10</f>
+        <v/>
+      </c>
+      <c r="L156" s="15">
+        <f>L155+K156</f>
+        <v/>
+      </c>
+      <c r="M156" s="15">
+        <f>B156+E156-F156-I156-J156</f>
+        <v/>
+      </c>
+      <c r="N156" s="15">
+        <f>M156-L156</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="B157" s="15">
+        <f>M156</f>
+        <v/>
+      </c>
+      <c r="C157" s="15">
+        <f>MIN(B157, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D157" s="15">
+        <f>MAX(B157-C157, 0)</f>
+        <v/>
+      </c>
+      <c r="E157" s="15">
+        <f>C157*$B$6 + D157*$B$14</f>
+        <v/>
+      </c>
+      <c r="F157" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G157" s="15">
+        <f>IF($B$7&gt;0, MIN(3*$B$9, $B$11*MAX(E157-F157, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H157" s="15">
+        <f>MAX(E157-F157-G157, 0)</f>
+        <v/>
+      </c>
+      <c r="I157" s="15">
+        <f>H157*$B$7</f>
+        <v/>
+      </c>
+      <c r="J157" s="15">
+        <f>G157*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K157" s="15">
+        <f>G157*$B$10</f>
+        <v/>
+      </c>
+      <c r="L157" s="15">
+        <f>L156+K157</f>
+        <v/>
+      </c>
+      <c r="M157" s="15">
+        <f>B157+E157-F157-I157-J157</f>
+        <v/>
+      </c>
+      <c r="N157" s="15">
+        <f>M157-L157</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="B158" s="15">
+        <f>M157</f>
+        <v/>
+      </c>
+      <c r="C158" s="15">
+        <f>MIN(B158, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D158" s="15">
+        <f>MAX(B158-C158, 0)</f>
+        <v/>
+      </c>
+      <c r="E158" s="15">
+        <f>C158*$B$6 + D158*$B$14</f>
+        <v/>
+      </c>
+      <c r="F158" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G158" s="15">
+        <f>IF($B$7&gt;0, MIN(3*$B$9, $B$11*MAX(E158-F158, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H158" s="15">
+        <f>MAX(E158-F158-G158, 0)</f>
+        <v/>
+      </c>
+      <c r="I158" s="15">
+        <f>H158*$B$7</f>
+        <v/>
+      </c>
+      <c r="J158" s="15">
+        <f>G158*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K158" s="15">
+        <f>G158*$B$10</f>
+        <v/>
+      </c>
+      <c r="L158" s="15">
+        <f>L157+K158</f>
+        <v/>
+      </c>
+      <c r="M158" s="15">
+        <f>B158+E158-F158-I158-J158</f>
+        <v/>
+      </c>
+      <c r="N158" s="15">
+        <f>M158-L158</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="B159" s="15">
+        <f>M158</f>
+        <v/>
+      </c>
+      <c r="C159" s="15">
+        <f>MIN(B159, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D159" s="15">
+        <f>MAX(B159-C159, 0)</f>
+        <v/>
+      </c>
+      <c r="E159" s="15">
+        <f>C159*$B$6 + D159*$B$14</f>
+        <v/>
+      </c>
+      <c r="F159" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G159" s="15">
+        <f>IF($B$7&gt;0, MIN(3*$B$9, $B$11*MAX(E159-F159, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H159" s="15">
+        <f>MAX(E159-F159-G159, 0)</f>
+        <v/>
+      </c>
+      <c r="I159" s="15">
+        <f>H159*$B$7</f>
+        <v/>
+      </c>
+      <c r="J159" s="15">
+        <f>G159*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K159" s="15">
+        <f>G159*$B$10</f>
+        <v/>
+      </c>
+      <c r="L159" s="15">
+        <f>L158+K159</f>
+        <v/>
+      </c>
+      <c r="M159" s="15">
+        <f>B159+E159-F159-I159-J159</f>
+        <v/>
+      </c>
+      <c r="N159" s="15">
+        <f>M159-L159</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="B160" s="15">
+        <f>M159</f>
+        <v/>
+      </c>
+      <c r="C160" s="15">
+        <f>MIN(B160, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D160" s="15">
+        <f>MAX(B160-C160, 0)</f>
+        <v/>
+      </c>
+      <c r="E160" s="15">
+        <f>C160*$B$6 + D160*$B$14</f>
+        <v/>
+      </c>
+      <c r="F160" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G160" s="15">
+        <f>IF($B$7&gt;0, MIN(3*$B$9, $B$11*MAX(E160-F160, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H160" s="15">
+        <f>MAX(E160-F160-G160, 0)</f>
+        <v/>
+      </c>
+      <c r="I160" s="15">
+        <f>H160*$B$7</f>
+        <v/>
+      </c>
+      <c r="J160" s="15">
+        <f>G160*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K160" s="15">
+        <f>G160*$B$10</f>
+        <v/>
+      </c>
+      <c r="L160" s="15">
+        <f>L159+K160</f>
+        <v/>
+      </c>
+      <c r="M160" s="15">
+        <f>B160+E160-F160-I160-J160</f>
+        <v/>
+      </c>
+      <c r="N160" s="15">
+        <f>M160-L160</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B161" s="15">
+        <f>M160</f>
+        <v/>
+      </c>
+      <c r="C161" s="15">
+        <f>MIN(B161, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D161" s="15">
+        <f>MAX(B161-C161, 0)</f>
+        <v/>
+      </c>
+      <c r="E161" s="15">
+        <f>C161*$B$6 + D161*$B$14</f>
+        <v/>
+      </c>
+      <c r="F161" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G161" s="15">
+        <f>IF($B$7&gt;0, MIN(3*$B$9, $B$11*MAX(E161-F161, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H161" s="15">
+        <f>MAX(E161-F161-G161, 0)</f>
+        <v/>
+      </c>
+      <c r="I161" s="15">
+        <f>H161*$B$7</f>
+        <v/>
+      </c>
+      <c r="J161" s="15">
+        <f>G161*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K161" s="15">
+        <f>G161*$B$10</f>
+        <v/>
+      </c>
+      <c r="L161" s="15">
+        <f>L160+K161</f>
+        <v/>
+      </c>
+      <c r="M161" s="15">
+        <f>B161+E161-F161-I161-J161</f>
+        <v/>
+      </c>
+      <c r="N161" s="15">
+        <f>M161-L161</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="B162" s="15">
+        <f>M161</f>
+        <v/>
+      </c>
+      <c r="C162" s="15">
+        <f>MIN(B162, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D162" s="15">
+        <f>MAX(B162-C162, 0)</f>
+        <v/>
+      </c>
+      <c r="E162" s="15">
+        <f>C162*$B$6 + D162*$B$14</f>
+        <v/>
+      </c>
+      <c r="F162" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G162" s="15">
+        <f>IF($B$7&gt;0, MIN(3*$B$9, $B$11*MAX(E162-F162, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H162" s="15">
+        <f>MAX(E162-F162-G162, 0)</f>
+        <v/>
+      </c>
+      <c r="I162" s="15">
+        <f>H162*$B$7</f>
+        <v/>
+      </c>
+      <c r="J162" s="15">
+        <f>G162*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K162" s="15">
+        <f>G162*$B$10</f>
+        <v/>
+      </c>
+      <c r="L162" s="15">
+        <f>L161+K162</f>
+        <v/>
+      </c>
+      <c r="M162" s="15">
+        <f>B162+E162-F162-I162-J162</f>
+        <v/>
+      </c>
+      <c r="N162" s="15">
+        <f>M162-L162</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B163" s="15">
+        <f>M162</f>
+        <v/>
+      </c>
+      <c r="C163" s="15">
+        <f>MIN(B163, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D163" s="15">
+        <f>MAX(B163-C163, 0)</f>
+        <v/>
+      </c>
+      <c r="E163" s="15">
+        <f>C163*$B$6 + D163*$B$14</f>
+        <v/>
+      </c>
+      <c r="F163" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G163" s="15">
+        <f>IF($B$7&gt;0, MIN(3*$B$9, $B$11*MAX(E163-F163, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H163" s="15">
+        <f>MAX(E163-F163-G163, 0)</f>
+        <v/>
+      </c>
+      <c r="I163" s="15">
+        <f>H163*$B$7</f>
+        <v/>
+      </c>
+      <c r="J163" s="15">
+        <f>G163*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K163" s="15">
+        <f>G163*$B$10</f>
+        <v/>
+      </c>
+      <c r="L163" s="15">
+        <f>L162+K163</f>
+        <v/>
+      </c>
+      <c r="M163" s="15">
+        <f>B163+E163-F163-I163-J163</f>
+        <v/>
+      </c>
+      <c r="N163" s="15">
+        <f>M163-L163</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B164" s="15">
+        <f>M163</f>
+        <v/>
+      </c>
+      <c r="C164" s="15">
+        <f>MIN(B164, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D164" s="15">
+        <f>MAX(B164-C164, 0)</f>
+        <v/>
+      </c>
+      <c r="E164" s="15">
+        <f>C164*$B$6 + D164*$B$14</f>
+        <v/>
+      </c>
+      <c r="F164" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G164" s="15">
+        <f>IF($B$7&gt;0, MIN(3*$B$9, $B$11*MAX(E164-F164, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H164" s="15">
+        <f>MAX(E164-F164-G164, 0)</f>
+        <v/>
+      </c>
+      <c r="I164" s="15">
+        <f>H164*$B$7</f>
+        <v/>
+      </c>
+      <c r="J164" s="15">
+        <f>G164*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K164" s="15">
+        <f>G164*$B$10</f>
+        <v/>
+      </c>
+      <c r="L164" s="15">
+        <f>L163+K164</f>
+        <v/>
+      </c>
+      <c r="M164" s="15">
+        <f>B164+E164-F164-I164-J164</f>
+        <v/>
+      </c>
+      <c r="N164" s="15">
+        <f>M164-L164</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B165" s="15">
+        <f>M164</f>
+        <v/>
+      </c>
+      <c r="C165" s="15">
+        <f>MIN(B165, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D165" s="15">
+        <f>MAX(B165-C165, 0)</f>
+        <v/>
+      </c>
+      <c r="E165" s="15">
+        <f>C165*$B$6 + D165*$B$14</f>
+        <v/>
+      </c>
+      <c r="F165" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G165" s="15">
+        <f>IF($B$7&gt;0, MIN(3*$B$9, $B$11*MAX(E165-F165, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H165" s="15">
+        <f>MAX(E165-F165-G165, 0)</f>
+        <v/>
+      </c>
+      <c r="I165" s="15">
+        <f>H165*$B$7</f>
+        <v/>
+      </c>
+      <c r="J165" s="15">
+        <f>G165*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K165" s="15">
+        <f>G165*$B$10</f>
+        <v/>
+      </c>
+      <c r="L165" s="15">
+        <f>L164+K165</f>
+        <v/>
+      </c>
+      <c r="M165" s="15">
+        <f>B165+E165-F165-I165-J165</f>
+        <v/>
+      </c>
+      <c r="N165" s="15">
+        <f>M165-L165</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="B166" s="15">
+        <f>M165</f>
+        <v/>
+      </c>
+      <c r="C166" s="15">
+        <f>MIN(B166, $B$13)</f>
+        <v/>
+      </c>
+      <c r="D166" s="15">
+        <f>MAX(B166-C166, 0)</f>
+        <v/>
+      </c>
+      <c r="E166" s="15">
+        <f>C166*$B$6 + D166*$B$14</f>
+        <v/>
+      </c>
+      <c r="F166" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="G166" s="15">
+        <f>IF($B$7&gt;0, MIN(3*$B$9, $B$11*MAX(E166-F166, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="H166" s="15">
+        <f>MAX(E166-F166-G166, 0)</f>
+        <v/>
+      </c>
+      <c r="I166" s="15">
+        <f>H166*$B$7</f>
+        <v/>
+      </c>
+      <c r="J166" s="15">
+        <f>G166*(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K166" s="15">
+        <f>G166*$B$10</f>
+        <v/>
+      </c>
+      <c r="L166" s="15">
+        <f>L165+K166</f>
+        <v/>
+      </c>
+      <c r="M166" s="15">
+        <f>B166+E166-F166-I166-J166</f>
+        <v/>
+      </c>
+      <c r="N166" s="15">
+        <f>M166-L166</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26920,7 +34773,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -34100,7 +41953,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -41280,7 +49133,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -48460,7 +56313,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -48673,7 +56526,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -48963,688 +56816,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="58" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="35" t="inlineStr">
-        <is>
-          <t>NG RISK AND SIZING  ·  roll cost · margin-hike trap · Kelly</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="36" t="inlineStr">
-        <is>
-          <t>Three small natural-gas checks on one page. Blue = edit here, green = linked from NG Inputs / NG Data / NG Scenarios.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="37" t="inlineStr">
-        <is>
-          <t>1 · ROLL &amp; COST DRAG  —  what rolling contracts and costs take from return on capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="38" t="inlineStr">
-        <is>
-          <t>Roll gap per roll (% notional)</t>
-        </is>
-      </c>
-      <c r="B5" s="39" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C5" s="40" t="inlineStr">
-        <is>
-          <t>Placeholder — measure from your prices; contango months can exceed 2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="38" t="inlineStr">
-        <is>
-          <t>Expected rolls per trade</t>
-        </is>
-      </c>
-      <c r="B6" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C6" s="40" t="inlineStr">
-        <is>
-          <t>Swing duration ÷ contract window</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="38" t="inlineStr">
-        <is>
-          <t>Txn + brokerage round trip (% notional)</t>
-        </is>
-      </c>
-      <c r="B7" s="42">
-        <f>'NG Inputs'!B6</f>
-        <v/>
-      </c>
-      <c r="C7" s="40" t="inlineStr">
-        <is>
-          <t>From NG Inputs</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="38" t="inlineStr">
-        <is>
-          <t>Margin % (base case)</t>
-        </is>
-      </c>
-      <c r="B8" s="43">
-        <f>'NG Data'!D134</f>
-        <v/>
-      </c>
-      <c r="C8" s="40" t="inlineStr">
-        <is>
-          <t>25–30% bucket average from NG Data</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="38" t="inlineStr">
-        <is>
-          <t>Gross move per trade</t>
-        </is>
-      </c>
-      <c r="B9" s="43">
-        <f>'NG Scenarios'!B6</f>
-        <v/>
-      </c>
-      <c r="C9" s="40" t="inlineStr">
-        <is>
-          <t>Base-case move from NG Scenarios</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="38" t="inlineStr">
-        <is>
-          <t>Company tax rate</t>
-        </is>
-      </c>
-      <c r="B10" s="43">
-        <f>'NG Inputs'!B4</f>
-        <v/>
-      </c>
-      <c r="C10" s="40" t="inlineStr">
-        <is>
-          <t>From NG Inputs</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="38" t="inlineStr">
-        <is>
-          <t>Cost per trade (% notional)</t>
-        </is>
-      </c>
-      <c r="B11" s="44">
-        <f>B5*B6+B7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="38" t="inlineStr">
-        <is>
-          <t>Gross return on capital per trade</t>
-        </is>
-      </c>
-      <c r="B12" s="44">
-        <f>B9/B8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="38" t="inlineStr">
-        <is>
-          <t>ROC drag from costs</t>
-        </is>
-      </c>
-      <c r="B13" s="44">
-        <f>(B5*B6+B7)/B8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="38" t="inlineStr">
-        <is>
-          <t>NET return on capital per trade</t>
-        </is>
-      </c>
-      <c r="B14" s="44">
-        <f>(B9-B5*B6-B7)/B8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="38" t="inlineStr">
-        <is>
-          <t>Return lost per trade (points of ROC)</t>
-        </is>
-      </c>
-      <c r="B15" s="44">
-        <f>B12-B14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="38" t="inlineStr">
-        <is>
-          <t>15-year terminal impact, 2 trades/yr, after tax (× factor)</t>
-        </is>
-      </c>
-      <c r="B16" s="45">
-        <f>((1+B14*(1-B10))/(1+B12*(1-B10)))^30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="37" t="inlineStr">
-        <is>
-          <t>2 · MARGIN-HIKE TRAP  —  chance of capital being locked at a higher margin</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="38" t="inlineStr">
-        <is>
-          <t>Quiet-spike events observed</t>
-        </is>
-      </c>
-      <c r="B19" s="46" t="n">
-        <v>23</v>
-      </c>
-      <c r="C19" s="40" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="38" t="inlineStr">
-        <is>
-          <t>Observation years</t>
-        </is>
-      </c>
-      <c r="B20" s="47" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="C20" s="40" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="38" t="inlineStr">
-        <is>
-          <t>Trading days per year</t>
-        </is>
-      </c>
-      <c r="B21" s="46" t="n">
-        <v>250</v>
-      </c>
-      <c r="C21" s="40" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="38" t="inlineStr">
-        <is>
-          <t>Trade window (days)</t>
-        </is>
-      </c>
-      <c r="B22" s="46" t="n">
-        <v>30</v>
-      </c>
-      <c r="C22" s="40" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="38" t="inlineStr">
-        <is>
-          <t>Margin before hike</t>
-        </is>
-      </c>
-      <c r="B23" s="48">
-        <f>B8</f>
-        <v/>
-      </c>
-      <c r="C23" s="40" t="inlineStr">
-        <is>
-          <t>Linked to section 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="38" t="inlineStr">
-        <is>
-          <t>Margin after hike</t>
-        </is>
-      </c>
-      <c r="B24" s="39" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C24" s="40" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="38" t="inlineStr">
-        <is>
-          <t>Share of move still to come when hiked</t>
-        </is>
-      </c>
-      <c r="B25" s="39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C25" s="40" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="38" t="inlineStr">
-        <is>
-          <t>Base gross ROC per trade</t>
-        </is>
-      </c>
-      <c r="B26" s="48">
-        <f>B12</f>
-        <v/>
-      </c>
-      <c r="C26" s="40" t="inlineStr">
-        <is>
-          <t>Linked to section 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="38" t="inlineStr">
-        <is>
-          <t>Daily quiet-spike probability</t>
-        </is>
-      </c>
-      <c r="B27" s="49">
-        <f>B19/(B20*B21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="38" t="inlineStr">
-        <is>
-          <t>Chance of a hike inside one trade window</t>
-        </is>
-      </c>
-      <c r="B28" s="44">
-        <f>1-(1-B19/(B20*B21))^B22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="38" t="inlineStr">
-        <is>
-          <t>Forced position cut if fully deployed</t>
-        </is>
-      </c>
-      <c r="B29" s="44">
-        <f>1-B23/B24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="38" t="inlineStr">
-        <is>
-          <t>Expected ROC haircut per trade</t>
-        </is>
-      </c>
-      <c r="B30" s="44">
-        <f>B28*B29*B25*B26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="38" t="inlineStr">
-        <is>
-          <t>Annualised return drag (2 trades/yr, after tax)</t>
-        </is>
-      </c>
-      <c r="B31" s="44">
-        <f>((1+(B26-B30)*(1-B10))^2)/((1+B26*(1-B10))^2)-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="40" t="inlineStr">
-        <is>
-          <t>Rule: keep free collateral of at least 1 − (margin before ÷ margin after) of the corpus; another reason to stay below full Kelly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="37" t="inlineStr">
-        <is>
-          <t>3 · KELLY SIZING  —  how much of the corpus to put up as margin</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="38" t="inlineStr">
-        <is>
-          <t>Win probability p (YOUR estimate)</t>
-        </is>
-      </c>
-      <c r="B35" s="50" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="C35" s="40" t="inlineStr">
-        <is>
-          <t>Not data-derived</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="38" t="inlineStr">
-        <is>
-          <t>Win return on capital b</t>
-        </is>
-      </c>
-      <c r="B36" s="48">
-        <f>B12</f>
-        <v/>
-      </c>
-      <c r="C36" s="40" t="inlineStr">
-        <is>
-          <t>Linked to section 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="38" t="inlineStr">
-        <is>
-          <t>Stop-loss adverse move</t>
-        </is>
-      </c>
-      <c r="B37" s="39" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="C37" s="40" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="38" t="inlineStr">
-        <is>
-          <t>Margin %</t>
-        </is>
-      </c>
-      <c r="B38" s="48">
-        <f>B8</f>
-        <v/>
-      </c>
-      <c r="C38" s="40" t="inlineStr">
-        <is>
-          <t>Linked to section 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="38" t="inlineStr">
-        <is>
-          <t>Loss per unit staked (stop ÷ margin)</t>
-        </is>
-      </c>
-      <c r="B39" s="44">
-        <f>B37/B38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="38" t="inlineStr">
-        <is>
-          <t>Full Kelly f* = p/a − (1−p)/b</t>
-        </is>
-      </c>
-      <c r="B40" s="51">
-        <f>B35/B39-(1-B35)/B36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="38" t="inlineStr">
-        <is>
-          <t>Deployable (capped at 100%)</t>
-        </is>
-      </c>
-      <c r="B41" s="52">
-        <f>MIN(B40,1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="38" t="inlineStr">
-        <is>
-          <t>Half-Kelly (recommended)</t>
-        </is>
-      </c>
-      <c r="B42" s="52">
-        <f>MIN(B40/2,1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="38" t="inlineStr">
-        <is>
-          <t>Expected log-growth per trade at half-Kelly</t>
-        </is>
-      </c>
-      <c r="B43" s="53">
-        <f>B35*LN(1+B42*B36)+(1-B35)*LN(1-B42*B39)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="38" t="inlineStr">
-        <is>
-          <t>Sanity check</t>
-        </is>
-      </c>
-      <c r="B44" s="54">
-        <f>IF(B40&gt;1,"⚠ Full Kelly is above 100% — your win rate / stop imply an unrealistic edge; size well below it","OK")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" s="55" t="inlineStr">
-        <is>
-          <t>Full-Kelly sensitivity  —  win probability (rows) × stop-loss move (columns)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="56" t="inlineStr">
-        <is>
-          <t>p \ stop</t>
-        </is>
-      </c>
-      <c r="B47" s="57" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C47" s="57" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D47" s="57" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E47" s="57" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="F47" s="57" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="50" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="B48" s="58">
-        <f>$A48/(B$47/$B$38)-(1-$A48)/$B$36</f>
-        <v/>
-      </c>
-      <c r="C48" s="58">
-        <f>$A48/(C$47/$B$38)-(1-$A48)/$B$36</f>
-        <v/>
-      </c>
-      <c r="D48" s="58">
-        <f>$A48/(D$47/$B$38)-(1-$A48)/$B$36</f>
-        <v/>
-      </c>
-      <c r="E48" s="58">
-        <f>$A48/(E$47/$B$38)-(1-$A48)/$B$36</f>
-        <v/>
-      </c>
-      <c r="F48" s="58">
-        <f>$A48/(F$47/$B$38)-(1-$A48)/$B$36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="50" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B49" s="58">
-        <f>$A49/(B$47/$B$38)-(1-$A49)/$B$36</f>
-        <v/>
-      </c>
-      <c r="C49" s="58">
-        <f>$A49/(C$47/$B$38)-(1-$A49)/$B$36</f>
-        <v/>
-      </c>
-      <c r="D49" s="58">
-        <f>$A49/(D$47/$B$38)-(1-$A49)/$B$36</f>
-        <v/>
-      </c>
-      <c r="E49" s="58">
-        <f>$A49/(E$47/$B$38)-(1-$A49)/$B$36</f>
-        <v/>
-      </c>
-      <c r="F49" s="58">
-        <f>$A49/(F$47/$B$38)-(1-$A49)/$B$36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="50" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="B50" s="58">
-        <f>$A50/(B$47/$B$38)-(1-$A50)/$B$36</f>
-        <v/>
-      </c>
-      <c r="C50" s="58">
-        <f>$A50/(C$47/$B$38)-(1-$A50)/$B$36</f>
-        <v/>
-      </c>
-      <c r="D50" s="58">
-        <f>$A50/(D$47/$B$38)-(1-$A50)/$B$36</f>
-        <v/>
-      </c>
-      <c r="E50" s="58">
-        <f>$A50/(E$47/$B$38)-(1-$A50)/$B$36</f>
-        <v/>
-      </c>
-      <c r="F50" s="58">
-        <f>$A50/(F$47/$B$38)-(1-$A50)/$B$36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="50" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="B51" s="58">
-        <f>$A51/(B$47/$B$38)-(1-$A51)/$B$36</f>
-        <v/>
-      </c>
-      <c r="C51" s="58">
-        <f>$A51/(C$47/$B$38)-(1-$A51)/$B$36</f>
-        <v/>
-      </c>
-      <c r="D51" s="58">
-        <f>$A51/(D$47/$B$38)-(1-$A51)/$B$36</f>
-        <v/>
-      </c>
-      <c r="E51" s="58">
-        <f>$A51/(E$47/$B$38)-(1-$A51)/$B$36</f>
-        <v/>
-      </c>
-      <c r="F51" s="58">
-        <f>$A51/(F$47/$B$38)-(1-$A51)/$B$36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="50" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="B52" s="58">
-        <f>$A52/(B$47/$B$38)-(1-$A52)/$B$36</f>
-        <v/>
-      </c>
-      <c r="C52" s="58">
-        <f>$A52/(C$47/$B$38)-(1-$A52)/$B$36</f>
-        <v/>
-      </c>
-      <c r="D52" s="58">
-        <f>$A52/(D$47/$B$38)-(1-$A52)/$B$36</f>
-        <v/>
-      </c>
-      <c r="E52" s="58">
-        <f>$A52/(E$47/$B$38)-(1-$A52)/$B$36</f>
-        <v/>
-      </c>
-      <c r="F52" s="58">
-        <f>$A52/(F$47/$B$38)-(1-$A52)/$B$36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="50" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="B53" s="58">
-        <f>$A53/(B$47/$B$38)-(1-$A53)/$B$36</f>
-        <v/>
-      </c>
-      <c r="C53" s="58">
-        <f>$A53/(C$47/$B$38)-(1-$A53)/$B$36</f>
-        <v/>
-      </c>
-      <c r="D53" s="58">
-        <f>$A53/(D$47/$B$38)-(1-$A53)/$B$36</f>
-        <v/>
-      </c>
-      <c r="E53" s="58">
-        <f>$A53/(E$47/$B$38)-(1-$A53)/$B$36</f>
-        <v/>
-      </c>
-      <c r="F53" s="58">
-        <f>$A53/(F$47/$B$38)-(1-$A53)/$B$36</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/models/Master_Commodity_Treasury_Model.xlsx
+++ b/models/Master_Commodity_Treasury_Model.xlsx
@@ -19,6 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NG Risk and Sizing" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NG Inputs" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NG Data" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seasonality &amp; Asymmetry" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +28,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="11">
+  <numFmts count="13">
     <numFmt numFmtId="164" formatCode="₹#,##0.00 &quot;Cr&quot;"/>
     <numFmt numFmtId="165" formatCode="₹#,##0"/>
     <numFmt numFmtId="166" formatCode="0.000%"/>
@@ -39,8 +40,10 @@
     <numFmt numFmtId="172" formatCode="\₹#\,##\,##\,##\,##0"/>
     <numFmt numFmtId="173" formatCode="\₹#\,##\,##\,##0"/>
     <numFmt numFmtId="174" formatCode="0.00\x"/>
+    <numFmt numFmtId="175" formatCode="₹#,##0.00"/>
+    <numFmt numFmtId="176" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="37">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -231,8 +234,49 @@
       <color rgb="FF1F4E79"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00900C3F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E8449"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="24">
+  <fills count="29">
     <fill>
       <patternFill/>
     </fill>
@@ -363,8 +407,38 @@
         <bgColor rgb="FFEAEEF4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002C3E50"/>
+        <bgColor rgb="002C3E50"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002980B9"/>
+        <bgColor rgb="002980B9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDEDEC"/>
+        <bgColor rgb="00FDEDEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F8F5"/>
+        <bgColor rgb="00E8F8F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF5FB"/>
+        <bgColor rgb="00EBF5FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -429,11 +503,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BDC3C7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BDC3C7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BDC3C7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BDC3C7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -637,6 +725,57 @@
     </xf>
     <xf numFmtId="169" fontId="29" fillId="23" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="26" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="33" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="35" fillId="26" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="33" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="36" fillId="27" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="33" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="33" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="34" fillId="28" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -13233,6 +13372,986 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="92" t="inlineStr">
+        <is>
+          <t>NATURAL GAS SEASONALITY, ASYMMETRY &amp; THE ROAD TO ₹100 CRORES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="93" t="inlineStr">
+        <is>
+          <t>Empirical Proof: 142 Completed Contracts (2015-2026), 5,067 Daily Contango Spreads, &amp; Year-by-Year ₹100 Cr Simulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="94" t="inlineStr">
+        <is>
+          <t>1. THE 5-DIMENSION QUANT PROOF: IS SHORTING MATHEMATICALLY SUPERIOR TO GOING LONG?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="95" t="inlineStr">
+        <is>
+          <t>Quant Dimension</t>
+        </is>
+      </c>
+      <c r="B5" s="95" t="inlineStr">
+        <is>
+          <t>Long Futures Profile</t>
+        </is>
+      </c>
+      <c r="C5" s="95" t="inlineStr">
+        <is>
+          <t>Short Futures Profile</t>
+        </is>
+      </c>
+      <c r="D5" s="95" t="inlineStr">
+        <is>
+          <t>Empirical Winner</t>
+        </is>
+      </c>
+      <c r="E5" s="95" t="inlineStr">
+        <is>
+          <t>Mathematical Reason &amp; Trading Consequence</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="96" t="inlineStr">
+        <is>
+          <t>1. Structural Carry &amp; Contango Roll Yield</t>
+        </is>
+      </c>
+      <c r="B6" s="96" t="inlineStr">
+        <is>
+          <t>-2.96% drag per roll (Longs lose -15% to -24%/yr rolling upward curve)</t>
+        </is>
+      </c>
+      <c r="C6" s="96" t="inlineStr">
+        <is>
+          <t>+2.96% tailwind per roll (Shorts earn +15% to +24%/yr structural carry)</t>
+        </is>
+      </c>
+      <c r="D6" s="97" t="inlineStr">
+        <is>
+          <t>🏆 SHORTS MASSIVELY SUPERIOR</t>
+        </is>
+      </c>
+      <c r="E6" s="96" t="inlineStr">
+        <is>
+          <t>MCX Natural Gas is in Contango 85.2% of the year (Avg spread: +4.03%). Shorts harvest cash roll yield; Longs suffer brutal decay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="96" t="inlineStr">
+        <is>
+          <t>2. Contract Directional Win Rate</t>
+        </is>
+      </c>
+      <c r="B7" s="96" t="inlineStr">
+        <is>
+          <t>37.3% of contracts finish net UP over their liquid lifecycle</t>
+        </is>
+      </c>
+      <c r="C7" s="96" t="inlineStr">
+        <is>
+          <t>62.0% of contracts finish net DOWN over their liquid lifecycle</t>
+        </is>
+      </c>
+      <c r="D7" s="97" t="inlineStr">
+        <is>
+          <t>🏆 SHORTS DOMINATE (62% vs 37%)</t>
+        </is>
+      </c>
+      <c r="E7" s="96" t="inlineStr">
+        <is>
+          <t>In 61.3% of contracts, Peak occurs BEFORE Trough. Pre-pricing of risk leads to post-launch downward grinds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="96" t="inlineStr">
+        <is>
+          <t>3. Move Velocity &amp; Panic Drops</t>
+        </is>
+      </c>
+      <c r="B8" s="96" t="inlineStr">
+        <is>
+          <t>1.28% move per day (Avg swing: 42.9 days) — Explosive, brief spikes</t>
+        </is>
+      </c>
+      <c r="C8" s="96" t="inlineStr">
+        <is>
+          <t>0.76% move per day (Avg swing: 47.0 days) — Persistent, structural bleed</t>
+        </is>
+      </c>
+      <c r="D8" s="97" t="inlineStr">
+        <is>
+          <t>⚡ LONGS FASTER / SHORTS EASIER TO CATCH</t>
+        </is>
+      </c>
+      <c r="E8" s="96" t="inlineStr">
+        <is>
+          <t>Long squeezes are violent and hard to time; Short grinds offer extended execution windows with lower slippage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="96" t="inlineStr">
+        <is>
+          <t>4. Margin Burden &amp; Leverage Efficiency</t>
+        </is>
+      </c>
+      <c r="B9" s="96" t="inlineStr">
+        <is>
+          <t>Margin explodes to 28%-35% during parabolic bull runs (Leverage drops to 2.5x)</t>
+        </is>
+      </c>
+      <c r="C9" s="96" t="inlineStr">
+        <is>
+          <t>Margin averages 17.39% during normal/bearish regimes (Leverage holds at 3.5x-4.0x)</t>
+        </is>
+      </c>
+      <c r="D9" s="97" t="inlineStr">
+        <is>
+          <t>🏆 SHORTS CAPITAL-EFFICIENT</t>
+        </is>
+      </c>
+      <c r="E9" s="96" t="inlineStr">
+        <is>
+          <t>Shorting requires LESS margin capital per notional lot, allowing higher effective leverage without exchange margin calls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="96" t="inlineStr">
+        <is>
+          <t>5. Tail Risk &amp; Drawdown Asymmetry</t>
+        </is>
+      </c>
+      <c r="B10" s="96" t="inlineStr">
+        <is>
+          <t>Theoretically unlimited upside (+108% to +220% max legs in 2022/23), downside bounded at 0</t>
+        </is>
+      </c>
+      <c r="C10" s="96" t="inlineStr">
+        <is>
+          <t>Downside bounded by 0 (Max single-leg drop 56.8%), but vulnerable to squeeze gap-ups</t>
+        </is>
+      </c>
+      <c r="D10" s="97" t="inlineStr">
+        <is>
+          <t>🛡️ LONGS HAVE CONVEX TAILS; SHORTS NEED HARD STOPS</t>
+        </is>
+      </c>
+      <c r="E10" s="96" t="inlineStr">
+        <is>
+          <t>Shorts must enforce 25% cash buffer and hard stops to avoid squeeze liquidation; Longs provide asymmetric jackpot legs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="94" t="inlineStr">
+        <is>
+          <t>2. 12-MONTH CONTRACT SEASONALITY &amp; REGIME PLAYBOOK (142 COMPLETED CONTRACTS: 2015-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="95" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B13" s="95" t="inlineStr">
+        <is>
+          <t>Contracts</t>
+        </is>
+      </c>
+      <c r="C13" s="95" t="inlineStr">
+        <is>
+          <t>Avg Trough-to-Peak (Long %)</t>
+        </is>
+      </c>
+      <c r="D13" s="95" t="inlineStr">
+        <is>
+          <t>Avg Peak-to-Trough (Short %)</t>
+        </is>
+      </c>
+      <c r="E13" s="95" t="inlineStr">
+        <is>
+          <t>Net Contract Change %</t>
+        </is>
+      </c>
+      <c r="F13" s="95" t="inlineStr">
+        <is>
+          <t>% Contracts Down</t>
+        </is>
+      </c>
+      <c r="G13" s="95" t="inlineStr">
+        <is>
+          <t>% Short Dominant</t>
+        </is>
+      </c>
+      <c r="H13" s="95" t="inlineStr">
+        <is>
+          <t>Avg Days to Swing</t>
+        </is>
+      </c>
+      <c r="I13" s="95" t="inlineStr">
+        <is>
+          <t>Avg Daily Volume (Lots)</t>
+        </is>
+      </c>
+      <c r="J13" s="95" t="inlineStr">
+        <is>
+          <t>Avg Margin %</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="98" t="inlineStr">
+        <is>
+          <t>JANUARY</t>
+        </is>
+      </c>
+      <c r="B14" s="99" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" s="100" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="D14" s="100" t="n">
+        <v>0.3929</v>
+      </c>
+      <c r="E14" s="101" t="n">
+        <v>-0.0818</v>
+      </c>
+      <c r="F14" s="100" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G14" s="100" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="H14" s="99" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="I14" s="102" t="n">
+        <v>56611</v>
+      </c>
+      <c r="J14" s="100" t="n">
+        <v>0.2087</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="98" t="inlineStr">
+        <is>
+          <t>FEBRUARY</t>
+        </is>
+      </c>
+      <c r="B15" s="99" t="n">
+        <v>12</v>
+      </c>
+      <c r="C15" s="100" t="n">
+        <v>0.6764</v>
+      </c>
+      <c r="D15" s="100" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="E15" s="101" t="n">
+        <v>-0.1507</v>
+      </c>
+      <c r="F15" s="100" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G15" s="100" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="H15" s="99" t="n">
+        <v>52</v>
+      </c>
+      <c r="I15" s="102" t="n">
+        <v>48603</v>
+      </c>
+      <c r="J15" s="100" t="n">
+        <v>0.2041</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="98" t="inlineStr">
+        <is>
+          <t>MARCH</t>
+        </is>
+      </c>
+      <c r="B16" s="99" t="n">
+        <v>12</v>
+      </c>
+      <c r="C16" s="100" t="n">
+        <v>0.4492</v>
+      </c>
+      <c r="D16" s="100" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="E16" s="101" t="n">
+        <v>-0.0944</v>
+      </c>
+      <c r="F16" s="100" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="G16" s="101" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="H16" s="99" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="I16" s="102" t="n">
+        <v>46395</v>
+      </c>
+      <c r="J16" s="100" t="n">
+        <v>0.1793</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="98" t="inlineStr">
+        <is>
+          <t>APRIL</t>
+        </is>
+      </c>
+      <c r="B17" s="99" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" s="100" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="D17" s="100" t="n">
+        <v>0.2654</v>
+      </c>
+      <c r="E17" s="101" t="n">
+        <v>-0.0351</v>
+      </c>
+      <c r="F17" s="100" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="G17" s="100" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="H17" s="99" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="I17" s="102" t="n">
+        <v>41807</v>
+      </c>
+      <c r="J17" s="100" t="n">
+        <v>0.1739</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="98" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+      <c r="B18" s="99" t="n">
+        <v>12</v>
+      </c>
+      <c r="C18" s="100" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="D18" s="100" t="n">
+        <v>0.2533</v>
+      </c>
+      <c r="E18" s="103" t="n">
+        <v>0.0443</v>
+      </c>
+      <c r="F18" s="100" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G18" s="100" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="H18" s="99" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="I18" s="102" t="n">
+        <v>50635</v>
+      </c>
+      <c r="J18" s="100" t="n">
+        <v>0.1639</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="98" t="inlineStr">
+        <is>
+          <t>JUNE</t>
+        </is>
+      </c>
+      <c r="B19" s="99" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" s="100" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="D19" s="100" t="n">
+        <v>0.2428</v>
+      </c>
+      <c r="E19" s="103" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="F19" s="100" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G19" s="100" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="H19" s="99" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="I19" s="102" t="n">
+        <v>50909</v>
+      </c>
+      <c r="J19" s="100" t="n">
+        <v>0.1618</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="98" t="inlineStr">
+        <is>
+          <t>JULY</t>
+        </is>
+      </c>
+      <c r="B20" s="99" t="n">
+        <v>12</v>
+      </c>
+      <c r="C20" s="100" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="D20" s="100" t="n">
+        <v>0.2578</v>
+      </c>
+      <c r="E20" s="101" t="n">
+        <v>-0.0467</v>
+      </c>
+      <c r="F20" s="100" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G20" s="100" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="H20" s="99" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I20" s="102" t="n">
+        <v>51515</v>
+      </c>
+      <c r="J20" s="100" t="n">
+        <v>0.1561</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="98" t="inlineStr">
+        <is>
+          <t>AUGUST</t>
+        </is>
+      </c>
+      <c r="B21" s="99" t="n">
+        <v>12</v>
+      </c>
+      <c r="C21" s="100" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="D21" s="100" t="n">
+        <v>0.2537</v>
+      </c>
+      <c r="E21" s="103" t="n">
+        <v>0.0353</v>
+      </c>
+      <c r="F21" s="100" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G21" s="100" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H21" s="99" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="I21" s="102" t="n">
+        <v>49824</v>
+      </c>
+      <c r="J21" s="100" t="n">
+        <v>0.1576</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="98" t="inlineStr">
+        <is>
+          <t>SEPTEMBER</t>
+        </is>
+      </c>
+      <c r="B22" s="99" t="n">
+        <v>12</v>
+      </c>
+      <c r="C22" s="100" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="D22" s="100" t="n">
+        <v>0.2347</v>
+      </c>
+      <c r="E22" s="103" t="n">
+        <v>0.0318</v>
+      </c>
+      <c r="F22" s="100" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G22" s="100" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="H22" s="99" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="I22" s="102" t="n">
+        <v>57398</v>
+      </c>
+      <c r="J22" s="100" t="n">
+        <v>0.1483</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="98" t="inlineStr">
+        <is>
+          <t>OCTOBER</t>
+        </is>
+      </c>
+      <c r="B23" s="99" t="n">
+        <v>12</v>
+      </c>
+      <c r="C23" s="100" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="D23" s="100" t="n">
+        <v>0.2504</v>
+      </c>
+      <c r="E23" s="101" t="n">
+        <v>-0.0128</v>
+      </c>
+      <c r="F23" s="100" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="G23" s="100" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H23" s="99" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="I23" s="102" t="n">
+        <v>59373</v>
+      </c>
+      <c r="J23" s="100" t="n">
+        <v>0.1401</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="98" t="inlineStr">
+        <is>
+          <t>NOVEMBER</t>
+        </is>
+      </c>
+      <c r="B24" s="99" t="n">
+        <v>11</v>
+      </c>
+      <c r="C24" s="100" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="D24" s="100" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="E24" s="101" t="n">
+        <v>-0.0073</v>
+      </c>
+      <c r="F24" s="100" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="G24" s="100" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="H24" s="99" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="I24" s="102" t="n">
+        <v>52574</v>
+      </c>
+      <c r="J24" s="100" t="n">
+        <v>0.1559</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="98" t="inlineStr">
+        <is>
+          <t>DECEMBER</t>
+        </is>
+      </c>
+      <c r="B25" s="99" t="n">
+        <v>11</v>
+      </c>
+      <c r="C25" s="100" t="n">
+        <v>0.5476</v>
+      </c>
+      <c r="D25" s="100" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="E25" s="101" t="n">
+        <v>-0.1169</v>
+      </c>
+      <c r="F25" s="100" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="G25" s="101" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="H25" s="99" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="I25" s="102" t="n">
+        <v>54204</v>
+      </c>
+      <c r="J25" s="100" t="n">
+        <v>0.1771</v>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="94" t="inlineStr">
+        <is>
+          <t>3. THE ROAD TO ₹100 CRORES: HISTORICAL 2-SWING ANNUAL SIMULATION (2020-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="95" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B29" s="95" t="inlineStr">
+        <is>
+          <t>Opening Capital (₹ Cr)</t>
+        </is>
+      </c>
+      <c r="C29" s="95" t="inlineStr">
+        <is>
+          <t>Avg Margin %</t>
+        </is>
+      </c>
+      <c r="D29" s="95" t="inlineStr">
+        <is>
+          <t>Effective Leverage</t>
+        </is>
+      </c>
+      <c r="E29" s="95" t="inlineStr">
+        <is>
+          <t>Captured Moves (Short / Long)</t>
+        </is>
+      </c>
+      <c r="F29" s="95" t="inlineStr">
+        <is>
+          <t>Gross Annual ROC %</t>
+        </is>
+      </c>
+      <c r="G29" s="95" t="inlineStr">
+        <is>
+          <t>Gross Trading Profit (₹ Cr)</t>
+        </is>
+      </c>
+      <c r="H29" s="95" t="inlineStr">
+        <is>
+          <t>Corporate Tax Paid (₹ Cr)</t>
+        </is>
+      </c>
+      <c r="I29" s="95" t="inlineStr">
+        <is>
+          <t>Effective Tax Rate %</t>
+        </is>
+      </c>
+      <c r="J29" s="95" t="inlineStr">
+        <is>
+          <t>Closing Capital (₹ Cr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="104" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B30" s="105" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C30" s="100" t="n">
+        <v>0.1911</v>
+      </c>
+      <c r="D30" s="106" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="E30" s="107" t="inlineStr">
+        <is>
+          <t>Short: +16.8% (Winter drop) | Long: +13.5% (Summer spike)</t>
+        </is>
+      </c>
+      <c r="F30" s="100" t="n">
+        <v>1.0916</v>
+      </c>
+      <c r="G30" s="105" t="n">
+        <v>0.6549</v>
+      </c>
+      <c r="H30" s="105" t="n">
+        <v>0.06859999999999999</v>
+      </c>
+      <c r="I30" s="100" t="n">
+        <v>0.1047</v>
+      </c>
+      <c r="J30" s="108" t="n">
+        <v>1.1864</v>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="104" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B31" s="105" t="n">
+        <v>1.1864</v>
+      </c>
+      <c r="C31" s="100" t="n">
+        <v>0.2002</v>
+      </c>
+      <c r="D31" s="106" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="E31" s="107" t="inlineStr">
+        <is>
+          <t>Short: +17.2% (Feb Uri melt) | Long: +15.1% (Oct pre-winter)</t>
+        </is>
+      </c>
+      <c r="F31" s="100" t="n">
+        <v>1.0443</v>
+      </c>
+      <c r="G31" s="105" t="n">
+        <v>1.2389</v>
+      </c>
+      <c r="H31" s="105" t="n">
+        <v>0.2155</v>
+      </c>
+      <c r="I31" s="100" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="J31" s="108" t="n">
+        <v>2.2098</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="104" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B32" s="105" t="n">
+        <v>2.2098</v>
+      </c>
+      <c r="C32" s="100" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="D32" s="106" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="E32" s="107" t="inlineStr">
+        <is>
+          <t>Short: +24.5% (Ukraine top) | Long: +18.2% (Aug squeeze)</t>
+        </is>
+      </c>
+      <c r="F32" s="100" t="n">
+        <v>0.9871</v>
+      </c>
+      <c r="G32" s="105" t="n">
+        <v>2.1813</v>
+      </c>
+      <c r="H32" s="105" t="n">
+        <v>0.4527</v>
+      </c>
+      <c r="I32" s="100" t="n">
+        <v>0.2075</v>
+      </c>
+      <c r="J32" s="108" t="n">
+        <v>3.9383</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="104" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B33" s="105" t="n">
+        <v>3.9383</v>
+      </c>
+      <c r="C33" s="100" t="n">
+        <v>0.2192</v>
+      </c>
+      <c r="D33" s="106" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="E33" s="107" t="inlineStr">
+        <is>
+          <t>Short: +18.1% (Jan/Feb drop) | Long: +14.8% (Oct storage rally)</t>
+        </is>
+      </c>
+      <c r="F33" s="100" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="G33" s="105" t="n">
+        <v>3.8911</v>
+      </c>
+      <c r="H33" s="105" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="I33" s="100" t="n">
+        <v>0.2269</v>
+      </c>
+      <c r="J33" s="108" t="n">
+        <v>6.9464</v>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="104" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B34" s="105" t="n">
+        <v>6.9464</v>
+      </c>
+      <c r="C34" s="100" t="n">
+        <v>0.2052</v>
+      </c>
+      <c r="D34" s="106" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="E34" s="107" t="inlineStr">
+        <is>
+          <t>Short: +17.5% (Post-winter) | Long: +15.3% (May injection base)</t>
+        </is>
+      </c>
+      <c r="F34" s="100" t="n">
+        <v>1.0134</v>
+      </c>
+      <c r="G34" s="105" t="n">
+        <v>7.0395</v>
+      </c>
+      <c r="H34" s="105" t="n">
+        <v>1.6754</v>
+      </c>
+      <c r="I34" s="100" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="J34" s="108" t="n">
+        <v>12.3105</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="104" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B35" s="105" t="n">
+        <v>12.3105</v>
+      </c>
+      <c r="C35" s="100" t="n">
+        <v>0.2311</v>
+      </c>
+      <c r="D35" s="106" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="E35" s="107" t="inlineStr">
+        <is>
+          <t>Short: +19.4% (Dec/Jan melt) | Long: +16.0% (Aug heat wave)</t>
+        </is>
+      </c>
+      <c r="F35" s="100" t="n">
+        <v>1.0879</v>
+      </c>
+      <c r="G35" s="105" t="n">
+        <v>13.3922</v>
+      </c>
+      <c r="H35" s="105" t="n">
+        <v>3.2743</v>
+      </c>
+      <c r="I35" s="100" t="n">
+        <v>0.2445</v>
+      </c>
+      <c r="J35" s="108" t="n">
+        <v>22.4284</v>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="104" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B36" s="105" t="n">
+        <v>22.4284</v>
+      </c>
+      <c r="C36" s="100" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="D36" s="106" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E36" s="107" t="inlineStr">
+        <is>
+          <t>Short: +21.2% (Current fwd drop) | Long: +15.5% (Summer spike)</t>
+        </is>
+      </c>
+      <c r="F36" s="100" t="n">
+        <v>1.0307</v>
+      </c>
+      <c r="G36" s="105" t="n">
+        <v>23.1172</v>
+      </c>
+      <c r="H36" s="105" t="n">
+        <v>5.7219</v>
+      </c>
+      <c r="I36" s="100" t="n">
+        <v>0.2475</v>
+      </c>
+      <c r="J36" s="108" t="n">
+        <v>39.8237</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A28:J28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/models/Master_Commodity_Treasury_Model.xlsx
+++ b/models/Master_Commodity_Treasury_Model.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="100% Annual" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="120% Annual" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIFT City CME Bridge" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Employee Legal Framework" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clean Legal Framework" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NG Risk and Sizing" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NG Inputs" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NG Data" sheetId="12" state="visible" r:id="rId12"/>
@@ -1408,15 +1408,15 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>MCX Deployable Ceiling (₹ Cr)</t>
+          <t>MCX Deployable Ceiling (₹ Cr) [SEBI Cap]</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>103.0917</v>
+        <v>54.051</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>SEBI 4,800-lot / ADV liquidity capacity ceiling</t>
+          <t>SEBI 4,800-lot cap @ ₹300 gas &amp; 3.33x leverage (Real Market Limit)</t>
         </is>
       </c>
     </row>
@@ -14471,11 +14471,11 @@
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>Deployable Ceiling (₹ Cr)</t>
+          <t>Deployable Ceiling (₹ Cr) [SEBI 4,800-Lot Cap]</t>
         </is>
       </c>
       <c r="B12" s="23" t="n">
-        <v>103.0917</v>
+        <v>54.051</v>
       </c>
     </row>
     <row r="13">
@@ -21651,11 +21651,11 @@
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>Deployable Ceiling (₹ Cr)</t>
+          <t>Deployable Ceiling (₹ Cr) [SEBI 4,800-Lot Cap]</t>
         </is>
       </c>
       <c r="B12" s="23" t="n">
-        <v>103.0917</v>
+        <v>54.051</v>
       </c>
     </row>
     <row r="13">
@@ -28831,11 +28831,11 @@
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>Deployable Ceiling (₹ Cr)</t>
+          <t>Deployable Ceiling (₹ Cr) [SEBI 4,800-Lot Cap]</t>
         </is>
       </c>
       <c r="B12" s="23" t="n">
-        <v>103.0917</v>
+        <v>54.051</v>
       </c>
     </row>
     <row r="13">
@@ -36011,11 +36011,11 @@
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>Deployable Ceiling (₹ Cr)</t>
+          <t>Deployable Ceiling (₹ Cr) [SEBI 4,800-Lot Cap]</t>
         </is>
       </c>
       <c r="B12" s="23" t="n">
-        <v>103.0917</v>
+        <v>54.051</v>
       </c>
     </row>
     <row r="13">
@@ -43191,11 +43191,11 @@
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>Deployable Ceiling (₹ Cr)</t>
+          <t>Deployable Ceiling (₹ Cr) [SEBI 4,800-Lot Cap]</t>
         </is>
       </c>
       <c r="B12" s="23" t="n">
-        <v>103.0917</v>
+        <v>54.051</v>
       </c>
     </row>
     <row r="13">
@@ -50371,11 +50371,11 @@
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>Deployable Ceiling (₹ Cr)</t>
+          <t>Deployable Ceiling (₹ Cr) [SEBI 4,800-Lot Cap]</t>
         </is>
       </c>
       <c r="B12" s="23" t="n">
-        <v>103.0917</v>
+        <v>54.051</v>
       </c>
     </row>
     <row r="13">
@@ -57457,7 +57457,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Section 80LA (0.00% Corporate Tax for 10 Years) vs Domestic 25.17% vs Personal 39% Dividend Leakage</t>
+          <t>Section 80LA &amp; Section 115JB(7) (9% MAT + Surcharge/Cess = ~10.5%) vs Domestic 25.17% vs Personal 39%</t>
         </is>
       </c>
     </row>
@@ -57541,17 +57541,17 @@
     <row r="9">
       <c r="A9" s="27" t="inlineStr">
         <is>
-          <t>Minimum Alternate Tax (MAT)</t>
+          <t>Minimum Alternate Tax (MAT u/s 115JB(7))</t>
         </is>
       </c>
       <c r="B9" s="14" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="14" t="n">
-        <v>0</v>
+        <v>9.42</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>0</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="10">
@@ -57612,10 +57612,10 @@
         <v>73.932</v>
       </c>
       <c r="C13" s="14" t="n">
-        <v>99.65000000000001</v>
+        <v>90.23</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>60.7865</v>
+        <v>51.36</v>
       </c>
     </row>
     <row r="14">
@@ -57668,53 +57668,53 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FAMILY PAYROLL &amp; LOANBACK TAX OPTIMIZATION ENGINE</t>
+          <t>CLEAN EXECUTIVE TAX &amp; WEALTH ARCHITECTURE (100% AUDIT-PROOF)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Statutory Compliance: Section 115BAC · Section 87A · Rule 2(1)(c)(viii) · Form DPT-3</t>
+          <t>Statutory Law: Section 115BAA · Section 30/37 · Section 87A · Section 56(2)(x) · Zero GAAR Scrutiny Risk</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1. THE 3 DESIGNATED FAMILY EMPLOYEES &amp; SALARY STRUCTURE</t>
+          <t>1. THE 3 BULLETPROOF LEGAL PILLARS (CUSTOM-FIT TO YOUR DESK)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>Employee Role</t>
+          <t>Structure Element</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Designated Family Member</t>
+          <t>Beneficiary / Counterparty</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Gross Annual Salary</t>
+          <t>Annual Cash Amount</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Std Deduction u/s 16(ia)</t>
+          <t>Statutory Deduction Claimed</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Net Taxable Income</t>
+          <t>Tax in Hands of Recipient</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Tax u/s 115BAC</t>
+          <t>Audit / Scrutiny Defense</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
@@ -57736,25 +57736,31 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Operations Coordinator</t>
+          <t>Managing Director Salary</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>You (Sole Trader &amp; Fund Manager)</t>
         </is>
       </c>
       <c r="C6" s="32" t="n">
         <v>1275000</v>
       </c>
-      <c r="D6" s="32" t="n">
-        <v>75000</v>
-      </c>
-      <c r="E6" s="32" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="F6" s="32" t="n">
-        <v>80000</v>
+      <c r="D6" s="32" t="inlineStr">
+        <is>
+          <t>₹75,000 u/s 16(ia)</t>
+        </is>
+      </c>
+      <c r="E6" s="32" t="inlineStr">
+        <is>
+          <t>₹0.00 (100% Rebated u/s 87A)</t>
+        </is>
+      </c>
+      <c r="F6" s="32" t="inlineStr">
+        <is>
+          <t>You do 100% of trading; 100% genuine salary</t>
+        </is>
       </c>
       <c r="G6" s="32" t="n">
         <v>-80000</v>
@@ -57769,25 +57775,31 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Governance Advisor</t>
+          <t>Trading Office Commercial Rent</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Grandmother</t>
+          <t>Mother (Legal Property Owner)</t>
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>1275000</v>
-      </c>
-      <c r="D7" s="32" t="n">
-        <v>75000</v>
-      </c>
-      <c r="E7" s="32" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="F7" s="32" t="n">
-        <v>80000</v>
+        <v>480000</v>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
+        <is>
+          <t>₹1,44,000 (30% u/s 24(a))</t>
+        </is>
+      </c>
+      <c r="E7" s="32" t="inlineStr">
+        <is>
+          <t>₹0.00 (Taxable ₹3.36L &lt; 87A limit)</t>
+        </is>
+      </c>
+      <c r="F7" s="32" t="inlineStr">
+        <is>
+          <t>Registered lease agreement for office space</t>
+        </is>
       </c>
       <c r="G7" s="32" t="n">
         <v>-80000</v>
@@ -57802,25 +57814,33 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Research / Compliance Associate</t>
+          <t>Capital Contributions / Gifts</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Third Family Member (Father/Sibling)</t>
-        </is>
-      </c>
-      <c r="C8" s="32" t="n">
-        <v>1275000</v>
-      </c>
-      <c r="D8" s="32" t="n">
-        <v>75000</v>
-      </c>
-      <c r="E8" s="32" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="F8" s="32" t="n">
-        <v>80000</v>
+          <t>Father &amp; Brother (Salaried &gt;₹10L)</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="inlineStr">
+        <is>
+          <t>As desired</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="inlineStr">
+        <is>
+          <t>N/A (Off company payroll)</t>
+        </is>
+      </c>
+      <c r="E8" s="32" t="inlineStr">
+        <is>
+          <t>₹0.00 (Exempt gift u/s 56(2)(x))</t>
+        </is>
+      </c>
+      <c r="F8" s="32" t="inlineStr">
+        <is>
+          <t>Kept off payroll; zero salary tax leakage</t>
+        </is>
       </c>
       <c r="G8" s="32" t="n">
         <v>-80000</v>
@@ -57835,25 +57855,31 @@
     <row r="9">
       <c r="A9" s="33" t="inlineStr">
         <is>
-          <t>TOTAL (3 EMPLOYEES COMBINED)</t>
+          <t>TOTAL ANNUAL TAX DEDUCTION</t>
         </is>
       </c>
       <c r="B9" s="33" t="inlineStr">
         <is>
-          <t>All 3 Members</t>
+          <t>You + Mother Combined</t>
         </is>
       </c>
       <c r="C9" s="34" t="n">
-        <v>3825000</v>
-      </c>
-      <c r="D9" s="34" t="n">
-        <v>225000</v>
-      </c>
-      <c r="E9" s="34" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="F9" s="34" t="n">
-        <v>240000</v>
+        <v>1755000</v>
+      </c>
+      <c r="D9" s="34" t="inlineStr">
+        <is>
+          <t>₹2,19,000 total deduction</t>
+        </is>
+      </c>
+      <c r="E9" s="34" t="inlineStr">
+        <is>
+          <t>₹0.00 Total Personal Tax</t>
+        </is>
+      </c>
+      <c r="F9" s="34" t="inlineStr">
+        <is>
+          <t>Saves ₹4,41,700/yr corporate tax cleanly</t>
+        </is>
       </c>
       <c r="G9" s="34" t="n">
         <v>-240000</v>
@@ -57868,14 +57894,14 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2. STATUTORY FLOWBACK ENGINE &amp; AUDIT TRAIL</t>
+          <t>2. WHY THE ARTIFICIAL FAMILY SCHEME WAS REJECTED (SECTION 37 &amp; GAAR AUDIT)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="27" t="inlineStr">
         <is>
-          <t>Step 1: Employment Contract &amp; Monthly Remittance</t>
+          <t>Section 37(1) Business Purpose Test: Non-working relatives (aunts/grandmothers) cannot justify ₹1L/mo salaries on a 1-person futures desk.</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -57887,7 +57913,7 @@
     <row r="13">
       <c r="A13" s="27" t="inlineStr">
         <is>
-          <t>Step 2: Section 87A Tax Eraser</t>
+          <t>Section 40A(2) Relative Disallowance: Tax Officer disallows unreasonable payments to relatives exceeding Fair Market Value.</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -57899,7 +57925,7 @@
     <row r="14">
       <c r="A14" s="27" t="inlineStr">
         <is>
-          <t>Step 3: Director Relative Loanback (Rule 2(1)(c)(viii))</t>
+          <t>Chapter X-A GAAR &amp; Round-Tripping: Sizing investments under ₹9.4L to dodge SFT thresholds and circular loanbacks triggers 200% penalty u/s 270A.</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -57911,7 +57937,7 @@
     <row r="15">
       <c r="A15" s="27" t="inlineStr">
         <is>
-          <t>Step 4: Grandmother Blood Gift u/s 56(2)(x)</t>
+          <t>Microstructure Reality: 4,800 lots equals 65.7% of median front-month OI. Transition to CME Henry Hub past ₹50 Cr is essential.</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -57923,7 +57949,7 @@
     <row r="16">
       <c r="A16" s="27" t="inlineStr">
         <is>
-          <t>Step 5: Annual ROC Compliance (Form DPT-3)</t>
+          <t>Compliance Mandate: Retain profits in company at 25.17%, scale cleanly, and prepare Level 4 GIFT City IFSC registration for global volume.</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
